--- a/planilhas_para_atualizar/CARGA_ENERGIA_2026.xlsx
+++ b/planilhas_para_atualizar/CARGA_ENERGIA_2026.xlsx
@@ -1,42 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d9161614252c80cc/Cursos/Antigraviti ^M ClaudeCode - YT/projeto8_enecel/planilhas_para_atualizar/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="21" documentId="11_684DC48CE616AFFA3DFC9890E2B2F2704B6F8B0A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C8510466-46A9-4735-88CB-C8A01DFB272C}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$1</definedName>
-  </definedNames>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1412" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1436" uniqueCount="12">
   <si>
     <t>id_subsistema</t>
   </si>
@@ -77,13 +55,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="dd/mm/yyyy\ hh:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="#,##0.00000000"/>
-    <numFmt numFmtId="166" formatCode="dd\-mm\-yy\ hh:mm:ss"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="@"/>
+    <numFmt numFmtId="165" formatCode="dd/mm/yyyy hh:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00000000"/>
+    <numFmt numFmtId="167" formatCode="dd-mm-yy hh:mm:ss"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -137,34 +116,26 @@
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -202,7 +173,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -236,7 +207,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -271,10 +241,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -447,18 +416,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E705"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D717"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="1"/>
-    <col min="2" max="2" width="21.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="9.140625" style="1"/>
+    <col min="3" max="3" width="9.140625" style="2"/>
+    <col min="4" max="4" width="9.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -472,7 +439,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -483,10 +450,10 @@
         <v>46023</v>
       </c>
       <c r="D2" s="3">
-        <v>7649.4388749999998</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+        <v>7649.438875</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -500,7 +467,7 @@
         <v>12269.97258333</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -514,7 +481,7 @@
         <v>11203.19591667</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
@@ -528,7 +495,7 @@
         <v>40463.7935</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -539,10 +506,10 @@
         <v>46024</v>
       </c>
       <c r="D6" s="3">
-        <v>8235.2083333299997</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8235.20833333</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -553,10 +520,10 @@
         <v>46024</v>
       </c>
       <c r="D7" s="3">
-        <v>13703.662208330001</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+        <v>13703.66220833</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
@@ -570,7 +537,7 @@
         <v>12560.747125</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
@@ -584,7 +551,7 @@
         <v>44884.27916667</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
@@ -595,10 +562,10 @@
         <v>46025</v>
       </c>
       <c r="D10" s="3">
-        <v>8129.2916666700003</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8129.29166667</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
         <v>5</v>
       </c>
@@ -609,10 +576,10 @@
         <v>46025</v>
       </c>
       <c r="D11" s="3">
-        <v>13457.452916669999</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+        <v>13457.45291667</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
         <v>6</v>
       </c>
@@ -623,10 +590,10 @@
         <v>46025</v>
       </c>
       <c r="D12" s="3">
-        <v>12131.754124999999</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+        <v>12131.754125</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
         <v>7</v>
       </c>
@@ -637,10 +604,10 @@
         <v>46025</v>
       </c>
       <c r="D13" s="3">
-        <v>43201.079916670002</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+        <v>43201.07991667</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
       <c r="A14" s="1" t="s">
         <v>4</v>
       </c>
@@ -651,10 +618,10 @@
         <v>46026</v>
       </c>
       <c r="D14" s="3">
-        <v>7888.9912083299996</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+        <v>7888.99120833</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
       <c r="A15" s="1" t="s">
         <v>5</v>
       </c>
@@ -665,10 +632,10 @@
         <v>46026</v>
       </c>
       <c r="D15" s="3">
-        <v>12708.166499999999</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+        <v>12708.1665</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
       <c r="A16" s="1" t="s">
         <v>6</v>
       </c>
@@ -682,7 +649,7 @@
         <v>10540.81058333</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4">
       <c r="A17" s="1" t="s">
         <v>7</v>
       </c>
@@ -696,7 +663,7 @@
         <v>40391.986375</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4">
       <c r="A18" s="1" t="s">
         <v>4</v>
       </c>
@@ -707,10 +674,10 @@
         <v>46027</v>
       </c>
       <c r="D18" s="3">
-        <v>8499.9761249999992</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8499.976124999999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
       <c r="A19" s="1" t="s">
         <v>5</v>
       </c>
@@ -724,7 +691,7 @@
         <v>14019.96679167</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4">
       <c r="A20" s="1" t="s">
         <v>6</v>
       </c>
@@ -735,10 +702,10 @@
         <v>46027</v>
       </c>
       <c r="D20" s="3">
-        <v>12786.241666669999</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+        <v>12786.24166667</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
       <c r="A21" s="1" t="s">
         <v>7</v>
       </c>
@@ -749,10 +716,10 @@
         <v>46027</v>
       </c>
       <c r="D21" s="3">
-        <v>43145.793708329998</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+        <v>43145.79370833</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
       <c r="A22" s="1" t="s">
         <v>4</v>
       </c>
@@ -763,10 +730,10 @@
         <v>46028</v>
       </c>
       <c r="D22" s="3">
-        <v>8471.5494999999992</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8471.549499999999</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
       <c r="A23" s="1" t="s">
         <v>5</v>
       </c>
@@ -777,10 +744,10 @@
         <v>46028</v>
       </c>
       <c r="D23" s="3">
-        <v>14193.675499999999</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+        <v>14193.6755</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
       <c r="A24" s="1" t="s">
         <v>6</v>
       </c>
@@ -794,7 +761,7 @@
         <v>14210.00229167</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4">
       <c r="A25" s="1" t="s">
         <v>7</v>
       </c>
@@ -805,10 +772,10 @@
         <v>46028</v>
       </c>
       <c r="D25" s="3">
-        <v>43893.261708329999</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+        <v>43893.26170833</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
       <c r="A26" s="1" t="s">
         <v>4</v>
       </c>
@@ -819,10 +786,10 @@
         <v>46029</v>
       </c>
       <c r="D26" s="3">
-        <v>8340.2170833300006</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8340.217083330001</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
       <c r="A27" s="1" t="s">
         <v>5</v>
       </c>
@@ -833,10 +800,10 @@
         <v>46029</v>
       </c>
       <c r="D27" s="3">
-        <v>14280.466708329999</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+        <v>14280.46670833</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
       <c r="A28" s="1" t="s">
         <v>6</v>
       </c>
@@ -847,10 +814,10 @@
         <v>46029</v>
       </c>
       <c r="D28" s="3">
-        <v>15939.287541670001</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+        <v>15939.28754167</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
       <c r="A29" s="1" t="s">
         <v>7</v>
       </c>
@@ -861,10 +828,10 @@
         <v>46029</v>
       </c>
       <c r="D29" s="3">
-        <v>45859.375583330002</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+        <v>45859.37558333</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
       <c r="A30" s="1" t="s">
         <v>4</v>
       </c>
@@ -875,10 +842,10 @@
         <v>46030</v>
       </c>
       <c r="D30" s="3">
-        <v>8369.8532916700005</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8369.853291670001</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
       <c r="A31" s="1" t="s">
         <v>5</v>
       </c>
@@ -892,7 +859,7 @@
         <v>14477.01858333</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4">
       <c r="A32" s="1" t="s">
         <v>6</v>
       </c>
@@ -906,7 +873,7 @@
         <v>16435.15258333</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4">
       <c r="A33" s="1" t="s">
         <v>7</v>
       </c>
@@ -917,10 +884,10 @@
         <v>46030</v>
       </c>
       <c r="D33" s="3">
-        <v>47396.491416669996</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+        <v>47396.49141667</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
       <c r="A34" s="1" t="s">
         <v>4</v>
       </c>
@@ -931,10 +898,10 @@
         <v>46031</v>
       </c>
       <c r="D34" s="3">
-        <v>8306.4809166699997</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8306.48091667</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
       <c r="A35" s="1" t="s">
         <v>5</v>
       </c>
@@ -945,10 +912,10 @@
         <v>46031</v>
       </c>
       <c r="D35" s="3">
-        <v>14492.449541669999</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+        <v>14492.44954167</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
       <c r="A36" s="1" t="s">
         <v>6</v>
       </c>
@@ -962,7 +929,7 @@
         <v>16384.60745833</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4">
       <c r="A37" s="1" t="s">
         <v>7</v>
       </c>
@@ -973,10 +940,10 @@
         <v>46031</v>
       </c>
       <c r="D37" s="3">
-        <v>49702.037166670001</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+        <v>49702.03716667</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
       <c r="A38" s="1" t="s">
         <v>4</v>
       </c>
@@ -987,10 +954,10 @@
         <v>46032</v>
       </c>
       <c r="D38" s="3">
-        <v>8267.0761249999996</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8267.076125</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
       <c r="A39" s="1" t="s">
         <v>5</v>
       </c>
@@ -1001,10 +968,10 @@
         <v>46032</v>
       </c>
       <c r="D39" s="3">
-        <v>13749.465708330001</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+        <v>13749.46570833</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
       <c r="A40" s="1" t="s">
         <v>6</v>
       </c>
@@ -1015,10 +982,10 @@
         <v>46032</v>
       </c>
       <c r="D40" s="3">
-        <v>13645.917458329999</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+        <v>13645.91745833</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
       <c r="A41" s="1" t="s">
         <v>7</v>
       </c>
@@ -1032,7 +999,7 @@
         <v>46929.53729167</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4">
       <c r="A42" s="1" t="s">
         <v>4</v>
       </c>
@@ -1043,10 +1010,10 @@
         <v>46033</v>
       </c>
       <c r="D42" s="3">
-        <v>7802.3812083299999</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+        <v>7802.38120833</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
       <c r="A43" s="1" t="s">
         <v>5</v>
       </c>
@@ -1060,7 +1027,7 @@
         <v>12942.20554167</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4">
       <c r="A44" s="1" t="s">
         <v>6</v>
       </c>
@@ -1074,7 +1041,7 @@
         <v>11519.192625</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4">
       <c r="A45" s="1" t="s">
         <v>7</v>
       </c>
@@ -1085,10 +1052,10 @@
         <v>46033</v>
       </c>
       <c r="D45" s="3">
-        <v>43884.431416669999</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+        <v>43884.43141667</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
       <c r="A46" s="1" t="s">
         <v>4</v>
       </c>
@@ -1099,10 +1066,10 @@
         <v>46034</v>
       </c>
       <c r="D46" s="3">
-        <v>8093.7920833300004</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8093.79208333</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
       <c r="A47" s="1" t="s">
         <v>5</v>
       </c>
@@ -1116,7 +1083,7 @@
         <v>14600.39341667</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4">
       <c r="A48" s="1" t="s">
         <v>6</v>
       </c>
@@ -1127,10 +1094,10 @@
         <v>46034</v>
       </c>
       <c r="D48" s="3">
-        <v>15062.539624999999</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+        <v>15062.539625</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4">
       <c r="A49" s="1" t="s">
         <v>7</v>
       </c>
@@ -1141,10 +1108,10 @@
         <v>46034</v>
       </c>
       <c r="D49" s="3">
-        <v>51195.190541670003</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+        <v>51195.19054167</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4">
       <c r="A50" s="1" t="s">
         <v>4</v>
       </c>
@@ -1155,10 +1122,10 @@
         <v>46035</v>
       </c>
       <c r="D50" s="3">
-        <v>8308.7772083300006</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8308.777208330001</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4">
       <c r="A51" s="1" t="s">
         <v>5</v>
       </c>
@@ -1172,7 +1139,7 @@
         <v>14151.28995833</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4">
       <c r="A52" s="1" t="s">
         <v>6</v>
       </c>
@@ -1186,7 +1153,7 @@
         <v>15907.14679167</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4">
       <c r="A53" s="1" t="s">
         <v>7</v>
       </c>
@@ -1197,10 +1164,10 @@
         <v>46035</v>
       </c>
       <c r="D53" s="3">
-        <v>50856.151875000003</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+        <v>50856.151875</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4">
       <c r="A54" s="1" t="s">
         <v>4</v>
       </c>
@@ -1211,10 +1178,10 @@
         <v>46036</v>
       </c>
       <c r="D54" s="3">
-        <v>8241.7875416700008</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8241.787541670001</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
       <c r="A55" s="1" t="s">
         <v>5</v>
       </c>
@@ -1225,10 +1192,10 @@
         <v>46036</v>
       </c>
       <c r="D55" s="3">
-        <v>14431.449000000001</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+        <v>14431.449</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4">
       <c r="A56" s="1" t="s">
         <v>6</v>
       </c>
@@ -1239,10 +1206,10 @@
         <v>46036</v>
       </c>
       <c r="D56" s="3">
-        <v>16799.247958330001</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+        <v>16799.24795833</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4">
       <c r="A57" s="1" t="s">
         <v>7</v>
       </c>
@@ -1253,10 +1220,10 @@
         <v>46036</v>
       </c>
       <c r="D57" s="3">
-        <v>50148.740833329997</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+        <v>50148.74083333</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4">
       <c r="A58" s="1" t="s">
         <v>4</v>
       </c>
@@ -1267,10 +1234,10 @@
         <v>46037</v>
       </c>
       <c r="D58" s="3">
-        <v>8354.9995416700003</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8354.99954167</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4">
       <c r="A59" s="1" t="s">
         <v>5</v>
       </c>
@@ -1281,10 +1248,10 @@
         <v>46037</v>
       </c>
       <c r="D59" s="3">
-        <v>14467.519666669999</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+        <v>14467.51966667</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4">
       <c r="A60" s="1" t="s">
         <v>6</v>
       </c>
@@ -1298,7 +1265,7 @@
         <v>17722.70558333</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4">
       <c r="A61" s="1" t="s">
         <v>7</v>
       </c>
@@ -1309,10 +1276,10 @@
         <v>46037</v>
       </c>
       <c r="D61" s="3">
-        <v>49976.894791669998</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+        <v>49976.89479167</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4">
       <c r="A62" s="1" t="s">
         <v>4</v>
       </c>
@@ -1323,10 +1290,10 @@
         <v>46038</v>
       </c>
       <c r="D62" s="3">
-        <v>8497.2615000000005</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8497.261500000001</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4">
       <c r="A63" s="1" t="s">
         <v>5</v>
       </c>
@@ -1337,10 +1304,10 @@
         <v>46038</v>
       </c>
       <c r="D63" s="3">
-        <v>14744.605958329999</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+        <v>14744.60595833</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4">
       <c r="A64" s="1" t="s">
         <v>6</v>
       </c>
@@ -1354,7 +1321,7 @@
         <v>17931.13075</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:4">
       <c r="A65" s="1" t="s">
         <v>7</v>
       </c>
@@ -1365,10 +1332,10 @@
         <v>46038</v>
       </c>
       <c r="D65" s="3">
-        <v>50055.221166670002</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+        <v>50055.22116667</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4">
       <c r="A66" s="1" t="s">
         <v>4</v>
       </c>
@@ -1379,10 +1346,10 @@
         <v>46039</v>
       </c>
       <c r="D66" s="3">
-        <v>8165.3355416699997</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8165.33554167</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4">
       <c r="A67" s="1" t="s">
         <v>5</v>
       </c>
@@ -1396,7 +1363,7 @@
         <v>14047.20779167</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:4">
       <c r="A68" s="1" t="s">
         <v>6</v>
       </c>
@@ -1410,7 +1377,7 @@
         <v>15287.258125</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:4">
       <c r="A69" s="1" t="s">
         <v>7</v>
       </c>
@@ -1421,10 +1388,10 @@
         <v>46039</v>
       </c>
       <c r="D69" s="3">
-        <v>46924.950624999998</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46924.950625</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4">
       <c r="A70" s="1" t="s">
         <v>4</v>
       </c>
@@ -1435,10 +1402,10 @@
         <v>46040</v>
       </c>
       <c r="D70" s="3">
-        <v>7790.2123333299996</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+        <v>7790.21233333</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4">
       <c r="A71" s="1" t="s">
         <v>5</v>
       </c>
@@ -1449,10 +1416,10 @@
         <v>46040</v>
       </c>
       <c r="D71" s="3">
-        <v>12902.274416669999</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+        <v>12902.27441667</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4">
       <c r="A72" s="1" t="s">
         <v>6</v>
       </c>
@@ -1463,10 +1430,10 @@
         <v>46040</v>
       </c>
       <c r="D72" s="3">
-        <v>13303.362291670001</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+        <v>13303.36229167</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4">
       <c r="A73" s="1" t="s">
         <v>7</v>
       </c>
@@ -1480,7 +1447,7 @@
         <v>43471.70120833</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:4">
       <c r="A74" s="1" t="s">
         <v>4</v>
       </c>
@@ -1491,10 +1458,10 @@
         <v>46041</v>
       </c>
       <c r="D74" s="3">
-        <v>8283.9130833300005</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8283.913083330001</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4">
       <c r="A75" s="1" t="s">
         <v>5</v>
       </c>
@@ -1508,7 +1475,7 @@
         <v>14171.5195</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:4">
       <c r="A76" s="1" t="s">
         <v>6</v>
       </c>
@@ -1522,7 +1489,7 @@
         <v>15292.799625</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:4">
       <c r="A77" s="1" t="s">
         <v>7</v>
       </c>
@@ -1533,10 +1500,10 @@
         <v>46041</v>
       </c>
       <c r="D77" s="3">
-        <v>48526.489166669999</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+        <v>48526.48916667</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4">
       <c r="A78" s="1" t="s">
         <v>4</v>
       </c>
@@ -1547,10 +1514,10 @@
         <v>46042</v>
       </c>
       <c r="D78" s="3">
-        <v>8171.9318750000002</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8171.931875</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4">
       <c r="A79" s="1" t="s">
         <v>5</v>
       </c>
@@ -1561,10 +1528,10 @@
         <v>46042</v>
       </c>
       <c r="D79" s="3">
-        <v>14269.275291669999</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+        <v>14269.27529167</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4">
       <c r="A80" s="1" t="s">
         <v>6</v>
       </c>
@@ -1575,10 +1542,10 @@
         <v>46042</v>
       </c>
       <c r="D80" s="3">
-        <v>14928.681416670001</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+        <v>14928.68141667</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4">
       <c r="A81" s="1" t="s">
         <v>7</v>
       </c>
@@ -1589,10 +1556,10 @@
         <v>46042</v>
       </c>
       <c r="D81" s="3">
-        <v>45766.910416669998</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+        <v>45766.91041667</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4">
       <c r="A82" s="1" t="s">
         <v>4</v>
       </c>
@@ -1603,10 +1570,10 @@
         <v>46043</v>
       </c>
       <c r="D82" s="3">
-        <v>8335.1853333300005</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8335.185333330001</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4">
       <c r="A83" s="1" t="s">
         <v>5</v>
       </c>
@@ -1620,7 +1587,7 @@
         <v>13922.33720833</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:4">
       <c r="A84" s="1" t="s">
         <v>6</v>
       </c>
@@ -1631,10 +1598,10 @@
         <v>46043</v>
       </c>
       <c r="D84" s="3">
-        <v>15261.645583330001</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+        <v>15261.64558333</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4">
       <c r="A85" s="1" t="s">
         <v>7</v>
       </c>
@@ -1645,10 +1612,10 @@
         <v>46043</v>
       </c>
       <c r="D85" s="3">
-        <v>44642.826500000003</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+        <v>44642.8265</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4">
       <c r="A86" s="1" t="s">
         <v>4</v>
       </c>
@@ -1659,10 +1626,10 @@
         <v>46044</v>
       </c>
       <c r="D86" s="3">
-        <v>8225.8578333299993</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8225.857833329999</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4">
       <c r="A87" s="1" t="s">
         <v>5</v>
       </c>
@@ -1676,7 +1643,7 @@
         <v>13718.29645833</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:4">
       <c r="A88" s="1" t="s">
         <v>6</v>
       </c>
@@ -1690,7 +1657,7 @@
         <v>15594.81633333</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:4">
       <c r="A89" s="1" t="s">
         <v>7</v>
       </c>
@@ -1704,7 +1671,7 @@
         <v>44616.07675</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:4">
       <c r="A90" s="1" t="s">
         <v>4</v>
       </c>
@@ -1715,10 +1682,10 @@
         <v>46045</v>
       </c>
       <c r="D90" s="3">
-        <v>8382.7468750000007</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8382.746875000001</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4">
       <c r="A91" s="1" t="s">
         <v>5</v>
       </c>
@@ -1732,7 +1699,7 @@
         <v>13853.75808333</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:4">
       <c r="A92" s="1" t="s">
         <v>6</v>
       </c>
@@ -1743,10 +1710,10 @@
         <v>46045</v>
       </c>
       <c r="D92" s="3">
-        <v>15728.559583329999</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+        <v>15728.55958333</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4">
       <c r="A93" s="1" t="s">
         <v>7</v>
       </c>
@@ -1757,10 +1724,10 @@
         <v>46045</v>
       </c>
       <c r="D93" s="3">
-        <v>44294.642249999997</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+        <v>44294.64225</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4">
       <c r="A94" s="1" t="s">
         <v>4</v>
       </c>
@@ -1771,10 +1738,10 @@
         <v>46046</v>
       </c>
       <c r="D94" s="3">
-        <v>7885.4690833300001</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+        <v>7885.46908333</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4">
       <c r="A95" s="1" t="s">
         <v>5</v>
       </c>
@@ -1788,7 +1755,7 @@
         <v>13331.14516667</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:4">
       <c r="A96" s="1" t="s">
         <v>6</v>
       </c>
@@ -1799,10 +1766,10 @@
         <v>46046</v>
       </c>
       <c r="D96" s="3">
-        <v>14298.866541670001</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+        <v>14298.86654167</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4">
       <c r="A97" s="1" t="s">
         <v>7</v>
       </c>
@@ -1813,10 +1780,10 @@
         <v>46046</v>
       </c>
       <c r="D97" s="3">
-        <v>41854.735625000001</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+        <v>41854.735625</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4">
       <c r="A98" s="1" t="s">
         <v>4</v>
       </c>
@@ -1827,10 +1794,10 @@
         <v>46047</v>
       </c>
       <c r="D98" s="3">
-        <v>7668.9013333299999</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+        <v>7668.90133333</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4">
       <c r="A99" s="1" t="s">
         <v>5</v>
       </c>
@@ -1844,7 +1811,7 @@
         <v>12743.37729167</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:4">
       <c r="A100" s="1" t="s">
         <v>6</v>
       </c>
@@ -1855,10 +1822,10 @@
         <v>46047</v>
       </c>
       <c r="D100" s="3">
-        <v>13267.742749999999</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+        <v>13267.74275</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4">
       <c r="A101" s="1" t="s">
         <v>7</v>
       </c>
@@ -1869,10 +1836,10 @@
         <v>46047</v>
       </c>
       <c r="D101" s="3">
-        <v>39558.263916670003</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+        <v>39558.26391667</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4">
       <c r="A102" s="1" t="s">
         <v>4</v>
       </c>
@@ -1883,10 +1850,10 @@
         <v>46048</v>
       </c>
       <c r="D102" s="3">
-        <v>8300.2852916699994</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8300.285291669999</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4">
       <c r="A103" s="1" t="s">
         <v>5</v>
       </c>
@@ -1897,10 +1864,10 @@
         <v>46048</v>
       </c>
       <c r="D103" s="3">
-        <v>14147.911125000001</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+        <v>14147.911125</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4">
       <c r="A104" s="1" t="s">
         <v>6</v>
       </c>
@@ -1911,10 +1878,10 @@
         <v>46048</v>
       </c>
       <c r="D104" s="3">
-        <v>17350.682208329999</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+        <v>17350.68220833</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4">
       <c r="A105" s="1" t="s">
         <v>7</v>
       </c>
@@ -1925,10 +1892,10 @@
         <v>46048</v>
       </c>
       <c r="D105" s="3">
-        <v>46376.322749999999</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46376.32275</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4">
       <c r="A106" s="1" t="s">
         <v>4</v>
       </c>
@@ -1939,10 +1906,10 @@
         <v>46049</v>
       </c>
       <c r="D106" s="3">
-        <v>8064.9341666700002</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8064.93416667</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4">
       <c r="A107" s="1" t="s">
         <v>5</v>
       </c>
@@ -1956,7 +1923,7 @@
         <v>14050.79445833</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:4">
       <c r="A108" s="1" t="s">
         <v>6</v>
       </c>
@@ -1967,10 +1934,10 @@
         <v>46049</v>
       </c>
       <c r="D108" s="3">
-        <v>18561.297083329999</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+        <v>18561.29708333</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4">
       <c r="A109" s="1" t="s">
         <v>7</v>
       </c>
@@ -1981,10 +1948,10 @@
         <v>46049</v>
       </c>
       <c r="D109" s="3">
-        <v>48370.904541670003</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+        <v>48370.90454167</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4">
       <c r="A110" s="1" t="s">
         <v>4</v>
       </c>
@@ -1995,10 +1962,10 @@
         <v>46050</v>
       </c>
       <c r="D110" s="3">
-        <v>8051.8731666699996</v>
-      </c>
-    </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8051.87316667</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4">
       <c r="A111" s="1" t="s">
         <v>5</v>
       </c>
@@ -2012,7 +1979,7 @@
         <v>13914.089875</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:4">
       <c r="A112" s="1" t="s">
         <v>6</v>
       </c>
@@ -2023,10 +1990,10 @@
         <v>46050</v>
       </c>
       <c r="D112" s="3">
-        <v>19116.812249999999</v>
-      </c>
-    </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+        <v>19116.81225</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4">
       <c r="A113" s="1" t="s">
         <v>7</v>
       </c>
@@ -2037,10 +2004,10 @@
         <v>46050</v>
       </c>
       <c r="D113" s="3">
-        <v>49138.845166669998</v>
-      </c>
-    </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+        <v>49138.84516667</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4">
       <c r="A114" s="1" t="s">
         <v>4</v>
       </c>
@@ -2051,10 +2018,10 @@
         <v>46051</v>
       </c>
       <c r="D114" s="3">
-        <v>8452.6948749999992</v>
-      </c>
-    </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8452.694874999999</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4">
       <c r="A115" s="1" t="s">
         <v>5</v>
       </c>
@@ -2068,7 +2035,7 @@
         <v>14083.6505</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:4">
       <c r="A116" s="1" t="s">
         <v>6</v>
       </c>
@@ -2079,10 +2046,10 @@
         <v>46051</v>
       </c>
       <c r="D116" s="3">
-        <v>18061.003333330002</v>
-      </c>
-    </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+        <v>18061.00333333</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4">
       <c r="A117" s="1" t="s">
         <v>7</v>
       </c>
@@ -2093,10 +2060,10 @@
         <v>46051</v>
       </c>
       <c r="D117" s="3">
-        <v>49187.577541669998</v>
-      </c>
-    </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+        <v>49187.57754167</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4">
       <c r="A118" s="1" t="s">
         <v>4</v>
       </c>
@@ -2107,10 +2074,10 @@
         <v>46052</v>
       </c>
       <c r="D118" s="3">
-        <v>8536.2770416700005</v>
-      </c>
-    </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8536.27704167</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4">
       <c r="A119" s="1" t="s">
         <v>5</v>
       </c>
@@ -2124,7 +2091,7 @@
         <v>14118.18425</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:4">
       <c r="A120" s="1" t="s">
         <v>6</v>
       </c>
@@ -2135,10 +2102,10 @@
         <v>46052</v>
       </c>
       <c r="D120" s="3">
-        <v>16727.247208330002</v>
-      </c>
-    </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+        <v>16727.24720833</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4">
       <c r="A121" s="1" t="s">
         <v>7</v>
       </c>
@@ -2149,10 +2116,10 @@
         <v>46052</v>
       </c>
       <c r="D121" s="3">
-        <v>48479.811458329998</v>
-      </c>
-    </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+        <v>48479.81145833</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4">
       <c r="A122" s="1" t="s">
         <v>4</v>
       </c>
@@ -2163,10 +2130,10 @@
         <v>46053</v>
       </c>
       <c r="D122" s="3">
-        <v>8111.5573333299999</v>
-      </c>
-    </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8111.55733333</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4">
       <c r="A123" s="1" t="s">
         <v>5</v>
       </c>
@@ -2177,10 +2144,10 @@
         <v>46053</v>
       </c>
       <c r="D123" s="3">
-        <v>13713.378208329999</v>
-      </c>
-    </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+        <v>13713.37820833</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4">
       <c r="A124" s="1" t="s">
         <v>6</v>
       </c>
@@ -2194,7 +2161,7 @@
         <v>14206.246625</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:4">
       <c r="A125" s="1" t="s">
         <v>7</v>
       </c>
@@ -2205,10 +2172,10 @@
         <v>46053</v>
       </c>
       <c r="D125" s="3">
-        <v>45134.870708330003</v>
-      </c>
-    </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
+        <v>45134.87070833</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4">
       <c r="A126" s="1" t="s">
         <v>4</v>
       </c>
@@ -2219,10 +2186,10 @@
         <v>46054</v>
       </c>
       <c r="D126" s="3">
-        <v>7907.7898750000004</v>
-      </c>
-    </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
+        <v>7907.789875</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4">
       <c r="A127" s="1" t="s">
         <v>5</v>
       </c>
@@ -2236,7 +2203,7 @@
         <v>12709.57429167</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:4">
       <c r="A128" s="1" t="s">
         <v>6</v>
       </c>
@@ -2250,7 +2217,7 @@
         <v>12950.6185</v>
       </c>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:4">
       <c r="A129" s="1" t="s">
         <v>7</v>
       </c>
@@ -2261,10 +2228,10 @@
         <v>46054</v>
       </c>
       <c r="D129" s="3">
-        <v>42714.195249999997</v>
-      </c>
-    </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
+        <v>42714.19525</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4">
       <c r="A130" s="1" t="s">
         <v>4</v>
       </c>
@@ -2275,10 +2242,10 @@
         <v>46055</v>
       </c>
       <c r="D130" s="3">
-        <v>8372.7917500000003</v>
-      </c>
-    </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8372.79175</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4">
       <c r="A131" s="1" t="s">
         <v>5</v>
       </c>
@@ -2292,7 +2259,7 @@
         <v>14226.37270833</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:4">
       <c r="A132" s="1" t="s">
         <v>6</v>
       </c>
@@ -2303,10 +2270,10 @@
         <v>46055</v>
       </c>
       <c r="D132" s="3">
-        <v>16318.825500000001</v>
-      </c>
-    </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
+        <v>16318.8255</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4">
       <c r="A133" s="1" t="s">
         <v>7</v>
       </c>
@@ -2320,7 +2287,7 @@
         <v>48130.97066667</v>
       </c>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:4">
       <c r="A134" s="1" t="s">
         <v>4</v>
       </c>
@@ -2331,10 +2298,10 @@
         <v>46056</v>
       </c>
       <c r="D134" s="3">
-        <v>8585.2927916699991</v>
-      </c>
-    </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8585.292791669999</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4">
       <c r="A135" s="1" t="s">
         <v>5</v>
       </c>
@@ -2348,7 +2315,7 @@
         <v>14623.46154167</v>
       </c>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:4">
       <c r="A136" s="1" t="s">
         <v>6</v>
       </c>
@@ -2362,7 +2329,7 @@
         <v>17363.05975</v>
       </c>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:4">
       <c r="A137" s="1" t="s">
         <v>7</v>
       </c>
@@ -2373,10 +2340,10 @@
         <v>46056</v>
       </c>
       <c r="D137" s="3">
-        <v>48711.308958330002</v>
-      </c>
-    </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
+        <v>48711.30895833</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4">
       <c r="A138" s="1" t="s">
         <v>4</v>
       </c>
@@ -2387,10 +2354,10 @@
         <v>46057</v>
       </c>
       <c r="D138" s="3">
-        <v>8543.8902916700008</v>
-      </c>
-    </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8543.890291670001</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4">
       <c r="A139" s="1" t="s">
         <v>5</v>
       </c>
@@ -2404,7 +2371,7 @@
         <v>14954.67470833</v>
       </c>
     </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:4">
       <c r="A140" s="1" t="s">
         <v>6</v>
       </c>
@@ -2415,10 +2382,10 @@
         <v>46057</v>
       </c>
       <c r="D140" s="3">
-        <v>17114.012458329998</v>
-      </c>
-    </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
+        <v>17114.01245833</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4">
       <c r="A141" s="1" t="s">
         <v>7</v>
       </c>
@@ -2432,7 +2399,7 @@
         <v>48913.12629167</v>
       </c>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:4">
       <c r="A142" s="1" t="s">
         <v>4</v>
       </c>
@@ -2443,10 +2410,10 @@
         <v>46058</v>
       </c>
       <c r="D142" s="3">
-        <v>8630.3144166700004</v>
-      </c>
-    </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8630.31441667</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4">
       <c r="A143" s="1" t="s">
         <v>5</v>
       </c>
@@ -2460,7 +2427,7 @@
         <v>14726.29925</v>
       </c>
     </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:4">
       <c r="A144" s="1" t="s">
         <v>6</v>
       </c>
@@ -2474,7 +2441,7 @@
         <v>17918.76041667</v>
       </c>
     </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:4">
       <c r="A145" s="1" t="s">
         <v>7</v>
       </c>
@@ -2485,10 +2452,10 @@
         <v>46058</v>
       </c>
       <c r="D145" s="3">
-        <v>48791.400541670002</v>
-      </c>
-    </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
+        <v>48791.40054167</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4">
       <c r="A146" s="1" t="s">
         <v>4</v>
       </c>
@@ -2502,7 +2469,7 @@
         <v>8412.89954167</v>
       </c>
     </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:4">
       <c r="A147" s="1" t="s">
         <v>5</v>
       </c>
@@ -2516,7 +2483,7 @@
         <v>14063.714</v>
       </c>
     </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:4">
       <c r="A148" s="1" t="s">
         <v>6</v>
       </c>
@@ -2527,10 +2494,10 @@
         <v>46059</v>
       </c>
       <c r="D148" s="3">
-        <v>18461.863249999999</v>
-      </c>
-    </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
+        <v>18461.86325</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4">
       <c r="A149" s="1" t="s">
         <v>7</v>
       </c>
@@ -2541,10 +2508,10 @@
         <v>46059</v>
       </c>
       <c r="D149" s="3">
-        <v>49429.308708329998</v>
-      </c>
-    </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
+        <v>49429.30870833</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4">
       <c r="A150" s="1" t="s">
         <v>4</v>
       </c>
@@ -2555,10 +2522,10 @@
         <v>46060</v>
       </c>
       <c r="D150" s="3">
-        <v>7917.8200416700001</v>
-      </c>
-    </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
+        <v>7917.82004167</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4">
       <c r="A151" s="1" t="s">
         <v>5</v>
       </c>
@@ -2572,7 +2539,7 @@
         <v>13489.48804167</v>
       </c>
     </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:4">
       <c r="A152" s="1" t="s">
         <v>6</v>
       </c>
@@ -2583,10 +2550,10 @@
         <v>46060</v>
       </c>
       <c r="D152" s="3">
-        <v>15396.744124999999</v>
-      </c>
-    </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
+        <v>15396.744125</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4">
       <c r="A153" s="1" t="s">
         <v>7</v>
       </c>
@@ -2597,10 +2564,10 @@
         <v>46060</v>
       </c>
       <c r="D153" s="3">
-        <v>46125.334458329999</v>
-      </c>
-    </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46125.33445833</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4">
       <c r="A154" s="1" t="s">
         <v>4</v>
       </c>
@@ -2611,10 +2578,10 @@
         <v>46061</v>
       </c>
       <c r="D154" s="3">
-        <v>7557.0563750000001</v>
-      </c>
-    </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
+        <v>7557.056375</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4">
       <c r="A155" s="1" t="s">
         <v>5</v>
       </c>
@@ -2628,7 +2595,7 @@
         <v>12381.40716667</v>
       </c>
     </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:4">
       <c r="A156" s="1" t="s">
         <v>6</v>
       </c>
@@ -2639,10 +2606,10 @@
         <v>46061</v>
       </c>
       <c r="D156" s="3">
-        <v>12375.970083329999</v>
-      </c>
-    </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
+        <v>12375.97008333</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4">
       <c r="A157" s="1" t="s">
         <v>7</v>
       </c>
@@ -2653,10 +2620,10 @@
         <v>46061</v>
       </c>
       <c r="D157" s="3">
-        <v>41805.482083329996</v>
-      </c>
-    </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
+        <v>41805.48208333</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4">
       <c r="A158" s="1" t="s">
         <v>4</v>
       </c>
@@ -2667,10 +2634,10 @@
         <v>46062</v>
       </c>
       <c r="D158" s="3">
-        <v>8164.7334583299998</v>
-      </c>
-    </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8164.73345833</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4">
       <c r="A159" s="1" t="s">
         <v>5</v>
       </c>
@@ -2681,10 +2648,10 @@
         <v>46062</v>
       </c>
       <c r="D159" s="3">
-        <v>13041.530541669999</v>
-      </c>
-    </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
+        <v>13041.53054167</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4">
       <c r="A160" s="1" t="s">
         <v>6</v>
       </c>
@@ -2698,7 +2665,7 @@
         <v>16398.73866667</v>
       </c>
     </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:4">
       <c r="A161" s="1" t="s">
         <v>7</v>
       </c>
@@ -2709,10 +2676,10 @@
         <v>46062</v>
       </c>
       <c r="D161" s="3">
-        <v>46366.418541669998</v>
-      </c>
-    </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46366.41854167</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4">
       <c r="A162" s="1" t="s">
         <v>4</v>
       </c>
@@ -2723,10 +2690,10 @@
         <v>46063</v>
       </c>
       <c r="D162" s="3">
-        <v>8239.9668333299996</v>
-      </c>
-    </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8239.96683333</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4">
       <c r="A163" s="1" t="s">
         <v>5</v>
       </c>
@@ -2737,10 +2704,10 @@
         <v>46063</v>
       </c>
       <c r="D163" s="3">
-        <v>13432.582541670001</v>
-      </c>
-    </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
+        <v>13432.58254167</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4">
       <c r="A164" s="1" t="s">
         <v>6</v>
       </c>
@@ -2751,10 +2718,10 @@
         <v>46063</v>
       </c>
       <c r="D164" s="3">
-        <v>17665.838291669999</v>
-      </c>
-    </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
+        <v>17665.83829167</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4">
       <c r="A165" s="1" t="s">
         <v>7</v>
       </c>
@@ -2765,10 +2732,10 @@
         <v>46063</v>
       </c>
       <c r="D165" s="3">
-        <v>46872.550958330001</v>
-      </c>
-    </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46872.55095833</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4">
       <c r="A166" s="1" t="s">
         <v>4</v>
       </c>
@@ -2779,10 +2746,10 @@
         <v>46064</v>
       </c>
       <c r="D166" s="3">
-        <v>8202.3174166699991</v>
-      </c>
-    </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8202.317416669999</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4">
       <c r="A167" s="1" t="s">
         <v>5</v>
       </c>
@@ -2793,10 +2760,10 @@
         <v>46064</v>
       </c>
       <c r="D167" s="3">
-        <v>13606.555708329999</v>
-      </c>
-    </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
+        <v>13606.55570833</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4">
       <c r="A168" s="1" t="s">
         <v>6</v>
       </c>
@@ -2807,10 +2774,10 @@
         <v>46064</v>
       </c>
       <c r="D168" s="3">
-        <v>18534.916874999999</v>
-      </c>
-    </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
+        <v>18534.916875</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4">
       <c r="A169" s="1" t="s">
         <v>7</v>
       </c>
@@ -2821,10 +2788,10 @@
         <v>46064</v>
       </c>
       <c r="D169" s="3">
-        <v>48302.594958330003</v>
-      </c>
-    </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
+        <v>48302.59495833</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4">
       <c r="A170" s="1" t="s">
         <v>4</v>
       </c>
@@ -2835,10 +2802,10 @@
         <v>46065</v>
       </c>
       <c r="D170" s="3">
-        <v>8388.5102499999994</v>
-      </c>
-    </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8388.510249999999</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4">
       <c r="A171" s="1" t="s">
         <v>5</v>
       </c>
@@ -2852,7 +2819,7 @@
         <v>13800.83470833</v>
       </c>
     </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:4">
       <c r="A172" s="1" t="s">
         <v>6</v>
       </c>
@@ -2863,10 +2830,10 @@
         <v>46065</v>
       </c>
       <c r="D172" s="3">
-        <v>19089.169249999999</v>
-      </c>
-    </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
+        <v>19089.16925</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4">
       <c r="A173" s="1" t="s">
         <v>7</v>
       </c>
@@ -2877,10 +2844,10 @@
         <v>46065</v>
       </c>
       <c r="D173" s="3">
-        <v>49654.143833330003</v>
-      </c>
-    </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
+        <v>49654.14383333</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4">
       <c r="A174" s="1" t="s">
         <v>4</v>
       </c>
@@ -2891,10 +2858,10 @@
         <v>46066</v>
       </c>
       <c r="D174" s="3">
-        <v>8201.3864166700005</v>
-      </c>
-    </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8201.38641667</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4">
       <c r="A175" s="1" t="s">
         <v>5</v>
       </c>
@@ -2905,10 +2872,10 @@
         <v>46066</v>
       </c>
       <c r="D175" s="3">
-        <v>13782.250249999999</v>
-      </c>
-    </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
+        <v>13782.25025</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4">
       <c r="A176" s="1" t="s">
         <v>6</v>
       </c>
@@ -2919,10 +2886,10 @@
         <v>46066</v>
       </c>
       <c r="D176" s="3">
-        <v>17987.053416670002</v>
-      </c>
-    </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
+        <v>17987.05341667</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4">
       <c r="A177" s="1" t="s">
         <v>7</v>
       </c>
@@ -2933,10 +2900,10 @@
         <v>46066</v>
       </c>
       <c r="D177" s="3">
-        <v>50724.269166669998</v>
-      </c>
-    </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
+        <v>50724.26916667</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4">
       <c r="A178" s="1" t="s">
         <v>4</v>
       </c>
@@ -2950,7 +2917,7 @@
         <v>7928.15191667</v>
       </c>
     </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:4">
       <c r="A179" s="1" t="s">
         <v>5</v>
       </c>
@@ -2964,7 +2931,7 @@
         <v>12816.964</v>
       </c>
     </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:4">
       <c r="A180" s="1" t="s">
         <v>6</v>
       </c>
@@ -2978,7 +2945,7 @@
         <v>14046.36408333</v>
       </c>
     </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:4">
       <c r="A181" s="1" t="s">
         <v>7</v>
       </c>
@@ -2989,10 +2956,10 @@
         <v>46067</v>
       </c>
       <c r="D181" s="3">
-        <v>47042.970333329999</v>
-      </c>
-    </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
+        <v>47042.97033333</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4">
       <c r="A182" s="1" t="s">
         <v>4</v>
       </c>
@@ -3003,10 +2970,10 @@
         <v>46068</v>
       </c>
       <c r="D182" s="3">
-        <v>7542.4377500000001</v>
-      </c>
-    </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
+        <v>7542.43775</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4">
       <c r="A183" s="1" t="s">
         <v>5</v>
       </c>
@@ -3020,7 +2987,7 @@
         <v>11874.47804167</v>
       </c>
     </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:4">
       <c r="A184" s="1" t="s">
         <v>6</v>
       </c>
@@ -3031,10 +2998,10 @@
         <v>46068</v>
       </c>
       <c r="D184" s="3">
-        <v>12684.289124999999</v>
-      </c>
-    </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
+        <v>12684.289125</v>
+      </c>
+    </row>
+    <row r="185" spans="1:4">
       <c r="A185" s="1" t="s">
         <v>7</v>
       </c>
@@ -3045,10 +3012,10 @@
         <v>46068</v>
       </c>
       <c r="D185" s="3">
-        <v>43809.900333329999</v>
-      </c>
-    </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
+        <v>43809.90033333</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4">
       <c r="A186" s="1" t="s">
         <v>4</v>
       </c>
@@ -3062,7 +3029,7 @@
         <v>7700.93</v>
       </c>
     </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:4">
       <c r="A187" s="1" t="s">
         <v>5</v>
       </c>
@@ -3076,7 +3043,7 @@
         <v>12182.42216667</v>
       </c>
     </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:4">
       <c r="A188" s="1" t="s">
         <v>6</v>
       </c>
@@ -3090,7 +3057,7 @@
         <v>15779.637375</v>
       </c>
     </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:4">
       <c r="A189" s="1" t="s">
         <v>7</v>
       </c>
@@ -3101,10 +3068,10 @@
         <v>46069</v>
       </c>
       <c r="D189" s="3">
-        <v>47965.103666670002</v>
-      </c>
-    </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
+        <v>47965.10366667</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4">
       <c r="A190" s="1" t="s">
         <v>4</v>
       </c>
@@ -3115,10 +3082,10 @@
         <v>46070</v>
       </c>
       <c r="D190" s="3">
-        <v>7752.6685833299998</v>
-      </c>
-    </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
+        <v>7752.66858333</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4">
       <c r="A191" s="1" t="s">
         <v>5</v>
       </c>
@@ -3132,7 +3099,7 @@
         <v>12441.62954167</v>
       </c>
     </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:4">
       <c r="A192" s="1" t="s">
         <v>6</v>
       </c>
@@ -3143,10 +3110,10 @@
         <v>46070</v>
       </c>
       <c r="D192" s="3">
-        <v>16527.146000000001</v>
-      </c>
-    </row>
-    <row r="193" spans="1:4" x14ac:dyDescent="0.25">
+        <v>16527.146</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4">
       <c r="A193" s="1" t="s">
         <v>7</v>
       </c>
@@ -3157,10 +3124,10 @@
         <v>46070</v>
       </c>
       <c r="D193" s="3">
-        <v>48931.586791670001</v>
-      </c>
-    </row>
-    <row r="194" spans="1:4" x14ac:dyDescent="0.25">
+        <v>48931.58679167</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4">
       <c r="A194" s="1" t="s">
         <v>4</v>
       </c>
@@ -3174,7 +3141,7 @@
         <v>7955.412875</v>
       </c>
     </row>
-    <row r="195" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:4">
       <c r="A195" s="1" t="s">
         <v>5</v>
       </c>
@@ -3188,7 +3155,7 @@
         <v>13386.84</v>
       </c>
     </row>
-    <row r="196" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:4">
       <c r="A196" s="1" t="s">
         <v>6</v>
       </c>
@@ -3199,10 +3166,10 @@
         <v>46071</v>
       </c>
       <c r="D196" s="3">
-        <v>17408.380249999998</v>
-      </c>
-    </row>
-    <row r="197" spans="1:4" x14ac:dyDescent="0.25">
+        <v>17408.38025</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4">
       <c r="A197" s="1" t="s">
         <v>7</v>
       </c>
@@ -3213,10 +3180,10 @@
         <v>46071</v>
       </c>
       <c r="D197" s="3">
-        <v>52273.536666669999</v>
-      </c>
-    </row>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.25">
+        <v>52273.53666667</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4">
       <c r="A198" s="1" t="s">
         <v>4</v>
       </c>
@@ -3227,10 +3194,10 @@
         <v>46072</v>
       </c>
       <c r="D198" s="3">
-        <v>8229.3412916699999</v>
-      </c>
-    </row>
-    <row r="199" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8229.34129167</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4">
       <c r="A199" s="1" t="s">
         <v>5</v>
       </c>
@@ -3241,10 +3208,10 @@
         <v>46072</v>
       </c>
       <c r="D199" s="3">
-        <v>13984.676374999999</v>
-      </c>
-    </row>
-    <row r="200" spans="1:4" x14ac:dyDescent="0.25">
+        <v>13984.676375</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4">
       <c r="A200" s="1" t="s">
         <v>6</v>
       </c>
@@ -3255,10 +3222,10 @@
         <v>46072</v>
       </c>
       <c r="D200" s="3">
-        <v>17389.914499999999</v>
-      </c>
-    </row>
-    <row r="201" spans="1:4" x14ac:dyDescent="0.25">
+        <v>17389.9145</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4">
       <c r="A201" s="1" t="s">
         <v>7</v>
       </c>
@@ -3269,10 +3236,10 @@
         <v>46072</v>
       </c>
       <c r="D201" s="3">
-        <v>52477.497708329996</v>
-      </c>
-    </row>
-    <row r="202" spans="1:4" x14ac:dyDescent="0.25">
+        <v>52477.49770833</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4">
       <c r="A202" s="1" t="s">
         <v>4</v>
       </c>
@@ -3283,10 +3250,10 @@
         <v>46073</v>
       </c>
       <c r="D202" s="3">
-        <v>8345.1852916700009</v>
-      </c>
-    </row>
-    <row r="203" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8345.185291670001</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4">
       <c r="A203" s="1" t="s">
         <v>5</v>
       </c>
@@ -3300,7 +3267,7 @@
         <v>14068.72341667</v>
       </c>
     </row>
-    <row r="204" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:4">
       <c r="A204" s="1" t="s">
         <v>6</v>
       </c>
@@ -3311,10 +3278,10 @@
         <v>46073</v>
       </c>
       <c r="D204" s="3">
-        <v>17073.196499999998</v>
-      </c>
-    </row>
-    <row r="205" spans="1:4" x14ac:dyDescent="0.25">
+        <v>17073.1965</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4">
       <c r="A205" s="1" t="s">
         <v>7</v>
       </c>
@@ -3325,10 +3292,10 @@
         <v>46073</v>
       </c>
       <c r="D205" s="3">
-        <v>52592.077458330001</v>
-      </c>
-    </row>
-    <row r="206" spans="1:4" x14ac:dyDescent="0.25">
+        <v>52592.07745833</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4">
       <c r="A206" s="1" t="s">
         <v>4</v>
       </c>
@@ -3339,10 +3306,10 @@
         <v>46074</v>
       </c>
       <c r="D206" s="3">
-        <v>8044.3747083300004</v>
-      </c>
-    </row>
-    <row r="207" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8044.37470833</v>
+      </c>
+    </row>
+    <row r="207" spans="1:4">
       <c r="A207" s="1" t="s">
         <v>5</v>
       </c>
@@ -3353,10 +3320,10 @@
         <v>46074</v>
       </c>
       <c r="D207" s="3">
-        <v>13151.486041669999</v>
-      </c>
-    </row>
-    <row r="208" spans="1:4" x14ac:dyDescent="0.25">
+        <v>13151.48604167</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4">
       <c r="A208" s="1" t="s">
         <v>6</v>
       </c>
@@ -3370,7 +3337,7 @@
         <v>14062.367875</v>
       </c>
     </row>
-    <row r="209" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:4">
       <c r="A209" s="1" t="s">
         <v>7</v>
       </c>
@@ -3381,10 +3348,10 @@
         <v>46074</v>
       </c>
       <c r="D209" s="3">
-        <v>48181.170375000002</v>
-      </c>
-    </row>
-    <row r="210" spans="1:4" x14ac:dyDescent="0.25">
+        <v>48181.170375</v>
+      </c>
+    </row>
+    <row r="210" spans="1:4">
       <c r="A210" s="1" t="s">
         <v>4</v>
       </c>
@@ -3395,10 +3362,10 @@
         <v>46075</v>
       </c>
       <c r="D210" s="3">
-        <v>7826.9495833299998</v>
-      </c>
-    </row>
-    <row r="211" spans="1:4" x14ac:dyDescent="0.25">
+        <v>7826.94958333</v>
+      </c>
+    </row>
+    <row r="211" spans="1:4">
       <c r="A211" s="1" t="s">
         <v>5</v>
       </c>
@@ -3412,7 +3379,7 @@
         <v>12501.21816667</v>
       </c>
     </row>
-    <row r="212" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:4">
       <c r="A212" s="1" t="s">
         <v>6</v>
       </c>
@@ -3426,7 +3393,7 @@
         <v>12467.78795833</v>
       </c>
     </row>
-    <row r="213" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:4">
       <c r="A213" s="1" t="s">
         <v>7</v>
       </c>
@@ -3437,10 +3404,10 @@
         <v>46075</v>
       </c>
       <c r="D213" s="3">
-        <v>42922.673666670002</v>
-      </c>
-    </row>
-    <row r="214" spans="1:4" x14ac:dyDescent="0.25">
+        <v>42922.67366667</v>
+      </c>
+    </row>
+    <row r="214" spans="1:4">
       <c r="A214" s="1" t="s">
         <v>4</v>
       </c>
@@ -3451,10 +3418,10 @@
         <v>46076</v>
       </c>
       <c r="D214" s="3">
-        <v>8177.5892916700004</v>
-      </c>
-    </row>
-    <row r="215" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8177.58929167</v>
+      </c>
+    </row>
+    <row r="215" spans="1:4">
       <c r="A215" s="1" t="s">
         <v>5</v>
       </c>
@@ -3465,10 +3432,10 @@
         <v>46076</v>
       </c>
       <c r="D215" s="3">
-        <v>13883.333416670001</v>
-      </c>
-    </row>
-    <row r="216" spans="1:4" x14ac:dyDescent="0.25">
+        <v>13883.33341667</v>
+      </c>
+    </row>
+    <row r="216" spans="1:4">
       <c r="A216" s="1" t="s">
         <v>6</v>
       </c>
@@ -3482,7 +3449,7 @@
         <v>16081.39525</v>
       </c>
     </row>
-    <row r="217" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:4">
       <c r="A217" s="1" t="s">
         <v>7</v>
       </c>
@@ -3496,7 +3463,7 @@
         <v>49283.61833333</v>
       </c>
     </row>
-    <row r="218" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:4">
       <c r="A218" s="1" t="s">
         <v>4</v>
       </c>
@@ -3507,10 +3474,10 @@
         <v>46077</v>
       </c>
       <c r="D218" s="3">
-        <v>8323.6375416699993</v>
-      </c>
-    </row>
-    <row r="219" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8323.637541669999</v>
+      </c>
+    </row>
+    <row r="219" spans="1:4">
       <c r="A219" s="1" t="s">
         <v>5</v>
       </c>
@@ -3521,10 +3488,10 @@
         <v>46077</v>
       </c>
       <c r="D219" s="3">
-        <v>14413.793291669999</v>
-      </c>
-    </row>
-    <row r="220" spans="1:4" x14ac:dyDescent="0.25">
+        <v>14413.79329167</v>
+      </c>
+    </row>
+    <row r="220" spans="1:4">
       <c r="A220" s="1" t="s">
         <v>6</v>
       </c>
@@ -3535,10 +3502,10 @@
         <v>46077</v>
       </c>
       <c r="D220" s="3">
-        <v>16699.502958329998</v>
-      </c>
-    </row>
-    <row r="221" spans="1:4" x14ac:dyDescent="0.25">
+        <v>16699.50295833</v>
+      </c>
+    </row>
+    <row r="221" spans="1:4">
       <c r="A221" s="1" t="s">
         <v>7</v>
       </c>
@@ -3549,10 +3516,10 @@
         <v>46077</v>
       </c>
       <c r="D221" s="3">
-        <v>48997.400916669998</v>
-      </c>
-    </row>
-    <row r="222" spans="1:4" x14ac:dyDescent="0.25">
+        <v>48997.40091667</v>
+      </c>
+    </row>
+    <row r="222" spans="1:4">
       <c r="A222" s="1" t="s">
         <v>4</v>
       </c>
@@ -3563,10 +3530,10 @@
         <v>46078</v>
       </c>
       <c r="D222" s="3">
-        <v>8357.3880416699994</v>
-      </c>
-    </row>
-    <row r="223" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8357.388041669999</v>
+      </c>
+    </row>
+    <row r="223" spans="1:4">
       <c r="A223" s="1" t="s">
         <v>5</v>
       </c>
@@ -3580,7 +3547,7 @@
         <v>14464.656125</v>
       </c>
     </row>
-    <row r="224" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:4">
       <c r="A224" s="1" t="s">
         <v>6</v>
       </c>
@@ -3591,10 +3558,10 @@
         <v>46078</v>
       </c>
       <c r="D224" s="3">
-        <v>16483.458999999999</v>
-      </c>
-    </row>
-    <row r="225" spans="1:4" x14ac:dyDescent="0.25">
+        <v>16483.459</v>
+      </c>
+    </row>
+    <row r="225" spans="1:4">
       <c r="A225" s="1" t="s">
         <v>7</v>
       </c>
@@ -3608,7 +3575,7 @@
         <v>49793.96070833</v>
       </c>
     </row>
-    <row r="226" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:4">
       <c r="A226" s="1" t="s">
         <v>4</v>
       </c>
@@ -3619,10 +3586,10 @@
         <v>46079</v>
       </c>
       <c r="D226" s="3">
-        <v>8154.9161666700002</v>
-      </c>
-    </row>
-    <row r="227" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8154.91616667</v>
+      </c>
+    </row>
+    <row r="227" spans="1:4">
       <c r="A227" s="1" t="s">
         <v>5</v>
       </c>
@@ -3636,7 +3603,7 @@
         <v>14250.85366667</v>
       </c>
     </row>
-    <row r="228" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:4">
       <c r="A228" s="1" t="s">
         <v>6</v>
       </c>
@@ -3647,10 +3614,10 @@
         <v>46079</v>
       </c>
       <c r="D228" s="3">
-        <v>15917.889416669999</v>
-      </c>
-    </row>
-    <row r="229" spans="1:4" x14ac:dyDescent="0.25">
+        <v>15917.88941667</v>
+      </c>
+    </row>
+    <row r="229" spans="1:4">
       <c r="A229" s="1" t="s">
         <v>7</v>
       </c>
@@ -3661,10 +3628,10 @@
         <v>46079</v>
       </c>
       <c r="D229" s="3">
-        <v>50015.616291669998</v>
-      </c>
-    </row>
-    <row r="230" spans="1:4" x14ac:dyDescent="0.25">
+        <v>50015.61629167</v>
+      </c>
+    </row>
+    <row r="230" spans="1:4">
       <c r="A230" s="1" t="s">
         <v>4</v>
       </c>
@@ -3675,10 +3642,10 @@
         <v>46080</v>
       </c>
       <c r="D230" s="3">
-        <v>8125.5947083299998</v>
-      </c>
-    </row>
-    <row r="231" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8125.59470833</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4">
       <c r="A231" s="1" t="s">
         <v>5</v>
       </c>
@@ -3692,7 +3659,7 @@
         <v>13821.527</v>
       </c>
     </row>
-    <row r="232" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:4">
       <c r="A232" s="1" t="s">
         <v>6</v>
       </c>
@@ -3703,10 +3670,10 @@
         <v>46080</v>
       </c>
       <c r="D232" s="3">
-        <v>15768.012583330001</v>
-      </c>
-    </row>
-    <row r="233" spans="1:4" x14ac:dyDescent="0.25">
+        <v>15768.01258333</v>
+      </c>
+    </row>
+    <row r="233" spans="1:4">
       <c r="A233" s="1" t="s">
         <v>7</v>
       </c>
@@ -3717,10 +3684,10 @@
         <v>46080</v>
       </c>
       <c r="D233" s="3">
-        <v>48228.448875000002</v>
-      </c>
-    </row>
-    <row r="234" spans="1:4" x14ac:dyDescent="0.25">
+        <v>48228.448875</v>
+      </c>
+    </row>
+    <row r="234" spans="1:4">
       <c r="A234" s="1" t="s">
         <v>4</v>
       </c>
@@ -3731,10 +3698,10 @@
         <v>46081</v>
       </c>
       <c r="D234" s="3">
-        <v>7841.3017499999996</v>
-      </c>
-    </row>
-    <row r="235" spans="1:4" x14ac:dyDescent="0.25">
+        <v>7841.30175</v>
+      </c>
+    </row>
+    <row r="235" spans="1:4">
       <c r="A235" s="1" t="s">
         <v>5</v>
       </c>
@@ -3745,10 +3712,10 @@
         <v>46081</v>
       </c>
       <c r="D235" s="3">
-        <v>13155.967041669999</v>
-      </c>
-    </row>
-    <row r="236" spans="1:4" x14ac:dyDescent="0.25">
+        <v>13155.96704167</v>
+      </c>
+    </row>
+    <row r="236" spans="1:4">
       <c r="A236" s="1" t="s">
         <v>6</v>
       </c>
@@ -3759,10 +3726,10 @@
         <v>46081</v>
       </c>
       <c r="D236" s="3">
-        <v>13867.973625000001</v>
-      </c>
-    </row>
-    <row r="237" spans="1:4" x14ac:dyDescent="0.25">
+        <v>13867.973625</v>
+      </c>
+    </row>
+    <row r="237" spans="1:4">
       <c r="A237" s="1" t="s">
         <v>7</v>
       </c>
@@ -3773,10 +3740,10 @@
         <v>46081</v>
       </c>
       <c r="D237" s="3">
-        <v>43607.458916670003</v>
-      </c>
-    </row>
-    <row r="238" spans="1:4" x14ac:dyDescent="0.25">
+        <v>43607.45891667</v>
+      </c>
+    </row>
+    <row r="238" spans="1:4">
       <c r="A238" s="1" t="s">
         <v>4</v>
       </c>
@@ -3787,10 +3754,10 @@
         <v>46082</v>
       </c>
       <c r="D238" s="3">
-        <v>7664.9179583300001</v>
-      </c>
-    </row>
-    <row r="239" spans="1:4" x14ac:dyDescent="0.25">
+        <v>7664.91795833</v>
+      </c>
+    </row>
+    <row r="239" spans="1:4">
       <c r="A239" s="1" t="s">
         <v>5</v>
       </c>
@@ -3801,10 +3768,10 @@
         <v>46082</v>
       </c>
       <c r="D239" s="3">
-        <v>12101.146124999999</v>
-      </c>
-    </row>
-    <row r="240" spans="1:4" x14ac:dyDescent="0.25">
+        <v>12101.146125</v>
+      </c>
+    </row>
+    <row r="240" spans="1:4">
       <c r="A240" s="1" t="s">
         <v>6</v>
       </c>
@@ -3818,7 +3785,7 @@
         <v>12371.37308333</v>
       </c>
     </row>
-    <row r="241" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:4">
       <c r="A241" s="1" t="s">
         <v>7</v>
       </c>
@@ -3829,10 +3796,10 @@
         <v>46082</v>
       </c>
       <c r="D241" s="3">
-        <v>39466.921999999999</v>
-      </c>
-    </row>
-    <row r="242" spans="1:4" x14ac:dyDescent="0.25">
+        <v>39466.922</v>
+      </c>
+    </row>
+    <row r="242" spans="1:4">
       <c r="A242" s="1" t="s">
         <v>4</v>
       </c>
@@ -3843,10 +3810,10 @@
         <v>46083</v>
       </c>
       <c r="D242" s="3">
-        <v>8436.2297916700008</v>
-      </c>
-    </row>
-    <row r="243" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8436.229791670001</v>
+      </c>
+    </row>
+    <row r="243" spans="1:4">
       <c r="A243" s="1" t="s">
         <v>5</v>
       </c>
@@ -3860,7 +3827,7 @@
         <v>13560.08720833</v>
       </c>
     </row>
-    <row r="244" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:4">
       <c r="A244" s="1" t="s">
         <v>6</v>
       </c>
@@ -3874,7 +3841,7 @@
         <v>15727.81220833</v>
       </c>
     </row>
-    <row r="245" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:4">
       <c r="A245" s="1" t="s">
         <v>7</v>
       </c>
@@ -3885,10 +3852,10 @@
         <v>46083</v>
       </c>
       <c r="D245" s="3">
-        <v>45991.094291670001</v>
-      </c>
-    </row>
-    <row r="246" spans="1:4" x14ac:dyDescent="0.25">
+        <v>45991.09429167</v>
+      </c>
+    </row>
+    <row r="246" spans="1:4">
       <c r="A246" s="1" t="s">
         <v>4</v>
       </c>
@@ -3899,10 +3866,10 @@
         <v>46084</v>
       </c>
       <c r="D246" s="3">
-        <v>8380.2550416699996</v>
-      </c>
-    </row>
-    <row r="247" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8380.25504167</v>
+      </c>
+    </row>
+    <row r="247" spans="1:4">
       <c r="A247" s="1" t="s">
         <v>5</v>
       </c>
@@ -3916,7 +3883,7 @@
         <v>13348.37629167</v>
       </c>
     </row>
-    <row r="248" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:4">
       <c r="A248" s="1" t="s">
         <v>6</v>
       </c>
@@ -3927,10 +3894,10 @@
         <v>46084</v>
       </c>
       <c r="D248" s="3">
-        <v>16725.195458329999</v>
-      </c>
-    </row>
-    <row r="249" spans="1:4" x14ac:dyDescent="0.25">
+        <v>16725.19545833</v>
+      </c>
+    </row>
+    <row r="249" spans="1:4">
       <c r="A249" s="1" t="s">
         <v>7</v>
       </c>
@@ -3941,10 +3908,10 @@
         <v>46084</v>
       </c>
       <c r="D249" s="3">
-        <v>47744.246333329997</v>
-      </c>
-    </row>
-    <row r="250" spans="1:4" x14ac:dyDescent="0.25">
+        <v>47744.24633333</v>
+      </c>
+    </row>
+    <row r="250" spans="1:4">
       <c r="A250" s="1" t="s">
         <v>4</v>
       </c>
@@ -3955,10 +3922,10 @@
         <v>46085</v>
       </c>
       <c r="D250" s="3">
-        <v>8316.7539583300004</v>
-      </c>
-    </row>
-    <row r="251" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8316.75395833</v>
+      </c>
+    </row>
+    <row r="251" spans="1:4">
       <c r="A251" s="1" t="s">
         <v>5</v>
       </c>
@@ -3969,10 +3936,10 @@
         <v>46085</v>
       </c>
       <c r="D251" s="3">
-        <v>13061.692916669999</v>
-      </c>
-    </row>
-    <row r="252" spans="1:4" x14ac:dyDescent="0.25">
+        <v>13061.69291667</v>
+      </c>
+    </row>
+    <row r="252" spans="1:4">
       <c r="A252" s="1" t="s">
         <v>6</v>
       </c>
@@ -3983,10 +3950,10 @@
         <v>46085</v>
       </c>
       <c r="D252" s="3">
-        <v>17650.836583330001</v>
-      </c>
-    </row>
-    <row r="253" spans="1:4" x14ac:dyDescent="0.25">
+        <v>17650.83658333</v>
+      </c>
+    </row>
+    <row r="253" spans="1:4">
       <c r="A253" s="1" t="s">
         <v>7</v>
       </c>
@@ -3997,10 +3964,10 @@
         <v>46085</v>
       </c>
       <c r="D253" s="3">
-        <v>48898.391250000001</v>
-      </c>
-    </row>
-    <row r="254" spans="1:4" x14ac:dyDescent="0.25">
+        <v>48898.39125</v>
+      </c>
+    </row>
+    <row r="254" spans="1:4">
       <c r="A254" s="1" t="s">
         <v>4</v>
       </c>
@@ -4011,10 +3978,10 @@
         <v>46086</v>
       </c>
       <c r="D254" s="3">
-        <v>8253.1061666700007</v>
-      </c>
-    </row>
-    <row r="255" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8253.106166670001</v>
+      </c>
+    </row>
+    <row r="255" spans="1:4">
       <c r="A255" s="1" t="s">
         <v>5</v>
       </c>
@@ -4025,10 +3992,10 @@
         <v>46086</v>
       </c>
       <c r="D255" s="3">
-        <v>12974.838750000001</v>
-      </c>
-    </row>
-    <row r="256" spans="1:4" x14ac:dyDescent="0.25">
+        <v>12974.83875</v>
+      </c>
+    </row>
+    <row r="256" spans="1:4">
       <c r="A256" s="1" t="s">
         <v>6</v>
       </c>
@@ -4042,7 +4009,7 @@
         <v>17809.96133333</v>
       </c>
     </row>
-    <row r="257" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:4">
       <c r="A257" s="1" t="s">
         <v>7</v>
       </c>
@@ -4053,10 +4020,10 @@
         <v>46086</v>
       </c>
       <c r="D257" s="3">
-        <v>50072.212291670003</v>
-      </c>
-    </row>
-    <row r="258" spans="1:4" x14ac:dyDescent="0.25">
+        <v>50072.21229167</v>
+      </c>
+    </row>
+    <row r="258" spans="1:4">
       <c r="A258" s="1" t="s">
         <v>4</v>
       </c>
@@ -4067,10 +4034,10 @@
         <v>46087</v>
       </c>
       <c r="D258" s="3">
-        <v>8172.2332500000002</v>
-      </c>
-    </row>
-    <row r="259" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8172.23325</v>
+      </c>
+    </row>
+    <row r="259" spans="1:4">
       <c r="A259" s="1" t="s">
         <v>5</v>
       </c>
@@ -4081,10 +4048,10 @@
         <v>46087</v>
       </c>
       <c r="D259" s="3">
-        <v>12542.845916669999</v>
-      </c>
-    </row>
-    <row r="260" spans="1:4" x14ac:dyDescent="0.25">
+        <v>12542.84591667</v>
+      </c>
+    </row>
+    <row r="260" spans="1:4">
       <c r="A260" s="1" t="s">
         <v>6</v>
       </c>
@@ -4095,10 +4062,10 @@
         <v>46087</v>
       </c>
       <c r="D260" s="3">
-        <v>17596.996208330002</v>
-      </c>
-    </row>
-    <row r="261" spans="1:4" x14ac:dyDescent="0.25">
+        <v>17596.99620833</v>
+      </c>
+    </row>
+    <row r="261" spans="1:4">
       <c r="A261" s="1" t="s">
         <v>7</v>
       </c>
@@ -4109,10 +4076,10 @@
         <v>46087</v>
       </c>
       <c r="D261" s="3">
-        <v>50836.646166669998</v>
-      </c>
-    </row>
-    <row r="262" spans="1:4" x14ac:dyDescent="0.25">
+        <v>50836.64616667</v>
+      </c>
+    </row>
+    <row r="262" spans="1:4">
       <c r="A262" s="1" t="s">
         <v>4</v>
       </c>
@@ -4123,10 +4090,10 @@
         <v>46088</v>
       </c>
       <c r="D262" s="3">
-        <v>7917.0610416700001</v>
-      </c>
-    </row>
-    <row r="263" spans="1:4" x14ac:dyDescent="0.25">
+        <v>7917.06104167</v>
+      </c>
+    </row>
+    <row r="263" spans="1:4">
       <c r="A263" s="1" t="s">
         <v>5</v>
       </c>
@@ -4137,10 +4104,10 @@
         <v>46088</v>
       </c>
       <c r="D263" s="3">
-        <v>12553.697333329999</v>
-      </c>
-    </row>
-    <row r="264" spans="1:4" x14ac:dyDescent="0.25">
+        <v>12553.69733333</v>
+      </c>
+    </row>
+    <row r="264" spans="1:4">
       <c r="A264" s="1" t="s">
         <v>6</v>
       </c>
@@ -4154,7 +4121,7 @@
         <v>15098.24570833</v>
       </c>
     </row>
-    <row r="265" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:4">
       <c r="A265" s="1" t="s">
         <v>7</v>
       </c>
@@ -4165,10 +4132,10 @@
         <v>46088</v>
       </c>
       <c r="D265" s="3">
-        <v>46334.114916669998</v>
-      </c>
-    </row>
-    <row r="266" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46334.11491667</v>
+      </c>
+    </row>
+    <row r="266" spans="1:4">
       <c r="A266" s="1" t="s">
         <v>4</v>
       </c>
@@ -4182,7 +4149,7 @@
         <v>7704.34358333</v>
       </c>
     </row>
-    <row r="267" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:4">
       <c r="A267" s="1" t="s">
         <v>5</v>
       </c>
@@ -4196,7 +4163,7 @@
         <v>11916.03595833</v>
       </c>
     </row>
-    <row r="268" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:4">
       <c r="A268" s="1" t="s">
         <v>6</v>
       </c>
@@ -4207,10 +4174,10 @@
         <v>46089</v>
       </c>
       <c r="D268" s="3">
-        <v>12991.644749999999</v>
-      </c>
-    </row>
-    <row r="269" spans="1:4" x14ac:dyDescent="0.25">
+        <v>12991.64475</v>
+      </c>
+    </row>
+    <row r="269" spans="1:4">
       <c r="A269" s="1" t="s">
         <v>7</v>
       </c>
@@ -4221,10 +4188,10 @@
         <v>46089</v>
       </c>
       <c r="D269" s="3">
-        <v>42106.928583330002</v>
-      </c>
-    </row>
-    <row r="270" spans="1:4" x14ac:dyDescent="0.25">
+        <v>42106.92858333</v>
+      </c>
+    </row>
+    <row r="270" spans="1:4">
       <c r="A270" s="1" t="s">
         <v>4</v>
       </c>
@@ -4235,10 +4202,10 @@
         <v>46090</v>
       </c>
       <c r="D270" s="3">
-        <v>8539.6626666699995</v>
-      </c>
-    </row>
-    <row r="271" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8539.662666669999</v>
+      </c>
+    </row>
+    <row r="271" spans="1:4">
       <c r="A271" s="1" t="s">
         <v>5</v>
       </c>
@@ -4249,10 +4216,10 @@
         <v>46090</v>
       </c>
       <c r="D271" s="3">
-        <v>13456.037249999999</v>
-      </c>
-    </row>
-    <row r="272" spans="1:4" x14ac:dyDescent="0.25">
+        <v>13456.03725</v>
+      </c>
+    </row>
+    <row r="272" spans="1:4">
       <c r="A272" s="1" t="s">
         <v>6</v>
       </c>
@@ -4266,7 +4233,7 @@
         <v>15338.88933333</v>
       </c>
     </row>
-    <row r="273" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:4">
       <c r="A273" s="1" t="s">
         <v>7</v>
       </c>
@@ -4280,7 +4247,7 @@
         <v>48601.44645833</v>
       </c>
     </row>
-    <row r="274" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:4">
       <c r="A274" s="1" t="s">
         <v>4</v>
       </c>
@@ -4291,10 +4258,10 @@
         <v>46091</v>
       </c>
       <c r="D274" s="3">
-        <v>8539.4301666699994</v>
-      </c>
-    </row>
-    <row r="275" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8539.430166669999</v>
+      </c>
+    </row>
+    <row r="275" spans="1:4">
       <c r="A275" s="1" t="s">
         <v>5</v>
       </c>
@@ -4308,7 +4275,7 @@
         <v>13949.86845833</v>
       </c>
     </row>
-    <row r="276" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:4">
       <c r="A276" s="1" t="s">
         <v>6</v>
       </c>
@@ -4322,7 +4289,7 @@
         <v>15405.18475</v>
       </c>
     </row>
-    <row r="277" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:4">
       <c r="A277" s="1" t="s">
         <v>7</v>
       </c>
@@ -4333,10 +4300,10 @@
         <v>46091</v>
       </c>
       <c r="D277" s="3">
-        <v>47381.669541670002</v>
-      </c>
-    </row>
-    <row r="278" spans="1:4" x14ac:dyDescent="0.25">
+        <v>47381.66954167</v>
+      </c>
+    </row>
+    <row r="278" spans="1:4">
       <c r="A278" s="1" t="s">
         <v>4</v>
       </c>
@@ -4347,10 +4314,10 @@
         <v>46092</v>
       </c>
       <c r="D278" s="3">
-        <v>8479.1131666700003</v>
-      </c>
-    </row>
-    <row r="279" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8479.11316667</v>
+      </c>
+    </row>
+    <row r="279" spans="1:4">
       <c r="A279" s="1" t="s">
         <v>5</v>
       </c>
@@ -4364,7 +4331,7 @@
         <v>14204.63133333</v>
       </c>
     </row>
-    <row r="280" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:4">
       <c r="A280" s="1" t="s">
         <v>6</v>
       </c>
@@ -4378,7 +4345,7 @@
         <v>15817.90825</v>
       </c>
     </row>
-    <row r="281" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:4">
       <c r="A281" s="1" t="s">
         <v>7</v>
       </c>
@@ -4389,10 +4356,10 @@
         <v>46092</v>
       </c>
       <c r="D281" s="3">
-        <v>47199.858249999997</v>
-      </c>
-    </row>
-    <row r="282" spans="1:4" x14ac:dyDescent="0.25">
+        <v>47199.85825</v>
+      </c>
+    </row>
+    <row r="282" spans="1:4">
       <c r="A282" s="1" t="s">
         <v>4</v>
       </c>
@@ -4403,10 +4370,10 @@
         <v>46093</v>
       </c>
       <c r="D282" s="3">
-        <v>8498.6261250000007</v>
-      </c>
-    </row>
-    <row r="283" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8498.626125000001</v>
+      </c>
+    </row>
+    <row r="283" spans="1:4">
       <c r="A283" s="1" t="s">
         <v>5</v>
       </c>
@@ -4417,10 +4384,10 @@
         <v>46093</v>
       </c>
       <c r="D283" s="3">
-        <v>14217.459000000001</v>
-      </c>
-    </row>
-    <row r="284" spans="1:4" x14ac:dyDescent="0.25">
+        <v>14217.459</v>
+      </c>
+    </row>
+    <row r="284" spans="1:4">
       <c r="A284" s="1" t="s">
         <v>6</v>
       </c>
@@ -4434,7 +4401,7 @@
         <v>16107.25158333</v>
       </c>
     </row>
-    <row r="285" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:4">
       <c r="A285" s="1" t="s">
         <v>7</v>
       </c>
@@ -4445,10 +4412,10 @@
         <v>46093</v>
       </c>
       <c r="D285" s="3">
-        <v>46936.522791670002</v>
-      </c>
-    </row>
-    <row r="286" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46936.52279167</v>
+      </c>
+    </row>
+    <row r="286" spans="1:4">
       <c r="A286" s="1" t="s">
         <v>4</v>
       </c>
@@ -4459,10 +4426,10 @@
         <v>46094</v>
       </c>
       <c r="D286" s="3">
-        <v>8341.2012500000001</v>
-      </c>
-    </row>
-    <row r="287" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8341.20125</v>
+      </c>
+    </row>
+    <row r="287" spans="1:4">
       <c r="A287" s="1" t="s">
         <v>5</v>
       </c>
@@ -4476,7 +4443,7 @@
         <v>14245.23483333</v>
       </c>
     </row>
-    <row r="288" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:4">
       <c r="A288" s="1" t="s">
         <v>6</v>
       </c>
@@ -4490,7 +4457,7 @@
         <v>15909.35729167</v>
       </c>
     </row>
-    <row r="289" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:4">
       <c r="A289" s="1" t="s">
         <v>7</v>
       </c>
@@ -4501,10 +4468,10 @@
         <v>46094</v>
       </c>
       <c r="D289" s="3">
-        <v>46628.152125000001</v>
-      </c>
-    </row>
-    <row r="290" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46628.152125</v>
+      </c>
+    </row>
+    <row r="290" spans="1:4">
       <c r="A290" s="1" t="s">
         <v>4</v>
       </c>
@@ -4515,10 +4482,10 @@
         <v>46095</v>
       </c>
       <c r="D290" s="3">
-        <v>8166.5209583300002</v>
-      </c>
-    </row>
-    <row r="291" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8166.52095833</v>
+      </c>
+    </row>
+    <row r="291" spans="1:4">
       <c r="A291" s="1" t="s">
         <v>5</v>
       </c>
@@ -4532,7 +4499,7 @@
         <v>13976.56345833</v>
       </c>
     </row>
-    <row r="292" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:4">
       <c r="A292" s="1" t="s">
         <v>6</v>
       </c>
@@ -4546,7 +4513,7 @@
         <v>14400.57566667</v>
       </c>
     </row>
-    <row r="293" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:4">
       <c r="A293" s="1" t="s">
         <v>7</v>
       </c>
@@ -4557,10 +4524,10 @@
         <v>46095</v>
       </c>
       <c r="D293" s="3">
-        <v>42670.101916669999</v>
-      </c>
-    </row>
-    <row r="294" spans="1:4" x14ac:dyDescent="0.25">
+        <v>42670.10191667</v>
+      </c>
+    </row>
+    <row r="294" spans="1:4">
       <c r="A294" s="1" t="s">
         <v>4</v>
       </c>
@@ -4574,7 +4541,7 @@
         <v>7997.27691667</v>
       </c>
     </row>
-    <row r="295" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:4">
       <c r="A295" s="1" t="s">
         <v>5</v>
       </c>
@@ -4588,7 +4555,7 @@
         <v>13272.589125</v>
       </c>
     </row>
-    <row r="296" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:4">
       <c r="A296" s="1" t="s">
         <v>6</v>
       </c>
@@ -4599,10 +4566,10 @@
         <v>46096</v>
       </c>
       <c r="D296" s="3">
-        <v>13446.001166669999</v>
-      </c>
-    </row>
-    <row r="297" spans="1:4" x14ac:dyDescent="0.25">
+        <v>13446.00116667</v>
+      </c>
+    </row>
+    <row r="297" spans="1:4">
       <c r="A297" s="1" t="s">
         <v>7</v>
       </c>
@@ -4616,7 +4583,7 @@
         <v>40114.5265</v>
       </c>
     </row>
-    <row r="298" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:4">
       <c r="A298" s="1" t="s">
         <v>4</v>
       </c>
@@ -4627,10 +4594,10 @@
         <v>46097</v>
       </c>
       <c r="D298" s="3">
-        <v>8611.2016666700001</v>
-      </c>
-    </row>
-    <row r="299" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8611.20166667</v>
+      </c>
+    </row>
+    <row r="299" spans="1:4">
       <c r="A299" s="1" t="s">
         <v>5</v>
       </c>
@@ -4641,10 +4608,10 @@
         <v>46097</v>
       </c>
       <c r="D299" s="3">
-        <v>14271.086375000001</v>
-      </c>
-    </row>
-    <row r="300" spans="1:4" x14ac:dyDescent="0.25">
+        <v>14271.086375</v>
+      </c>
+    </row>
+    <row r="300" spans="1:4">
       <c r="A300" s="1" t="s">
         <v>6</v>
       </c>
@@ -4655,10 +4622,10 @@
         <v>46097</v>
       </c>
       <c r="D300" s="3">
-        <v>17837.167791669999</v>
-      </c>
-    </row>
-    <row r="301" spans="1:4" x14ac:dyDescent="0.25">
+        <v>17837.16779167</v>
+      </c>
+    </row>
+    <row r="301" spans="1:4">
       <c r="A301" s="1" t="s">
         <v>7</v>
       </c>
@@ -4669,10 +4636,10 @@
         <v>46097</v>
       </c>
       <c r="D301" s="3">
-        <v>48022.454166670002</v>
-      </c>
-    </row>
-    <row r="302" spans="1:4" x14ac:dyDescent="0.25">
+        <v>48022.45416667</v>
+      </c>
+    </row>
+    <row r="302" spans="1:4">
       <c r="A302" s="1" t="s">
         <v>4</v>
       </c>
@@ -4686,7 +4653,7 @@
         <v>8448.22308333</v>
       </c>
     </row>
-    <row r="303" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:4">
       <c r="A303" s="1" t="s">
         <v>5</v>
       </c>
@@ -4700,7 +4667,7 @@
         <v>13915.953625</v>
       </c>
     </row>
-    <row r="304" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:4">
       <c r="A304" s="1" t="s">
         <v>6</v>
       </c>
@@ -4711,10 +4678,10 @@
         <v>46098</v>
       </c>
       <c r="D304" s="3">
-        <v>17977.628166670002</v>
-      </c>
-    </row>
-    <row r="305" spans="1:4" x14ac:dyDescent="0.25">
+        <v>17977.62816667</v>
+      </c>
+    </row>
+    <row r="305" spans="1:4">
       <c r="A305" s="1" t="s">
         <v>7</v>
       </c>
@@ -4725,10 +4692,10 @@
         <v>46098</v>
       </c>
       <c r="D305" s="3">
-        <v>49710.679875000002</v>
-      </c>
-    </row>
-    <row r="306" spans="1:4" x14ac:dyDescent="0.25">
+        <v>49710.679875</v>
+      </c>
+    </row>
+    <row r="306" spans="1:4">
       <c r="A306" s="1" t="s">
         <v>4</v>
       </c>
@@ -4739,10 +4706,10 @@
         <v>46099</v>
       </c>
       <c r="D306" s="3">
-        <v>8376.4633749999994</v>
-      </c>
-    </row>
-    <row r="307" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8376.463374999999</v>
+      </c>
+    </row>
+    <row r="307" spans="1:4">
       <c r="A307" s="1" t="s">
         <v>5</v>
       </c>
@@ -4753,10 +4720,10 @@
         <v>46099</v>
       </c>
       <c r="D307" s="3">
-        <v>13966.371999999999</v>
-      </c>
-    </row>
-    <row r="308" spans="1:4" x14ac:dyDescent="0.25">
+        <v>13966.372</v>
+      </c>
+    </row>
+    <row r="308" spans="1:4">
       <c r="A308" s="1" t="s">
         <v>6</v>
       </c>
@@ -4767,10 +4734,10 @@
         <v>46099</v>
       </c>
       <c r="D308" s="3">
-        <v>17386.450583329999</v>
-      </c>
-    </row>
-    <row r="309" spans="1:4" x14ac:dyDescent="0.25">
+        <v>17386.45058333</v>
+      </c>
+    </row>
+    <row r="309" spans="1:4">
       <c r="A309" s="1" t="s">
         <v>7</v>
       </c>
@@ -4781,10 +4748,10 @@
         <v>46099</v>
       </c>
       <c r="D309" s="3">
-        <v>49875.424124999998</v>
-      </c>
-    </row>
-    <row r="310" spans="1:4" x14ac:dyDescent="0.25">
+        <v>49875.424125</v>
+      </c>
+    </row>
+    <row r="310" spans="1:4">
       <c r="A310" s="1" t="s">
         <v>4</v>
       </c>
@@ -4795,10 +4762,10 @@
         <v>46100</v>
       </c>
       <c r="D310" s="3">
-        <v>8130.4827916699996</v>
-      </c>
-    </row>
-    <row r="311" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8130.48279167</v>
+      </c>
+    </row>
+    <row r="311" spans="1:4">
       <c r="A311" s="1" t="s">
         <v>5</v>
       </c>
@@ -4812,7 +4779,7 @@
         <v>13936.72866667</v>
       </c>
     </row>
-    <row r="312" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:4">
       <c r="A312" s="1" t="s">
         <v>6</v>
       </c>
@@ -4823,10 +4790,10 @@
         <v>46100</v>
       </c>
       <c r="D312" s="3">
-        <v>17437.765416670001</v>
-      </c>
-    </row>
-    <row r="313" spans="1:4" x14ac:dyDescent="0.25">
+        <v>17437.76541667</v>
+      </c>
+    </row>
+    <row r="313" spans="1:4">
       <c r="A313" s="1" t="s">
         <v>7</v>
       </c>
@@ -4837,10 +4804,10 @@
         <v>46100</v>
       </c>
       <c r="D313" s="3">
-        <v>49310.789499999999</v>
-      </c>
-    </row>
-    <row r="314" spans="1:4" x14ac:dyDescent="0.25">
+        <v>49310.7895</v>
+      </c>
+    </row>
+    <row r="314" spans="1:4">
       <c r="A314" s="1" t="s">
         <v>4</v>
       </c>
@@ -4851,10 +4818,10 @@
         <v>46101</v>
       </c>
       <c r="D314" s="3">
-        <v>8185.6992916700001</v>
-      </c>
-    </row>
-    <row r="315" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8185.69929167</v>
+      </c>
+    </row>
+    <row r="315" spans="1:4">
       <c r="A315" s="1" t="s">
         <v>5</v>
       </c>
@@ -4865,10 +4832,10 @@
         <v>46101</v>
       </c>
       <c r="D315" s="3">
-        <v>14302.282458330001</v>
-      </c>
-    </row>
-    <row r="316" spans="1:4" x14ac:dyDescent="0.25">
+        <v>14302.28245833</v>
+      </c>
+    </row>
+    <row r="316" spans="1:4">
       <c r="A316" s="1" t="s">
         <v>6</v>
       </c>
@@ -4882,7 +4849,7 @@
         <v>17392.88258333</v>
       </c>
     </row>
-    <row r="317" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:4">
       <c r="A317" s="1" t="s">
         <v>7</v>
       </c>
@@ -4893,10 +4860,10 @@
         <v>46101</v>
       </c>
       <c r="D317" s="3">
-        <v>47891.504000000001</v>
-      </c>
-    </row>
-    <row r="318" spans="1:4" x14ac:dyDescent="0.25">
+        <v>47891.504</v>
+      </c>
+    </row>
+    <row r="318" spans="1:4">
       <c r="A318" s="1" t="s">
         <v>4</v>
       </c>
@@ -4907,10 +4874,10 @@
         <v>46102</v>
       </c>
       <c r="D318" s="3">
-        <v>7955.4722916700002</v>
-      </c>
-    </row>
-    <row r="319" spans="1:4" x14ac:dyDescent="0.25">
+        <v>7955.47229167</v>
+      </c>
+    </row>
+    <row r="319" spans="1:4">
       <c r="A319" s="1" t="s">
         <v>5</v>
       </c>
@@ -4924,7 +4891,7 @@
         <v>13715.86591667</v>
       </c>
     </row>
-    <row r="320" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:4">
       <c r="A320" s="1" t="s">
         <v>6</v>
       </c>
@@ -4935,10 +4902,10 @@
         <v>46102</v>
       </c>
       <c r="D320" s="3">
-        <v>15520.887583330001</v>
-      </c>
-    </row>
-    <row r="321" spans="1:4" x14ac:dyDescent="0.25">
+        <v>15520.88758333</v>
+      </c>
+    </row>
+    <row r="321" spans="1:4">
       <c r="A321" s="1" t="s">
         <v>7</v>
       </c>
@@ -4949,10 +4916,10 @@
         <v>46102</v>
       </c>
       <c r="D321" s="3">
-        <v>43782.757958330003</v>
-      </c>
-    </row>
-    <row r="322" spans="1:4" x14ac:dyDescent="0.25">
+        <v>43782.75795833</v>
+      </c>
+    </row>
+    <row r="322" spans="1:4">
       <c r="A322" s="1" t="s">
         <v>4</v>
       </c>
@@ -4963,10 +4930,10 @@
         <v>46103</v>
       </c>
       <c r="D322" s="3">
-        <v>8037.3424166699997</v>
-      </c>
-    </row>
-    <row r="323" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8037.34241667</v>
+      </c>
+    </row>
+    <row r="323" spans="1:4">
       <c r="A323" s="1" t="s">
         <v>5</v>
       </c>
@@ -4977,10 +4944,10 @@
         <v>46103</v>
       </c>
       <c r="D323" s="3">
-        <v>13080.504499999999</v>
-      </c>
-    </row>
-    <row r="324" spans="1:4" x14ac:dyDescent="0.25">
+        <v>13080.5045</v>
+      </c>
+    </row>
+    <row r="324" spans="1:4">
       <c r="A324" s="1" t="s">
         <v>6</v>
       </c>
@@ -4991,10 +4958,10 @@
         <v>46103</v>
       </c>
       <c r="D324" s="3">
-        <v>13721.566124999999</v>
-      </c>
-    </row>
-    <row r="325" spans="1:4" x14ac:dyDescent="0.25">
+        <v>13721.566125</v>
+      </c>
+    </row>
+    <row r="325" spans="1:4">
       <c r="A325" s="1" t="s">
         <v>7</v>
       </c>
@@ -5005,10 +4972,10 @@
         <v>46103</v>
       </c>
       <c r="D325" s="3">
-        <v>40857.993583329997</v>
-      </c>
-    </row>
-    <row r="326" spans="1:4" x14ac:dyDescent="0.25">
+        <v>40857.99358333</v>
+      </c>
+    </row>
+    <row r="326" spans="1:4">
       <c r="A326" s="1" t="s">
         <v>4</v>
       </c>
@@ -5019,10 +4986,10 @@
         <v>46104</v>
       </c>
       <c r="D326" s="3">
-        <v>8685.0597916700008</v>
-      </c>
-    </row>
-    <row r="327" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8685.059791670001</v>
+      </c>
+    </row>
+    <row r="327" spans="1:4">
       <c r="A327" s="1" t="s">
         <v>5</v>
       </c>
@@ -5033,10 +5000,10 @@
         <v>46104</v>
       </c>
       <c r="D327" s="3">
-        <v>14460.670166669999</v>
-      </c>
-    </row>
-    <row r="328" spans="1:4" x14ac:dyDescent="0.25">
+        <v>14460.67016667</v>
+      </c>
+    </row>
+    <row r="328" spans="1:4">
       <c r="A328" s="1" t="s">
         <v>6</v>
       </c>
@@ -5047,10 +5014,10 @@
         <v>46104</v>
       </c>
       <c r="D328" s="3">
-        <v>16591.168166669999</v>
-      </c>
-    </row>
-    <row r="329" spans="1:4" x14ac:dyDescent="0.25">
+        <v>16591.16816667</v>
+      </c>
+    </row>
+    <row r="329" spans="1:4">
       <c r="A329" s="1" t="s">
         <v>7</v>
       </c>
@@ -5061,10 +5028,10 @@
         <v>46104</v>
       </c>
       <c r="D329" s="3">
-        <v>48031.707291669998</v>
-      </c>
-    </row>
-    <row r="330" spans="1:4" x14ac:dyDescent="0.25">
+        <v>48031.70729167</v>
+      </c>
+    </row>
+    <row r="330" spans="1:4">
       <c r="A330" s="1" t="s">
         <v>4</v>
       </c>
@@ -5075,10 +5042,10 @@
         <v>46105</v>
       </c>
       <c r="D330" s="3">
-        <v>8624.7330833300002</v>
-      </c>
-    </row>
-    <row r="331" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8624.73308333</v>
+      </c>
+    </row>
+    <row r="331" spans="1:4">
       <c r="A331" s="1" t="s">
         <v>5</v>
       </c>
@@ -5089,10 +5056,10 @@
         <v>46105</v>
       </c>
       <c r="D331" s="3">
-        <v>14371.632333330001</v>
-      </c>
-    </row>
-    <row r="332" spans="1:4" x14ac:dyDescent="0.25">
+        <v>14371.63233333</v>
+      </c>
+    </row>
+    <row r="332" spans="1:4">
       <c r="A332" s="1" t="s">
         <v>6</v>
       </c>
@@ -5106,7 +5073,7 @@
         <v>16669.51991667</v>
       </c>
     </row>
-    <row r="333" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:4">
       <c r="A333" s="1" t="s">
         <v>7</v>
       </c>
@@ -5117,10 +5084,10 @@
         <v>46105</v>
       </c>
       <c r="D333" s="3">
-        <v>48772.133083330002</v>
-      </c>
-    </row>
-    <row r="334" spans="1:4" x14ac:dyDescent="0.25">
+        <v>48772.13308333</v>
+      </c>
+    </row>
+    <row r="334" spans="1:4">
       <c r="A334" s="1" t="s">
         <v>4</v>
       </c>
@@ -5131,10 +5098,10 @@
         <v>46106</v>
       </c>
       <c r="D334" s="3">
-        <v>8446.9134166700005</v>
-      </c>
-    </row>
-    <row r="335" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8446.913416670001</v>
+      </c>
+    </row>
+    <row r="335" spans="1:4">
       <c r="A335" s="1" t="s">
         <v>5</v>
       </c>
@@ -5145,10 +5112,10 @@
         <v>46106</v>
       </c>
       <c r="D335" s="3">
-        <v>13985.085916669999</v>
-      </c>
-    </row>
-    <row r="336" spans="1:4" x14ac:dyDescent="0.25">
+        <v>13985.08591667</v>
+      </c>
+    </row>
+    <row r="336" spans="1:4">
       <c r="A336" s="1" t="s">
         <v>6</v>
       </c>
@@ -5159,10 +5126,10 @@
         <v>46106</v>
       </c>
       <c r="D336" s="3">
-        <v>16671.696791670001</v>
-      </c>
-    </row>
-    <row r="337" spans="1:4" x14ac:dyDescent="0.25">
+        <v>16671.69679167</v>
+      </c>
+    </row>
+    <row r="337" spans="1:4">
       <c r="A337" s="1" t="s">
         <v>7</v>
       </c>
@@ -5176,7 +5143,7 @@
         <v>48993.86266667</v>
       </c>
     </row>
-    <row r="338" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:4">
       <c r="A338" s="1" t="s">
         <v>4</v>
       </c>
@@ -5187,10 +5154,10 @@
         <v>46107</v>
       </c>
       <c r="D338" s="3">
-        <v>8548.1126666700002</v>
-      </c>
-    </row>
-    <row r="339" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8548.11266667</v>
+      </c>
+    </row>
+    <row r="339" spans="1:4">
       <c r="A339" s="1" t="s">
         <v>5</v>
       </c>
@@ -5201,10 +5168,10 @@
         <v>46107</v>
       </c>
       <c r="D339" s="3">
-        <v>14252.479291670001</v>
-      </c>
-    </row>
-    <row r="340" spans="1:4" x14ac:dyDescent="0.25">
+        <v>14252.47929167</v>
+      </c>
+    </row>
+    <row r="340" spans="1:4">
       <c r="A340" s="1" t="s">
         <v>6</v>
       </c>
@@ -5215,10 +5182,10 @@
         <v>46107</v>
       </c>
       <c r="D340" s="3">
-        <v>17188.372416670001</v>
-      </c>
-    </row>
-    <row r="341" spans="1:4" x14ac:dyDescent="0.25">
+        <v>17188.37241667</v>
+      </c>
+    </row>
+    <row r="341" spans="1:4">
       <c r="A341" s="1" t="s">
         <v>7</v>
       </c>
@@ -5229,10 +5196,10 @@
         <v>46107</v>
       </c>
       <c r="D341" s="3">
-        <v>48855.129124999999</v>
-      </c>
-    </row>
-    <row r="342" spans="1:4" x14ac:dyDescent="0.25">
+        <v>48855.129125</v>
+      </c>
+    </row>
+    <row r="342" spans="1:4">
       <c r="A342" s="1" t="s">
         <v>4</v>
       </c>
@@ -5243,10 +5210,10 @@
         <v>46108</v>
       </c>
       <c r="D342" s="3">
-        <v>8670.0948750000007</v>
-      </c>
-    </row>
-    <row r="343" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8670.094875000001</v>
+      </c>
+    </row>
+    <row r="343" spans="1:4">
       <c r="A343" s="1" t="s">
         <v>5</v>
       </c>
@@ -5260,7 +5227,7 @@
         <v>14089.11866667</v>
       </c>
     </row>
-    <row r="344" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:4">
       <c r="A344" s="1" t="s">
         <v>6</v>
       </c>
@@ -5271,10 +5238,10 @@
         <v>46108</v>
       </c>
       <c r="D344" s="3">
-        <v>17975.524958329999</v>
-      </c>
-    </row>
-    <row r="345" spans="1:4" x14ac:dyDescent="0.25">
+        <v>17975.52495833</v>
+      </c>
+    </row>
+    <row r="345" spans="1:4">
       <c r="A345" s="1" t="s">
         <v>7</v>
       </c>
@@ -5285,10 +5252,10 @@
         <v>46108</v>
       </c>
       <c r="D345" s="3">
-        <v>48511.238499999999</v>
-      </c>
-    </row>
-    <row r="346" spans="1:4" x14ac:dyDescent="0.25">
+        <v>48511.2385</v>
+      </c>
+    </row>
+    <row r="346" spans="1:4">
       <c r="A346" s="1" t="s">
         <v>4</v>
       </c>
@@ -5299,10 +5266,10 @@
         <v>46109</v>
       </c>
       <c r="D346" s="3">
-        <v>8288.8773333299996</v>
-      </c>
-    </row>
-    <row r="347" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8288.87733333</v>
+      </c>
+    </row>
+    <row r="347" spans="1:4">
       <c r="A347" s="1" t="s">
         <v>5</v>
       </c>
@@ -5313,10 +5280,10 @@
         <v>46109</v>
       </c>
       <c r="D347" s="3">
-        <v>13202.127624999999</v>
-      </c>
-    </row>
-    <row r="348" spans="1:4" x14ac:dyDescent="0.25">
+        <v>13202.127625</v>
+      </c>
+    </row>
+    <row r="348" spans="1:4">
       <c r="A348" s="1" t="s">
         <v>6</v>
       </c>
@@ -5327,10 +5294,10 @@
         <v>46109</v>
       </c>
       <c r="D348" s="3">
-        <v>16133.481374999999</v>
-      </c>
-    </row>
-    <row r="349" spans="1:4" x14ac:dyDescent="0.25">
+        <v>16133.481375</v>
+      </c>
+    </row>
+    <row r="349" spans="1:4">
       <c r="A349" s="1" t="s">
         <v>7</v>
       </c>
@@ -5341,10 +5308,10 @@
         <v>46109</v>
       </c>
       <c r="D349" s="3">
-        <v>44519.355333330001</v>
-      </c>
-    </row>
-    <row r="350" spans="1:4" x14ac:dyDescent="0.25">
+        <v>44519.35533333</v>
+      </c>
+    </row>
+    <row r="350" spans="1:4">
       <c r="A350" s="1" t="s">
         <v>4</v>
       </c>
@@ -5355,10 +5322,10 @@
         <v>46110</v>
       </c>
       <c r="D350" s="3">
-        <v>7935.3704166699999</v>
-      </c>
-    </row>
-    <row r="351" spans="1:4" x14ac:dyDescent="0.25">
+        <v>7935.37041667</v>
+      </c>
+    </row>
+    <row r="351" spans="1:4">
       <c r="A351" s="1" t="s">
         <v>5</v>
       </c>
@@ -5369,10 +5336,10 @@
         <v>46110</v>
       </c>
       <c r="D351" s="3">
-        <v>12432.198541670001</v>
-      </c>
-    </row>
-    <row r="352" spans="1:4" x14ac:dyDescent="0.25">
+        <v>12432.19854167</v>
+      </c>
+    </row>
+    <row r="352" spans="1:4">
       <c r="A352" s="1" t="s">
         <v>6</v>
       </c>
@@ -5386,7 +5353,7 @@
         <v>14544.94608333</v>
       </c>
     </row>
-    <row r="353" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:4">
       <c r="A353" s="1" t="s">
         <v>7</v>
       </c>
@@ -5397,10 +5364,10 @@
         <v>46110</v>
       </c>
       <c r="D353" s="3">
-        <v>41072.324791669998</v>
-      </c>
-    </row>
-    <row r="354" spans="1:4" x14ac:dyDescent="0.25">
+        <v>41072.32479167</v>
+      </c>
+    </row>
+    <row r="354" spans="1:4">
       <c r="A354" s="1" t="s">
         <v>4</v>
       </c>
@@ -5411,10 +5378,10 @@
         <v>46111</v>
       </c>
       <c r="D354" s="3">
-        <v>8404.9472083300006</v>
-      </c>
-    </row>
-    <row r="355" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8404.947208330001</v>
+      </c>
+    </row>
+    <row r="355" spans="1:4">
       <c r="A355" s="1" t="s">
         <v>5</v>
       </c>
@@ -5428,7 +5395,7 @@
         <v>13951.45520833</v>
       </c>
     </row>
-    <row r="356" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:4">
       <c r="A356" s="1" t="s">
         <v>6</v>
       </c>
@@ -5439,10 +5406,10 @@
         <v>46111</v>
       </c>
       <c r="D356" s="3">
-        <v>17906.939916669999</v>
-      </c>
-    </row>
-    <row r="357" spans="1:4" x14ac:dyDescent="0.25">
+        <v>17906.93991667</v>
+      </c>
+    </row>
+    <row r="357" spans="1:4">
       <c r="A357" s="1" t="s">
         <v>7</v>
       </c>
@@ -5453,10 +5420,10 @@
         <v>46111</v>
       </c>
       <c r="D357" s="3">
-        <v>47745.181125000003</v>
-      </c>
-    </row>
-    <row r="358" spans="1:4" x14ac:dyDescent="0.25">
+        <v>47745.181125</v>
+      </c>
+    </row>
+    <row r="358" spans="1:4">
       <c r="A358" s="1" t="s">
         <v>4</v>
       </c>
@@ -5467,10 +5434,10 @@
         <v>46112</v>
       </c>
       <c r="D358" s="3">
-        <v>8394.8669166700001</v>
-      </c>
-    </row>
-    <row r="359" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8394.86691667</v>
+      </c>
+    </row>
+    <row r="359" spans="1:4">
       <c r="A359" s="1" t="s">
         <v>5</v>
       </c>
@@ -5481,10 +5448,10 @@
         <v>46112</v>
       </c>
       <c r="D359" s="3">
-        <v>14091.618125000001</v>
-      </c>
-    </row>
-    <row r="360" spans="1:4" x14ac:dyDescent="0.25">
+        <v>14091.618125</v>
+      </c>
+    </row>
+    <row r="360" spans="1:4">
       <c r="A360" s="1" t="s">
         <v>6</v>
       </c>
@@ -5498,7 +5465,7 @@
         <v>17146.760875</v>
       </c>
     </row>
-    <row r="361" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:4">
       <c r="A361" s="1" t="s">
         <v>7</v>
       </c>
@@ -5509,10 +5476,10 @@
         <v>46112</v>
       </c>
       <c r="D361" s="3">
-        <v>48134.925708330004</v>
-      </c>
-    </row>
-    <row r="362" spans="1:4" x14ac:dyDescent="0.25">
+        <v>48134.92570833</v>
+      </c>
+    </row>
+    <row r="362" spans="1:4">
       <c r="A362" s="1" t="s">
         <v>4</v>
       </c>
@@ -5523,10 +5490,10 @@
         <v>46113</v>
       </c>
       <c r="D362" s="3">
-        <v>8039.5242500000004</v>
-      </c>
-    </row>
-    <row r="363" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8039.52425</v>
+      </c>
+    </row>
+    <row r="363" spans="1:4">
       <c r="A363" s="1" t="s">
         <v>5</v>
       </c>
@@ -5540,7 +5507,7 @@
         <v>13815.490125</v>
       </c>
     </row>
-    <row r="364" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:4">
       <c r="A364" s="1" t="s">
         <v>6</v>
       </c>
@@ -5551,10 +5518,10 @@
         <v>46113</v>
       </c>
       <c r="D364" s="3">
-        <v>16674.427208329998</v>
-      </c>
-    </row>
-    <row r="365" spans="1:4" x14ac:dyDescent="0.25">
+        <v>16674.42720833</v>
+      </c>
+    </row>
+    <row r="365" spans="1:4">
       <c r="A365" s="1" t="s">
         <v>7</v>
       </c>
@@ -5565,10 +5532,10 @@
         <v>46113</v>
       </c>
       <c r="D365" s="3">
-        <v>47213.429624999997</v>
-      </c>
-    </row>
-    <row r="366" spans="1:4" x14ac:dyDescent="0.25">
+        <v>47213.429625</v>
+      </c>
+    </row>
+    <row r="366" spans="1:4">
       <c r="A366" s="1" t="s">
         <v>4</v>
       </c>
@@ -5579,10 +5546,10 @@
         <v>46114</v>
       </c>
       <c r="D366" s="3">
-        <v>7987.1240416700002</v>
-      </c>
-    </row>
-    <row r="367" spans="1:4" x14ac:dyDescent="0.25">
+        <v>7987.12404167</v>
+      </c>
+    </row>
+    <row r="367" spans="1:4">
       <c r="A367" s="1" t="s">
         <v>5</v>
       </c>
@@ -5596,7 +5563,7 @@
         <v>13343.61645833</v>
       </c>
     </row>
-    <row r="368" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:4">
       <c r="A368" s="1" t="s">
         <v>6</v>
       </c>
@@ -5607,10 +5574,10 @@
         <v>46114</v>
       </c>
       <c r="D368" s="3">
-        <v>16802.568291669999</v>
-      </c>
-    </row>
-    <row r="369" spans="1:4" x14ac:dyDescent="0.25">
+        <v>16802.56829167</v>
+      </c>
+    </row>
+    <row r="369" spans="1:4">
       <c r="A369" s="1" t="s">
         <v>7</v>
       </c>
@@ -5621,10 +5588,10 @@
         <v>46114</v>
       </c>
       <c r="D369" s="3">
-        <v>47041.257541669998</v>
-      </c>
-    </row>
-    <row r="370" spans="1:4" x14ac:dyDescent="0.25">
+        <v>47041.25754167</v>
+      </c>
+    </row>
+    <row r="370" spans="1:4">
       <c r="A370" s="1" t="s">
         <v>4</v>
       </c>
@@ -5635,10 +5602,10 @@
         <v>46115</v>
       </c>
       <c r="D370" s="3">
-        <v>7605.6803333300004</v>
-      </c>
-    </row>
-    <row r="371" spans="1:4" x14ac:dyDescent="0.25">
+        <v>7605.68033333</v>
+      </c>
+    </row>
+    <row r="371" spans="1:4">
       <c r="A371" s="1" t="s">
         <v>5</v>
       </c>
@@ -5652,7 +5619,7 @@
         <v>11674.82091667</v>
       </c>
     </row>
-    <row r="372" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:4">
       <c r="A372" s="1" t="s">
         <v>6</v>
       </c>
@@ -5663,10 +5630,10 @@
         <v>46115</v>
       </c>
       <c r="D372" s="3">
-        <v>13350.050375000001</v>
-      </c>
-    </row>
-    <row r="373" spans="1:4" x14ac:dyDescent="0.25">
+        <v>13350.050375</v>
+      </c>
+    </row>
+    <row r="373" spans="1:4">
       <c r="A373" s="1" t="s">
         <v>7</v>
       </c>
@@ -5677,10 +5644,10 @@
         <v>46115</v>
       </c>
       <c r="D373" s="3">
-        <v>41142.406750000002</v>
-      </c>
-    </row>
-    <row r="374" spans="1:4" x14ac:dyDescent="0.25">
+        <v>41142.40675</v>
+      </c>
+    </row>
+    <row r="374" spans="1:4">
       <c r="A374" s="1" t="s">
         <v>4</v>
       </c>
@@ -5691,10 +5658,10 @@
         <v>46116</v>
       </c>
       <c r="D374" s="3">
-        <v>7887.0739583300001</v>
-      </c>
-    </row>
-    <row r="375" spans="1:4" x14ac:dyDescent="0.25">
+        <v>7887.07395833</v>
+      </c>
+    </row>
+    <row r="375" spans="1:4">
       <c r="A375" s="1" t="s">
         <v>5</v>
       </c>
@@ -5708,7 +5675,7 @@
         <v>12200.56154167</v>
       </c>
     </row>
-    <row r="376" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:4">
       <c r="A376" s="1" t="s">
         <v>6</v>
       </c>
@@ -5722,7 +5689,7 @@
         <v>13670.00566667</v>
       </c>
     </row>
-    <row r="377" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:4">
       <c r="A377" s="1" t="s">
         <v>7</v>
       </c>
@@ -5733,10 +5700,10 @@
         <v>46116</v>
       </c>
       <c r="D377" s="3">
-        <v>41955.166499999999</v>
-      </c>
-    </row>
-    <row r="378" spans="1:4" x14ac:dyDescent="0.25">
+        <v>41955.1665</v>
+      </c>
+    </row>
+    <row r="378" spans="1:4">
       <c r="A378" s="1" t="s">
         <v>4</v>
       </c>
@@ -5747,10 +5714,10 @@
         <v>46117</v>
       </c>
       <c r="D378" s="3">
-        <v>7613.2225416700003</v>
-      </c>
-    </row>
-    <row r="379" spans="1:4" x14ac:dyDescent="0.25">
+        <v>7613.22254167</v>
+      </c>
+    </row>
+    <row r="379" spans="1:4">
       <c r="A379" s="1" t="s">
         <v>5</v>
       </c>
@@ -5764,7 +5731,7 @@
         <v>12033.44404167</v>
       </c>
     </row>
-    <row r="380" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:4">
       <c r="A380" s="1" t="s">
         <v>6</v>
       </c>
@@ -5778,7 +5745,7 @@
         <v>12250.20370833</v>
       </c>
     </row>
-    <row r="381" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:4">
       <c r="A381" s="1" t="s">
         <v>7</v>
       </c>
@@ -5789,10 +5756,10 @@
         <v>46117</v>
       </c>
       <c r="D381" s="3">
-        <v>40182.650833330001</v>
-      </c>
-    </row>
-    <row r="382" spans="1:4" x14ac:dyDescent="0.25">
+        <v>40182.65083333</v>
+      </c>
+    </row>
+    <row r="382" spans="1:4">
       <c r="A382" s="1" t="s">
         <v>4</v>
       </c>
@@ -5803,10 +5770,10 @@
         <v>46118</v>
       </c>
       <c r="D382" s="3">
-        <v>8272.3658333300009</v>
-      </c>
-    </row>
-    <row r="383" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8272.365833330001</v>
+      </c>
+    </row>
+    <row r="383" spans="1:4">
       <c r="A383" s="1" t="s">
         <v>5</v>
       </c>
@@ -5820,7 +5787,7 @@
         <v>13435.33525</v>
       </c>
     </row>
-    <row r="384" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:4">
       <c r="A384" s="1" t="s">
         <v>6</v>
       </c>
@@ -5834,7 +5801,7 @@
         <v>15613.624875</v>
       </c>
     </row>
-    <row r="385" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:4">
       <c r="A385" s="1" t="s">
         <v>7</v>
       </c>
@@ -5845,10 +5812,10 @@
         <v>46118</v>
       </c>
       <c r="D385" s="3">
-        <v>47889.587583330002</v>
-      </c>
-    </row>
-    <row r="386" spans="1:4" x14ac:dyDescent="0.25">
+        <v>47889.58758333</v>
+      </c>
+    </row>
+    <row r="386" spans="1:4">
       <c r="A386" s="1" t="s">
         <v>4</v>
       </c>
@@ -5859,10 +5826,10 @@
         <v>46119</v>
       </c>
       <c r="D386" s="3">
-        <v>8203.1516666700008</v>
-      </c>
-    </row>
-    <row r="387" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8203.151666670001</v>
+      </c>
+    </row>
+    <row r="387" spans="1:4">
       <c r="A387" s="1" t="s">
         <v>5</v>
       </c>
@@ -5876,7 +5843,7 @@
         <v>13682.17945833</v>
       </c>
     </row>
-    <row r="388" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:4">
       <c r="A388" s="1" t="s">
         <v>6</v>
       </c>
@@ -5890,7 +5857,7 @@
         <v>16291.59929167</v>
       </c>
     </row>
-    <row r="389" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:4">
       <c r="A389" s="1" t="s">
         <v>7</v>
       </c>
@@ -5901,10 +5868,10 @@
         <v>46119</v>
       </c>
       <c r="D389" s="3">
-        <v>49442.742250000003</v>
-      </c>
-    </row>
-    <row r="390" spans="1:4" x14ac:dyDescent="0.25">
+        <v>49442.74225</v>
+      </c>
+    </row>
+    <row r="390" spans="1:4">
       <c r="A390" s="1" t="s">
         <v>4</v>
       </c>
@@ -5915,10 +5882,10 @@
         <v>46120</v>
       </c>
       <c r="D390" s="3">
-        <v>8414.2911666700002</v>
-      </c>
-    </row>
-    <row r="391" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8414.29116667</v>
+      </c>
+    </row>
+    <row r="391" spans="1:4">
       <c r="A391" s="1" t="s">
         <v>5</v>
       </c>
@@ -5929,10 +5896,10 @@
         <v>46120</v>
       </c>
       <c r="D391" s="3">
-        <v>13839.408874999999</v>
-      </c>
-    </row>
-    <row r="392" spans="1:4" x14ac:dyDescent="0.25">
+        <v>13839.408875</v>
+      </c>
+    </row>
+    <row r="392" spans="1:4">
       <c r="A392" s="1" t="s">
         <v>6</v>
       </c>
@@ -5943,10 +5910,10 @@
         <v>46120</v>
       </c>
       <c r="D392" s="3">
-        <v>15391.950916670001</v>
-      </c>
-    </row>
-    <row r="393" spans="1:4" x14ac:dyDescent="0.25">
+        <v>15391.95091667</v>
+      </c>
+    </row>
+    <row r="393" spans="1:4">
       <c r="A393" s="1" t="s">
         <v>7</v>
       </c>
@@ -5957,10 +5924,10 @@
         <v>46120</v>
       </c>
       <c r="D393" s="3">
-        <v>49517.842250000002</v>
-      </c>
-    </row>
-    <row r="394" spans="1:4" x14ac:dyDescent="0.25">
+        <v>49517.84225</v>
+      </c>
+    </row>
+    <row r="394" spans="1:4">
       <c r="A394" s="1" t="s">
         <v>4</v>
       </c>
@@ -5971,10 +5938,10 @@
         <v>46121</v>
       </c>
       <c r="D394" s="3">
-        <v>8270.6055416700001</v>
-      </c>
-    </row>
-    <row r="395" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8270.60554167</v>
+      </c>
+    </row>
+    <row r="395" spans="1:4">
       <c r="A395" s="1" t="s">
         <v>5</v>
       </c>
@@ -5988,7 +5955,7 @@
         <v>14039.02608333</v>
       </c>
     </row>
-    <row r="396" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:4">
       <c r="A396" s="1" t="s">
         <v>6</v>
       </c>
@@ -5999,10 +5966,10 @@
         <v>46121</v>
       </c>
       <c r="D396" s="3">
-        <v>14794.853291670001</v>
-      </c>
-    </row>
-    <row r="397" spans="1:4" x14ac:dyDescent="0.25">
+        <v>14794.85329167</v>
+      </c>
+    </row>
+    <row r="397" spans="1:4">
       <c r="A397" s="1" t="s">
         <v>7</v>
       </c>
@@ -6013,10 +5980,10 @@
         <v>46121</v>
       </c>
       <c r="D397" s="3">
-        <v>49202.735000000001</v>
-      </c>
-    </row>
-    <row r="398" spans="1:4" x14ac:dyDescent="0.25">
+        <v>49202.735</v>
+      </c>
+    </row>
+    <row r="398" spans="1:4">
       <c r="A398" s="1" t="s">
         <v>4</v>
       </c>
@@ -6027,10 +5994,10 @@
         <v>46122</v>
       </c>
       <c r="D398" s="3">
-        <v>8452.5638749999998</v>
-      </c>
-    </row>
-    <row r="399" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8452.563875</v>
+      </c>
+    </row>
+    <row r="399" spans="1:4">
       <c r="A399" s="1" t="s">
         <v>5</v>
       </c>
@@ -6041,10 +6008,10 @@
         <v>46122</v>
       </c>
       <c r="D399" s="3">
-        <v>14052.709041669999</v>
-      </c>
-    </row>
-    <row r="400" spans="1:4" x14ac:dyDescent="0.25">
+        <v>14052.70904167</v>
+      </c>
+    </row>
+    <row r="400" spans="1:4">
       <c r="A400" s="1" t="s">
         <v>6</v>
       </c>
@@ -6058,7 +6025,7 @@
         <v>14700.73645833</v>
       </c>
     </row>
-    <row r="401" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:4">
       <c r="A401" s="1" t="s">
         <v>7</v>
       </c>
@@ -6069,10 +6036,10 @@
         <v>46122</v>
       </c>
       <c r="D401" s="3">
-        <v>47045.354208329998</v>
-      </c>
-    </row>
-    <row r="402" spans="1:4" x14ac:dyDescent="0.25">
+        <v>47045.35420833</v>
+      </c>
+    </row>
+    <row r="402" spans="1:4">
       <c r="A402" s="1" t="s">
         <v>4</v>
       </c>
@@ -6083,10 +6050,10 @@
         <v>46123</v>
       </c>
       <c r="D402" s="3">
-        <v>8126.2259166699996</v>
-      </c>
-    </row>
-    <row r="403" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8126.22591667</v>
+      </c>
+    </row>
+    <row r="403" spans="1:4">
       <c r="A403" s="1" t="s">
         <v>5</v>
       </c>
@@ -6100,7 +6067,7 @@
         <v>13191.63204167</v>
       </c>
     </row>
-    <row r="404" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:4">
       <c r="A404" s="1" t="s">
         <v>6</v>
       </c>
@@ -6114,7 +6081,7 @@
         <v>12887.45154167</v>
       </c>
     </row>
-    <row r="405" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:4">
       <c r="A405" s="1" t="s">
         <v>7</v>
       </c>
@@ -6125,10 +6092,10 @@
         <v>46123</v>
       </c>
       <c r="D405" s="3">
-        <v>41562.047208329997</v>
-      </c>
-    </row>
-    <row r="406" spans="1:4" x14ac:dyDescent="0.25">
+        <v>41562.04720833</v>
+      </c>
+    </row>
+    <row r="406" spans="1:4">
       <c r="A406" s="1" t="s">
         <v>4</v>
       </c>
@@ -6139,10 +6106,10 @@
         <v>46124</v>
       </c>
       <c r="D406" s="3">
-        <v>7706.2781249999998</v>
-      </c>
-    </row>
-    <row r="407" spans="1:4" x14ac:dyDescent="0.25">
+        <v>7706.278125</v>
+      </c>
+    </row>
+    <row r="407" spans="1:4">
       <c r="A407" s="1" t="s">
         <v>5</v>
       </c>
@@ -6156,7 +6123,7 @@
         <v>12400.45104167</v>
       </c>
     </row>
-    <row r="408" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:4">
       <c r="A408" s="1" t="s">
         <v>6</v>
       </c>
@@ -6170,7 +6137,7 @@
         <v>11450.980625</v>
       </c>
     </row>
-    <row r="409" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:4">
       <c r="A409" s="1" t="s">
         <v>7</v>
       </c>
@@ -6184,7 +6151,7 @@
         <v>38278.26425</v>
       </c>
     </row>
-    <row r="410" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:4">
       <c r="A410" s="1" t="s">
         <v>4</v>
       </c>
@@ -6198,7 +6165,7 @@
         <v>8279.01129167</v>
       </c>
     </row>
-    <row r="411" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:4">
       <c r="A411" s="1" t="s">
         <v>5</v>
       </c>
@@ -6212,7 +6179,7 @@
         <v>13384.33620833</v>
       </c>
     </row>
-    <row r="412" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:4">
       <c r="A412" s="1" t="s">
         <v>6</v>
       </c>
@@ -6226,7 +6193,7 @@
         <v>14600.9195</v>
       </c>
     </row>
-    <row r="413" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:4">
       <c r="A413" s="1" t="s">
         <v>7</v>
       </c>
@@ -6237,10 +6204,10 @@
         <v>46125</v>
       </c>
       <c r="D413" s="3">
-        <v>45032.581208329997</v>
-      </c>
-    </row>
-    <row r="414" spans="1:4" x14ac:dyDescent="0.25">
+        <v>45032.58120833</v>
+      </c>
+    </row>
+    <row r="414" spans="1:4">
       <c r="A414" s="1" t="s">
         <v>4</v>
       </c>
@@ -6251,10 +6218,10 @@
         <v>46126</v>
       </c>
       <c r="D414" s="3">
-        <v>8254.2927500000005</v>
-      </c>
-    </row>
-    <row r="415" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8254.292750000001</v>
+      </c>
+    </row>
+    <row r="415" spans="1:4">
       <c r="A415" s="1" t="s">
         <v>5</v>
       </c>
@@ -6268,7 +6235,7 @@
         <v>13924.39583333</v>
       </c>
     </row>
-    <row r="416" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:4">
       <c r="A416" s="1" t="s">
         <v>6</v>
       </c>
@@ -6282,7 +6249,7 @@
         <v>15500.19925</v>
       </c>
     </row>
-    <row r="417" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:4">
       <c r="A417" s="1" t="s">
         <v>7</v>
       </c>
@@ -6296,7 +6263,7 @@
         <v>45680.21208333</v>
       </c>
     </row>
-    <row r="418" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:4">
       <c r="A418" s="1" t="s">
         <v>4</v>
       </c>
@@ -6307,10 +6274,10 @@
         <v>46127</v>
       </c>
       <c r="D418" s="3">
-        <v>8266.6923750000005</v>
-      </c>
-    </row>
-    <row r="419" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8266.692375000001</v>
+      </c>
+    </row>
+    <row r="419" spans="1:4">
       <c r="A419" s="1" t="s">
         <v>5</v>
       </c>
@@ -6324,7 +6291,7 @@
         <v>13595.30054167</v>
       </c>
     </row>
-    <row r="420" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:4">
       <c r="A420" s="1" t="s">
         <v>6</v>
       </c>
@@ -6338,7 +6305,7 @@
         <v>15627.81170833</v>
       </c>
     </row>
-    <row r="421" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:4">
       <c r="A421" s="1" t="s">
         <v>7</v>
       </c>
@@ -6349,10 +6316,10 @@
         <v>46127</v>
       </c>
       <c r="D421" s="3">
-        <v>45547.678458330003</v>
-      </c>
-    </row>
-    <row r="422" spans="1:4" x14ac:dyDescent="0.25">
+        <v>45547.67845833</v>
+      </c>
+    </row>
+    <row r="422" spans="1:4">
       <c r="A422" s="1" t="s">
         <v>4</v>
       </c>
@@ -6363,10 +6330,10 @@
         <v>46128</v>
       </c>
       <c r="D422" s="3">
-        <v>8400.6462083299994</v>
-      </c>
-    </row>
-    <row r="423" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8400.646208329999</v>
+      </c>
+    </row>
+    <row r="423" spans="1:4">
       <c r="A423" s="1" t="s">
         <v>5</v>
       </c>
@@ -6377,10 +6344,10 @@
         <v>46128</v>
       </c>
       <c r="D423" s="3">
-        <v>13780.782958330001</v>
-      </c>
-    </row>
-    <row r="424" spans="1:4" x14ac:dyDescent="0.25">
+        <v>13780.78295833</v>
+      </c>
+    </row>
+    <row r="424" spans="1:4">
       <c r="A424" s="1" t="s">
         <v>6</v>
       </c>
@@ -6394,7 +6361,7 @@
         <v>15783.89854167</v>
       </c>
     </row>
-    <row r="425" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:4">
       <c r="A425" s="1" t="s">
         <v>7</v>
       </c>
@@ -6405,10 +6372,10 @@
         <v>46128</v>
       </c>
       <c r="D425" s="3">
-        <v>45614.728000000003</v>
-      </c>
-    </row>
-    <row r="426" spans="1:4" x14ac:dyDescent="0.25">
+        <v>45614.728</v>
+      </c>
+    </row>
+    <row r="426" spans="1:4">
       <c r="A426" s="1" t="s">
         <v>4</v>
       </c>
@@ -6419,10 +6386,10 @@
         <v>46129</v>
       </c>
       <c r="D426" s="3">
-        <v>8362.2609166700004</v>
-      </c>
-    </row>
-    <row r="427" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8362.26091667</v>
+      </c>
+    </row>
+    <row r="427" spans="1:4">
       <c r="A427" s="1" t="s">
         <v>5</v>
       </c>
@@ -6436,7 +6403,7 @@
         <v>13965.53691667</v>
       </c>
     </row>
-    <row r="428" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:4">
       <c r="A428" s="1" t="s">
         <v>6</v>
       </c>
@@ -6447,10 +6414,10 @@
         <v>46129</v>
       </c>
       <c r="D428" s="3">
-        <v>15974.692416669999</v>
-      </c>
-    </row>
-    <row r="429" spans="1:4" x14ac:dyDescent="0.25">
+        <v>15974.69241667</v>
+      </c>
+    </row>
+    <row r="429" spans="1:4">
       <c r="A429" s="1" t="s">
         <v>7</v>
       </c>
@@ -6461,10 +6428,10 @@
         <v>46129</v>
       </c>
       <c r="D429" s="3">
-        <v>46654.342250000002</v>
-      </c>
-    </row>
-    <row r="430" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46654.34225</v>
+      </c>
+    </row>
+    <row r="430" spans="1:4">
       <c r="A430" s="1" t="s">
         <v>4</v>
       </c>
@@ -6475,10 +6442,10 @@
         <v>46130</v>
       </c>
       <c r="D430" s="3">
-        <v>8050.7593333300001</v>
-      </c>
-    </row>
-    <row r="431" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8050.75933333</v>
+      </c>
+    </row>
+    <row r="431" spans="1:4">
       <c r="A431" s="1" t="s">
         <v>5</v>
       </c>
@@ -6492,7 +6459,7 @@
         <v>13365.27841667</v>
       </c>
     </row>
-    <row r="432" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:4">
       <c r="A432" s="1" t="s">
         <v>6</v>
       </c>
@@ -6506,7 +6473,7 @@
         <v>13285.12929167</v>
       </c>
     </row>
-    <row r="433" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:4">
       <c r="A433" s="1" t="s">
         <v>7</v>
       </c>
@@ -6517,10 +6484,10 @@
         <v>46130</v>
       </c>
       <c r="D433" s="3">
-        <v>42903.387041670001</v>
-      </c>
-    </row>
-    <row r="434" spans="1:4" x14ac:dyDescent="0.25">
+        <v>42903.38704167</v>
+      </c>
+    </row>
+    <row r="434" spans="1:4">
       <c r="A434" s="1" t="s">
         <v>4</v>
       </c>
@@ -6531,10 +6498,10 @@
         <v>46131</v>
       </c>
       <c r="D434" s="3">
-        <v>7659.6522916699996</v>
-      </c>
-    </row>
-    <row r="435" spans="1:4" x14ac:dyDescent="0.25">
+        <v>7659.65229167</v>
+      </c>
+    </row>
+    <row r="435" spans="1:4">
       <c r="A435" s="1" t="s">
         <v>5</v>
       </c>
@@ -6545,10 +6512,10 @@
         <v>46131</v>
       </c>
       <c r="D435" s="3">
-        <v>12630.012583330001</v>
-      </c>
-    </row>
-    <row r="436" spans="1:4" x14ac:dyDescent="0.25">
+        <v>12630.01258333</v>
+      </c>
+    </row>
+    <row r="436" spans="1:4">
       <c r="A436" s="1" t="s">
         <v>6</v>
       </c>
@@ -6562,7 +6529,7 @@
         <v>11586.32670833</v>
       </c>
     </row>
-    <row r="437" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:4">
       <c r="A437" s="1" t="s">
         <v>7</v>
       </c>
@@ -6573,10 +6540,10 @@
         <v>46131</v>
       </c>
       <c r="D437" s="3">
-        <v>39159.273999999998</v>
-      </c>
-    </row>
-    <row r="438" spans="1:4" x14ac:dyDescent="0.25">
+        <v>39159.274</v>
+      </c>
+    </row>
+    <row r="438" spans="1:4">
       <c r="A438" s="1" t="s">
         <v>4</v>
       </c>
@@ -6587,10 +6554,10 @@
         <v>46132</v>
       </c>
       <c r="D438" s="3">
-        <v>7947.4844999999996</v>
-      </c>
-    </row>
-    <row r="439" spans="1:4" x14ac:dyDescent="0.25">
+        <v>7947.4845</v>
+      </c>
+    </row>
+    <row r="439" spans="1:4">
       <c r="A439" s="1" t="s">
         <v>5</v>
       </c>
@@ -6604,7 +6571,7 @@
         <v>13634.408125</v>
       </c>
     </row>
-    <row r="440" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:4">
       <c r="A440" s="1" t="s">
         <v>6</v>
       </c>
@@ -6618,7 +6585,7 @@
         <v>13934.1075</v>
       </c>
     </row>
-    <row r="441" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:4">
       <c r="A441" s="1" t="s">
         <v>7</v>
       </c>
@@ -6629,10 +6596,10 @@
         <v>46132</v>
       </c>
       <c r="D441" s="3">
-        <v>42645.508708330002</v>
-      </c>
-    </row>
-    <row r="442" spans="1:4" x14ac:dyDescent="0.25">
+        <v>42645.50870833</v>
+      </c>
+    </row>
+    <row r="442" spans="1:4">
       <c r="A442" s="1" t="s">
         <v>4</v>
       </c>
@@ -6643,10 +6610,10 @@
         <v>46133</v>
       </c>
       <c r="D442" s="3">
-        <v>7894.8174166700001</v>
-      </c>
-    </row>
-    <row r="443" spans="1:4" x14ac:dyDescent="0.25">
+        <v>7894.81741667</v>
+      </c>
+    </row>
+    <row r="443" spans="1:4">
       <c r="A443" s="1" t="s">
         <v>5</v>
       </c>
@@ -6660,7 +6627,7 @@
         <v>12990.715375</v>
       </c>
     </row>
-    <row r="444" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:4">
       <c r="A444" s="1" t="s">
         <v>6</v>
       </c>
@@ -6671,10 +6638,10 @@
         <v>46133</v>
       </c>
       <c r="D444" s="3">
-        <v>13807.992333329999</v>
-      </c>
-    </row>
-    <row r="445" spans="1:4" x14ac:dyDescent="0.25">
+        <v>13807.99233333</v>
+      </c>
+    </row>
+    <row r="445" spans="1:4">
       <c r="A445" s="1" t="s">
         <v>7</v>
       </c>
@@ -6688,7 +6655,7 @@
         <v>41656.0435</v>
       </c>
     </row>
-    <row r="446" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:4">
       <c r="A446" s="1" t="s">
         <v>4</v>
       </c>
@@ -6699,10 +6666,10 @@
         <v>46134</v>
       </c>
       <c r="D446" s="3">
-        <v>8170.4963749999997</v>
-      </c>
-    </row>
-    <row r="447" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8170.496375</v>
+      </c>
+    </row>
+    <row r="447" spans="1:4">
       <c r="A447" s="1" t="s">
         <v>5</v>
       </c>
@@ -6716,7 +6683,7 @@
         <v>13683.18708333</v>
       </c>
     </row>
-    <row r="448" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:4">
       <c r="A448" s="1" t="s">
         <v>6</v>
       </c>
@@ -6730,7 +6697,7 @@
         <v>15477.11075</v>
       </c>
     </row>
-    <row r="449" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:4">
       <c r="A449" s="1" t="s">
         <v>7</v>
       </c>
@@ -6741,10 +6708,10 @@
         <v>46134</v>
       </c>
       <c r="D449" s="3">
-        <v>45331.150333329999</v>
-      </c>
-    </row>
-    <row r="450" spans="1:4" x14ac:dyDescent="0.25">
+        <v>45331.15033333</v>
+      </c>
+    </row>
+    <row r="450" spans="1:4">
       <c r="A450" s="1" t="s">
         <v>4</v>
       </c>
@@ -6755,10 +6722,10 @@
         <v>46135</v>
       </c>
       <c r="D450" s="3">
-        <v>8184.0377500000004</v>
-      </c>
-    </row>
-    <row r="451" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8184.03775</v>
+      </c>
+    </row>
+    <row r="451" spans="1:4">
       <c r="A451" s="1" t="s">
         <v>5</v>
       </c>
@@ -6769,10 +6736,10 @@
         <v>46135</v>
       </c>
       <c r="D451" s="3">
-        <v>13825.214250000001</v>
-      </c>
-    </row>
-    <row r="452" spans="1:4" x14ac:dyDescent="0.25">
+        <v>13825.21425</v>
+      </c>
+    </row>
+    <row r="452" spans="1:4">
       <c r="A452" s="1" t="s">
         <v>6</v>
       </c>
@@ -6783,10 +6750,10 @@
         <v>46135</v>
       </c>
       <c r="D452" s="3">
-        <v>15670.154083330001</v>
-      </c>
-    </row>
-    <row r="453" spans="1:4" x14ac:dyDescent="0.25">
+        <v>15670.15408333</v>
+      </c>
+    </row>
+    <row r="453" spans="1:4">
       <c r="A453" s="1" t="s">
         <v>7</v>
       </c>
@@ -6797,10 +6764,10 @@
         <v>46135</v>
       </c>
       <c r="D453" s="3">
-        <v>45338.885541670003</v>
-      </c>
-    </row>
-    <row r="454" spans="1:4" x14ac:dyDescent="0.25">
+        <v>45338.88554167</v>
+      </c>
+    </row>
+    <row r="454" spans="1:4">
       <c r="A454" s="1" t="s">
         <v>4</v>
       </c>
@@ -6811,10 +6778,10 @@
         <v>46136</v>
       </c>
       <c r="D454" s="3">
-        <v>8219.7653333300004</v>
-      </c>
-    </row>
-    <row r="455" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8219.76533333</v>
+      </c>
+    </row>
+    <row r="455" spans="1:4">
       <c r="A455" s="1" t="s">
         <v>5</v>
       </c>
@@ -6825,10 +6792,10 @@
         <v>46136</v>
       </c>
       <c r="D455" s="3">
-        <v>13834.704291669999</v>
-      </c>
-    </row>
-    <row r="456" spans="1:4" x14ac:dyDescent="0.25">
+        <v>13834.70429167</v>
+      </c>
+    </row>
+    <row r="456" spans="1:4">
       <c r="A456" s="1" t="s">
         <v>6</v>
       </c>
@@ -6842,7 +6809,7 @@
         <v>15383.79579167</v>
       </c>
     </row>
-    <row r="457" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:4">
       <c r="A457" s="1" t="s">
         <v>7</v>
       </c>
@@ -6856,7 +6823,7 @@
         <v>45848.87079167</v>
       </c>
     </row>
-    <row r="458" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:4">
       <c r="A458" s="1" t="s">
         <v>4</v>
       </c>
@@ -6870,7 +6837,7 @@
         <v>7947.12033333</v>
       </c>
     </row>
-    <row r="459" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:4">
       <c r="A459" s="1" t="s">
         <v>5</v>
       </c>
@@ -6884,7 +6851,7 @@
         <v>12820.00379167</v>
       </c>
     </row>
-    <row r="460" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:4">
       <c r="A460" s="1" t="s">
         <v>6</v>
       </c>
@@ -6898,7 +6865,7 @@
         <v>13400.45691667</v>
       </c>
     </row>
-    <row r="461" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:4">
       <c r="A461" s="1" t="s">
         <v>7</v>
       </c>
@@ -6909,10 +6876,10 @@
         <v>46137</v>
       </c>
       <c r="D461" s="3">
-        <v>42938.047291670002</v>
-      </c>
-    </row>
-    <row r="462" spans="1:4" x14ac:dyDescent="0.25">
+        <v>42938.04729167</v>
+      </c>
+    </row>
+    <row r="462" spans="1:4">
       <c r="A462" s="1" t="s">
         <v>4</v>
       </c>
@@ -6923,10 +6890,10 @@
         <v>46138</v>
       </c>
       <c r="D462" s="3">
-        <v>7657.2757083300003</v>
-      </c>
-    </row>
-    <row r="463" spans="1:4" x14ac:dyDescent="0.25">
+        <v>7657.27570833</v>
+      </c>
+    </row>
+    <row r="463" spans="1:4">
       <c r="A463" s="1" t="s">
         <v>5</v>
       </c>
@@ -6940,7 +6907,7 @@
         <v>12023.28895833</v>
       </c>
     </row>
-    <row r="464" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:4">
       <c r="A464" s="1" t="s">
         <v>6</v>
       </c>
@@ -6951,10 +6918,10 @@
         <v>46138</v>
       </c>
       <c r="D464" s="3">
-        <v>11667.080749999999</v>
-      </c>
-    </row>
-    <row r="465" spans="1:4" x14ac:dyDescent="0.25">
+        <v>11667.08075</v>
+      </c>
+    </row>
+    <row r="465" spans="1:4">
       <c r="A465" s="1" t="s">
         <v>7</v>
       </c>
@@ -6965,10 +6932,10 @@
         <v>46138</v>
       </c>
       <c r="D465" s="3">
-        <v>40211.352208329998</v>
-      </c>
-    </row>
-    <row r="466" spans="1:4" x14ac:dyDescent="0.25">
+        <v>40211.35220833</v>
+      </c>
+    </row>
+    <row r="466" spans="1:4">
       <c r="A466" s="1" t="s">
         <v>4</v>
       </c>
@@ -6979,10 +6946,10 @@
         <v>46139</v>
       </c>
       <c r="D466" s="3">
-        <v>8503.1241666700007</v>
-      </c>
-    </row>
-    <row r="467" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8503.124166670001</v>
+      </c>
+    </row>
+    <row r="467" spans="1:4">
       <c r="A467" s="1" t="s">
         <v>5</v>
       </c>
@@ -6996,7 +6963,7 @@
         <v>13611.31120833</v>
       </c>
     </row>
-    <row r="468" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:4">
       <c r="A468" s="1" t="s">
         <v>6</v>
       </c>
@@ -7010,7 +6977,7 @@
         <v>13584.77458333</v>
       </c>
     </row>
-    <row r="469" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:4">
       <c r="A469" s="1" t="s">
         <v>7</v>
       </c>
@@ -7021,10 +6988,10 @@
         <v>46139</v>
       </c>
       <c r="D469" s="3">
-        <v>47558.809791669999</v>
-      </c>
-    </row>
-    <row r="470" spans="1:4" x14ac:dyDescent="0.25">
+        <v>47558.80979167</v>
+      </c>
+    </row>
+    <row r="470" spans="1:4">
       <c r="A470" s="1" t="s">
         <v>4</v>
       </c>
@@ -7035,10 +7002,10 @@
         <v>46140</v>
       </c>
       <c r="D470" s="3">
-        <v>8679.5174999999999</v>
-      </c>
-    </row>
-    <row r="471" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8679.5175</v>
+      </c>
+    </row>
+    <row r="471" spans="1:4">
       <c r="A471" s="1" t="s">
         <v>5</v>
       </c>
@@ -7049,10 +7016,10 @@
         <v>46140</v>
       </c>
       <c r="D471" s="3">
-        <v>13925.177166670001</v>
-      </c>
-    </row>
-    <row r="472" spans="1:4" x14ac:dyDescent="0.25">
+        <v>13925.17716667</v>
+      </c>
+    </row>
+    <row r="472" spans="1:4">
       <c r="A472" s="1" t="s">
         <v>6</v>
       </c>
@@ -7063,10 +7030,10 @@
         <v>46140</v>
       </c>
       <c r="D472" s="3">
-        <v>14168.173583330001</v>
-      </c>
-    </row>
-    <row r="473" spans="1:4" x14ac:dyDescent="0.25">
+        <v>14168.17358333</v>
+      </c>
+    </row>
+    <row r="473" spans="1:4">
       <c r="A473" s="1" t="s">
         <v>7</v>
       </c>
@@ -7077,10 +7044,10 @@
         <v>46140</v>
       </c>
       <c r="D473" s="3">
-        <v>48006.491708330002</v>
-      </c>
-    </row>
-    <row r="474" spans="1:4" x14ac:dyDescent="0.25">
+        <v>48006.49170833</v>
+      </c>
+    </row>
+    <row r="474" spans="1:4">
       <c r="A474" s="1" t="s">
         <v>4</v>
       </c>
@@ -7091,10 +7058,10 @@
         <v>46141</v>
       </c>
       <c r="D474" s="3">
-        <v>8847.6529583299998</v>
-      </c>
-    </row>
-    <row r="475" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8847.65295833</v>
+      </c>
+    </row>
+    <row r="475" spans="1:4">
       <c r="A475" s="1" t="s">
         <v>5</v>
       </c>
@@ -7105,10 +7072,10 @@
         <v>46141</v>
       </c>
       <c r="D475" s="3">
-        <v>13818.179333329999</v>
-      </c>
-    </row>
-    <row r="476" spans="1:4" x14ac:dyDescent="0.25">
+        <v>13818.17933333</v>
+      </c>
+    </row>
+    <row r="476" spans="1:4">
       <c r="A476" s="1" t="s">
         <v>6</v>
       </c>
@@ -7119,10 +7086,10 @@
         <v>46141</v>
       </c>
       <c r="D476" s="3">
-        <v>14626.847458329999</v>
-      </c>
-    </row>
-    <row r="477" spans="1:4" x14ac:dyDescent="0.25">
+        <v>14626.84745833</v>
+      </c>
+    </row>
+    <row r="477" spans="1:4">
       <c r="A477" s="1" t="s">
         <v>7</v>
       </c>
@@ -7133,10 +7100,10 @@
         <v>46141</v>
       </c>
       <c r="D477" s="3">
-        <v>48199.643875000002</v>
-      </c>
-    </row>
-    <row r="478" spans="1:4" x14ac:dyDescent="0.25">
+        <v>48199.643875</v>
+      </c>
+    </row>
+    <row r="478" spans="1:4">
       <c r="A478" s="1" t="s">
         <v>4</v>
       </c>
@@ -7147,10 +7114,10 @@
         <v>46142</v>
       </c>
       <c r="D478" s="3">
-        <v>8715.7270833300008</v>
-      </c>
-    </row>
-    <row r="479" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8715.727083330001</v>
+      </c>
+    </row>
+    <row r="479" spans="1:4">
       <c r="A479" s="1" t="s">
         <v>5</v>
       </c>
@@ -7161,10 +7128,10 @@
         <v>46142</v>
       </c>
       <c r="D479" s="3">
-        <v>13589.848749999999</v>
-      </c>
-    </row>
-    <row r="480" spans="1:4" x14ac:dyDescent="0.25">
+        <v>13589.84875</v>
+      </c>
+    </row>
+    <row r="480" spans="1:4">
       <c r="A480" s="1" t="s">
         <v>6</v>
       </c>
@@ -7178,7 +7145,7 @@
         <v>13756.207</v>
       </c>
     </row>
-    <row r="481" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:4">
       <c r="A481" s="1" t="s">
         <v>7</v>
       </c>
@@ -7192,7 +7159,7 @@
         <v>47051.59979167</v>
       </c>
     </row>
-    <row r="482" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:4">
       <c r="A482" s="1" t="s">
         <v>4</v>
       </c>
@@ -7203,10 +7170,10 @@
         <v>46143</v>
       </c>
       <c r="D482" s="3">
-        <v>7981.7756250000002</v>
-      </c>
-    </row>
-    <row r="483" spans="1:4" x14ac:dyDescent="0.25">
+        <v>7981.775625</v>
+      </c>
+    </row>
+    <row r="483" spans="1:4">
       <c r="A483" s="1" t="s">
         <v>5</v>
       </c>
@@ -7217,10 +7184,10 @@
         <v>46143</v>
       </c>
       <c r="D483" s="3">
-        <v>12429.189041670001</v>
-      </c>
-    </row>
-    <row r="484" spans="1:4" x14ac:dyDescent="0.25">
+        <v>12429.18904167</v>
+      </c>
+    </row>
+    <row r="484" spans="1:4">
       <c r="A484" s="1" t="s">
         <v>6</v>
       </c>
@@ -7231,10 +7198,10 @@
         <v>46143</v>
       </c>
       <c r="D484" s="3">
-        <v>11162.464166670001</v>
-      </c>
-    </row>
-    <row r="485" spans="1:4" x14ac:dyDescent="0.25">
+        <v>11162.46416667</v>
+      </c>
+    </row>
+    <row r="485" spans="1:4">
       <c r="A485" s="1" t="s">
         <v>7</v>
       </c>
@@ -7248,7 +7215,7 @@
         <v>41156.77841667</v>
       </c>
     </row>
-    <row r="486" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:4">
       <c r="A486" s="1" t="s">
         <v>4</v>
       </c>
@@ -7259,10 +7226,10 @@
         <v>46144</v>
       </c>
       <c r="D486" s="3">
-        <v>8212.3590000000004</v>
-      </c>
-    </row>
-    <row r="487" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8212.359</v>
+      </c>
+    </row>
+    <row r="487" spans="1:4">
       <c r="A487" s="1" t="s">
         <v>5</v>
       </c>
@@ -7276,7 +7243,7 @@
         <v>12206.11083333</v>
       </c>
     </row>
-    <row r="488" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:4">
       <c r="A488" s="1" t="s">
         <v>6</v>
       </c>
@@ -7287,10 +7254,10 @@
         <v>46144</v>
       </c>
       <c r="D488" s="3">
-        <v>10857.886583330001</v>
-      </c>
-    </row>
-    <row r="489" spans="1:4" x14ac:dyDescent="0.25">
+        <v>10857.88658333</v>
+      </c>
+    </row>
+    <row r="489" spans="1:4">
       <c r="A489" s="1" t="s">
         <v>7</v>
       </c>
@@ -7301,10 +7268,10 @@
         <v>46144</v>
       </c>
       <c r="D489" s="3">
-        <v>40543.816375000002</v>
-      </c>
-    </row>
-    <row r="490" spans="1:4" x14ac:dyDescent="0.25">
+        <v>40543.816375</v>
+      </c>
+    </row>
+    <row r="490" spans="1:4">
       <c r="A490" s="1" t="s">
         <v>4</v>
       </c>
@@ -7315,10 +7282,10 @@
         <v>46145</v>
       </c>
       <c r="D490" s="3">
-        <v>7772.9988750000002</v>
-      </c>
-    </row>
-    <row r="491" spans="1:4" x14ac:dyDescent="0.25">
+        <v>7772.998875</v>
+      </c>
+    </row>
+    <row r="491" spans="1:4">
       <c r="A491" s="1" t="s">
         <v>5</v>
       </c>
@@ -7332,7 +7299,7 @@
         <v>11915.507</v>
       </c>
     </row>
-    <row r="492" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:4">
       <c r="A492" s="1" t="s">
         <v>6</v>
       </c>
@@ -7343,10 +7310,10 @@
         <v>46145</v>
       </c>
       <c r="D492" s="3">
-        <v>8872.5753750000003</v>
-      </c>
-    </row>
-    <row r="493" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8872.575375</v>
+      </c>
+    </row>
+    <row r="493" spans="1:4">
       <c r="A493" s="1" t="s">
         <v>7</v>
       </c>
@@ -7357,10 +7324,10 @@
         <v>46145</v>
       </c>
       <c r="D493" s="3">
-        <v>37328.978666670002</v>
-      </c>
-    </row>
-    <row r="494" spans="1:4" x14ac:dyDescent="0.25">
+        <v>37328.97866667</v>
+      </c>
+    </row>
+    <row r="494" spans="1:4">
       <c r="A494" s="1" t="s">
         <v>4</v>
       </c>
@@ -7371,10 +7338,10 @@
         <v>46146</v>
       </c>
       <c r="D494" s="3">
-        <v>8343.9433750000007</v>
-      </c>
-    </row>
-    <row r="495" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8343.943375000001</v>
+      </c>
+    </row>
+    <row r="495" spans="1:4">
       <c r="A495" s="1" t="s">
         <v>5</v>
       </c>
@@ -7388,7 +7355,7 @@
         <v>13326.9485</v>
       </c>
     </row>
-    <row r="496" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:4">
       <c r="A496" s="1" t="s">
         <v>6</v>
       </c>
@@ -7402,7 +7369,7 @@
         <v>12616.0995</v>
       </c>
     </row>
-    <row r="497" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:4">
       <c r="A497" s="1" t="s">
         <v>7</v>
       </c>
@@ -7413,10 +7380,10 @@
         <v>46146</v>
       </c>
       <c r="D497" s="3">
-        <v>42847.244208329997</v>
-      </c>
-    </row>
-    <row r="498" spans="1:4" x14ac:dyDescent="0.25">
+        <v>42847.24420833</v>
+      </c>
+    </row>
+    <row r="498" spans="1:4">
       <c r="A498" s="1" t="s">
         <v>4</v>
       </c>
@@ -7427,10 +7394,10 @@
         <v>46147</v>
       </c>
       <c r="D498" s="3">
-        <v>8398.0886666700007</v>
-      </c>
-    </row>
-    <row r="499" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8398.088666670001</v>
+      </c>
+    </row>
+    <row r="499" spans="1:4">
       <c r="A499" s="1" t="s">
         <v>5</v>
       </c>
@@ -7444,7 +7411,7 @@
         <v>13539.855125</v>
       </c>
     </row>
-    <row r="500" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:4">
       <c r="A500" s="1" t="s">
         <v>6</v>
       </c>
@@ -7458,7 +7425,7 @@
         <v>13558.09325</v>
       </c>
     </row>
-    <row r="501" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:4">
       <c r="A501" s="1" t="s">
         <v>7</v>
       </c>
@@ -7469,10 +7436,10 @@
         <v>46147</v>
       </c>
       <c r="D501" s="3">
-        <v>44720.864500000003</v>
-      </c>
-    </row>
-    <row r="502" spans="1:4" x14ac:dyDescent="0.25">
+        <v>44720.8645</v>
+      </c>
+    </row>
+    <row r="502" spans="1:4">
       <c r="A502" s="1" t="s">
         <v>4</v>
       </c>
@@ -7483,10 +7450,10 @@
         <v>46148</v>
       </c>
       <c r="D502" s="3">
-        <v>8450.3235416700008</v>
-      </c>
-    </row>
-    <row r="503" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8450.323541670001</v>
+      </c>
+    </row>
+    <row r="503" spans="1:4">
       <c r="A503" s="1" t="s">
         <v>5</v>
       </c>
@@ -7497,10 +7464,10 @@
         <v>46148</v>
       </c>
       <c r="D503" s="3">
-        <v>14074.559458330001</v>
-      </c>
-    </row>
-    <row r="504" spans="1:4" x14ac:dyDescent="0.25">
+        <v>14074.55945833</v>
+      </c>
+    </row>
+    <row r="504" spans="1:4">
       <c r="A504" s="1" t="s">
         <v>6</v>
       </c>
@@ -7514,7 +7481,7 @@
         <v>14482.4995</v>
       </c>
     </row>
-    <row r="505" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:4">
       <c r="A505" s="1" t="s">
         <v>7</v>
       </c>
@@ -7525,10 +7492,10 @@
         <v>46148</v>
       </c>
       <c r="D505" s="3">
-        <v>45743.645958330002</v>
-      </c>
-    </row>
-    <row r="506" spans="1:4" x14ac:dyDescent="0.25">
+        <v>45743.64595833</v>
+      </c>
+    </row>
+    <row r="506" spans="1:4">
       <c r="A506" s="1" t="s">
         <v>4</v>
       </c>
@@ -7542,7 +7509,7 @@
         <v>8490.560125</v>
       </c>
     </row>
-    <row r="507" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:4">
       <c r="A507" s="1" t="s">
         <v>5</v>
       </c>
@@ -7553,10 +7520,10 @@
         <v>46149</v>
       </c>
       <c r="D507" s="3">
-        <v>13645.749666670001</v>
-      </c>
-    </row>
-    <row r="508" spans="1:4" x14ac:dyDescent="0.25">
+        <v>13645.74966667</v>
+      </c>
+    </row>
+    <row r="508" spans="1:4">
       <c r="A508" s="1" t="s">
         <v>6</v>
       </c>
@@ -7567,10 +7534,10 @@
         <v>46149</v>
       </c>
       <c r="D508" s="3">
-        <v>14608.772041669999</v>
-      </c>
-    </row>
-    <row r="509" spans="1:4" x14ac:dyDescent="0.25">
+        <v>14608.77204167</v>
+      </c>
+    </row>
+    <row r="509" spans="1:4">
       <c r="A509" s="1" t="s">
         <v>7</v>
       </c>
@@ -7584,7 +7551,7 @@
         <v>47018.35333333</v>
       </c>
     </row>
-    <row r="510" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:4">
       <c r="A510" s="1" t="s">
         <v>4</v>
       </c>
@@ -7595,10 +7562,10 @@
         <v>46150</v>
       </c>
       <c r="D510" s="3">
-        <v>8522.1304166699992</v>
-      </c>
-    </row>
-    <row r="511" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8522.130416669999</v>
+      </c>
+    </row>
+    <row r="511" spans="1:4">
       <c r="A511" s="1" t="s">
         <v>5</v>
       </c>
@@ -7609,10 +7576,10 @@
         <v>46150</v>
       </c>
       <c r="D511" s="3">
-        <v>13641.182000000001</v>
-      </c>
-    </row>
-    <row r="512" spans="1:4" x14ac:dyDescent="0.25">
+        <v>13641.182</v>
+      </c>
+    </row>
+    <row r="512" spans="1:4">
       <c r="A512" s="1" t="s">
         <v>6</v>
       </c>
@@ -7623,10 +7590,10 @@
         <v>46150</v>
       </c>
       <c r="D512" s="3">
-        <v>14029.195291669999</v>
-      </c>
-    </row>
-    <row r="513" spans="1:4" x14ac:dyDescent="0.25">
+        <v>14029.19529167</v>
+      </c>
+    </row>
+    <row r="513" spans="1:4">
       <c r="A513" s="1" t="s">
         <v>7</v>
       </c>
@@ -7637,10 +7604,10 @@
         <v>46150</v>
       </c>
       <c r="D513" s="3">
-        <v>47534.814208329997</v>
-      </c>
-    </row>
-    <row r="514" spans="1:4" x14ac:dyDescent="0.25">
+        <v>47534.81420833</v>
+      </c>
+    </row>
+    <row r="514" spans="1:4">
       <c r="A514" s="1" t="s">
         <v>4</v>
       </c>
@@ -7651,10 +7618,10 @@
         <v>46151</v>
       </c>
       <c r="D514" s="3">
-        <v>8206.3577499999992</v>
-      </c>
-    </row>
-    <row r="515" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8206.357749999999</v>
+      </c>
+    </row>
+    <row r="515" spans="1:4">
       <c r="A515" s="1" t="s">
         <v>5</v>
       </c>
@@ -7665,10 +7632,10 @@
         <v>46151</v>
       </c>
       <c r="D515" s="3">
-        <v>12851.137916670001</v>
-      </c>
-    </row>
-    <row r="516" spans="1:4" x14ac:dyDescent="0.25">
+        <v>12851.13791667</v>
+      </c>
+    </row>
+    <row r="516" spans="1:4">
       <c r="A516" s="1" t="s">
         <v>6</v>
       </c>
@@ -7682,7 +7649,7 @@
         <v>11683.80820833</v>
       </c>
     </row>
-    <row r="517" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:4">
       <c r="A517" s="1" t="s">
         <v>7</v>
       </c>
@@ -7693,10 +7660,10 @@
         <v>46151</v>
       </c>
       <c r="D517" s="3">
-        <v>43994.144500000002</v>
-      </c>
-    </row>
-    <row r="518" spans="1:4" x14ac:dyDescent="0.25">
+        <v>43994.1445</v>
+      </c>
+    </row>
+    <row r="518" spans="1:4">
       <c r="A518" s="1" t="s">
         <v>4</v>
       </c>
@@ -7707,10 +7674,10 @@
         <v>46152</v>
       </c>
       <c r="D518" s="3">
-        <v>7727.9523749999998</v>
-      </c>
-    </row>
-    <row r="519" spans="1:4" x14ac:dyDescent="0.25">
+        <v>7727.952375</v>
+      </c>
+    </row>
+    <row r="519" spans="1:4">
       <c r="A519" s="1" t="s">
         <v>5</v>
       </c>
@@ -7724,7 +7691,7 @@
         <v>12212.09041667</v>
       </c>
     </row>
-    <row r="520" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:4">
       <c r="A520" s="1" t="s">
         <v>6</v>
       </c>
@@ -7735,10 +7702,10 @@
         <v>46152</v>
       </c>
       <c r="D520" s="3">
-        <v>9463.0417083299999</v>
-      </c>
-    </row>
-    <row r="521" spans="1:4" x14ac:dyDescent="0.25">
+        <v>9463.04170833</v>
+      </c>
+    </row>
+    <row r="521" spans="1:4">
       <c r="A521" s="1" t="s">
         <v>7</v>
       </c>
@@ -7749,10 +7716,10 @@
         <v>46152</v>
       </c>
       <c r="D521" s="3">
-        <v>38345.524166670002</v>
-      </c>
-    </row>
-    <row r="522" spans="1:4" x14ac:dyDescent="0.25">
+        <v>38345.52416667</v>
+      </c>
+    </row>
+    <row r="522" spans="1:4">
       <c r="A522" s="1" t="s">
         <v>4</v>
       </c>
@@ -7763,10 +7730,10 @@
         <v>46153</v>
       </c>
       <c r="D522" s="3">
-        <v>8519.2494166699998</v>
-      </c>
-    </row>
-    <row r="523" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8519.24941667</v>
+      </c>
+    </row>
+    <row r="523" spans="1:4">
       <c r="A523" s="1" t="s">
         <v>5</v>
       </c>
@@ -7780,7 +7747,7 @@
         <v>13242.394375</v>
       </c>
     </row>
-    <row r="524" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:4">
       <c r="A524" s="1" t="s">
         <v>6</v>
       </c>
@@ -7791,10 +7758,10 @@
         <v>46153</v>
       </c>
       <c r="D524" s="3">
-        <v>12595.856374999999</v>
-      </c>
-    </row>
-    <row r="525" spans="1:4" x14ac:dyDescent="0.25">
+        <v>12595.856375</v>
+      </c>
+    </row>
+    <row r="525" spans="1:4">
       <c r="A525" s="1" t="s">
         <v>7</v>
       </c>
@@ -7805,10 +7772,10 @@
         <v>46153</v>
       </c>
       <c r="D525" s="3">
-        <v>41788.470874999999</v>
-      </c>
-    </row>
-    <row r="526" spans="1:4" x14ac:dyDescent="0.25">
+        <v>41788.470875</v>
+      </c>
+    </row>
+    <row r="526" spans="1:4">
       <c r="A526" s="1" t="s">
         <v>4</v>
       </c>
@@ -7819,10 +7786,10 @@
         <v>46154</v>
       </c>
       <c r="D526" s="3">
-        <v>8437.8624583300007</v>
-      </c>
-    </row>
-    <row r="527" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8437.862458330001</v>
+      </c>
+    </row>
+    <row r="527" spans="1:4">
       <c r="A527" s="1" t="s">
         <v>5</v>
       </c>
@@ -7836,7 +7803,7 @@
         <v>13488.04675</v>
       </c>
     </row>
-    <row r="528" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:4">
       <c r="A528" s="1" t="s">
         <v>6</v>
       </c>
@@ -7850,7 +7817,7 @@
         <v>13209.87508333</v>
       </c>
     </row>
-    <row r="529" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:4">
       <c r="A529" s="1" t="s">
         <v>7</v>
       </c>
@@ -7861,10 +7828,10 @@
         <v>46154</v>
       </c>
       <c r="D529" s="3">
-        <v>41879.643041670002</v>
-      </c>
-    </row>
-    <row r="530" spans="1:4" x14ac:dyDescent="0.25">
+        <v>41879.64304167</v>
+      </c>
+    </row>
+    <row r="530" spans="1:4">
       <c r="A530" s="1" t="s">
         <v>4</v>
       </c>
@@ -7878,7 +7845,7 @@
         <v>8030.39045833</v>
       </c>
     </row>
-    <row r="531" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:4">
       <c r="A531" s="1" t="s">
         <v>5</v>
       </c>
@@ -7889,10 +7856,10 @@
         <v>46155</v>
       </c>
       <c r="D531" s="3">
-        <v>13390.155000000001</v>
-      </c>
-    </row>
-    <row r="532" spans="1:4" x14ac:dyDescent="0.25">
+        <v>13390.155</v>
+      </c>
+    </row>
+    <row r="532" spans="1:4">
       <c r="A532" s="1" t="s">
         <v>6</v>
       </c>
@@ -7903,10 +7870,10 @@
         <v>46155</v>
       </c>
       <c r="D532" s="3">
-        <v>13378.518625000001</v>
-      </c>
-    </row>
-    <row r="533" spans="1:4" x14ac:dyDescent="0.25">
+        <v>13378.518625</v>
+      </c>
+    </row>
+    <row r="533" spans="1:4">
       <c r="A533" s="1" t="s">
         <v>7</v>
       </c>
@@ -7917,10 +7884,10 @@
         <v>46155</v>
       </c>
       <c r="D533" s="3">
-        <v>42768.322166669997</v>
-      </c>
-    </row>
-    <row r="534" spans="1:4" x14ac:dyDescent="0.25">
+        <v>42768.32216667</v>
+      </c>
+    </row>
+    <row r="534" spans="1:4">
       <c r="A534" s="1" t="s">
         <v>4</v>
       </c>
@@ -7931,10 +7898,10 @@
         <v>46156</v>
       </c>
       <c r="D534" s="3">
-        <v>8391.0449583299996</v>
-      </c>
-    </row>
-    <row r="535" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8391.04495833</v>
+      </c>
+    </row>
+    <row r="535" spans="1:4">
       <c r="A535" s="1" t="s">
         <v>5</v>
       </c>
@@ -7948,7 +7915,7 @@
         <v>13577.359875</v>
       </c>
     </row>
-    <row r="536" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:4">
       <c r="A536" s="1" t="s">
         <v>6</v>
       </c>
@@ -7962,7 +7929,7 @@
         <v>13622.124875</v>
       </c>
     </row>
-    <row r="537" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:4">
       <c r="A537" s="1" t="s">
         <v>7</v>
       </c>
@@ -7973,10 +7940,10 @@
         <v>46156</v>
       </c>
       <c r="D537" s="3">
-        <v>44186.666333330002</v>
-      </c>
-    </row>
-    <row r="538" spans="1:4" x14ac:dyDescent="0.25">
+        <v>44186.66633333</v>
+      </c>
+    </row>
+    <row r="538" spans="1:4">
       <c r="A538" s="1" t="s">
         <v>4</v>
       </c>
@@ -7987,10 +7954,10 @@
         <v>46157</v>
       </c>
       <c r="D538" s="3">
-        <v>8435.2047083300004</v>
-      </c>
-    </row>
-    <row r="539" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8435.20470833</v>
+      </c>
+    </row>
+    <row r="539" spans="1:4">
       <c r="A539" s="1" t="s">
         <v>5</v>
       </c>
@@ -8004,7 +7971,7 @@
         <v>13334.23920833</v>
       </c>
     </row>
-    <row r="540" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:4">
       <c r="A540" s="1" t="s">
         <v>6</v>
       </c>
@@ -8018,7 +7985,7 @@
         <v>14344.37045833</v>
       </c>
     </row>
-    <row r="541" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:4">
       <c r="A541" s="1" t="s">
         <v>7</v>
       </c>
@@ -8029,10 +7996,10 @@
         <v>46157</v>
       </c>
       <c r="D541" s="3">
-        <v>45601.632541669998</v>
-      </c>
-    </row>
-    <row r="542" spans="1:4" x14ac:dyDescent="0.25">
+        <v>45601.63254167</v>
+      </c>
+    </row>
+    <row r="542" spans="1:4">
       <c r="A542" s="1" t="s">
         <v>4</v>
       </c>
@@ -8043,10 +8010,10 @@
         <v>46158</v>
       </c>
       <c r="D542" s="3">
-        <v>8246.2368333300001</v>
-      </c>
-    </row>
-    <row r="543" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8246.23683333</v>
+      </c>
+    </row>
+    <row r="543" spans="1:4">
       <c r="A543" s="1" t="s">
         <v>5</v>
       </c>
@@ -8057,10 +8024,10 @@
         <v>46158</v>
       </c>
       <c r="D543" s="3">
-        <v>12573.538208329999</v>
-      </c>
-    </row>
-    <row r="544" spans="1:4" x14ac:dyDescent="0.25">
+        <v>12573.53820833</v>
+      </c>
+    </row>
+    <row r="544" spans="1:4">
       <c r="A544" s="1" t="s">
         <v>6</v>
       </c>
@@ -8074,7 +8041,7 @@
         <v>12471.90783333</v>
       </c>
     </row>
-    <row r="545" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:4">
       <c r="A545" s="1" t="s">
         <v>7</v>
       </c>
@@ -8085,10 +8052,10 @@
         <v>46158</v>
       </c>
       <c r="D545" s="3">
-        <v>42359.038166669998</v>
-      </c>
-    </row>
-    <row r="546" spans="1:4" x14ac:dyDescent="0.25">
+        <v>42359.03816667</v>
+      </c>
+    </row>
+    <row r="546" spans="1:4">
       <c r="A546" s="1" t="s">
         <v>4</v>
       </c>
@@ -8102,7 +8069,7 @@
         <v>7877.21654167</v>
       </c>
     </row>
-    <row r="547" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:4">
       <c r="A547" s="1" t="s">
         <v>5</v>
       </c>
@@ -8116,7 +8083,7 @@
         <v>11801.7125</v>
       </c>
     </row>
-    <row r="548" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:4">
       <c r="A548" s="1" t="s">
         <v>6</v>
       </c>
@@ -8127,10 +8094,10 @@
         <v>46159</v>
       </c>
       <c r="D548" s="3">
-        <v>11514.898958330001</v>
-      </c>
-    </row>
-    <row r="549" spans="1:4" x14ac:dyDescent="0.25">
+        <v>11514.89895833</v>
+      </c>
+    </row>
+    <row r="549" spans="1:4">
       <c r="A549" s="1" t="s">
         <v>7</v>
       </c>
@@ -8141,10 +8108,10 @@
         <v>46159</v>
       </c>
       <c r="D549" s="3">
-        <v>39792.117624999999</v>
-      </c>
-    </row>
-    <row r="550" spans="1:4" x14ac:dyDescent="0.25">
+        <v>39792.117625</v>
+      </c>
+    </row>
+    <row r="550" spans="1:4">
       <c r="A550" s="1" t="s">
         <v>4</v>
       </c>
@@ -8155,10 +8122,10 @@
         <v>46160</v>
       </c>
       <c r="D550" s="3">
-        <v>8640.6350833300003</v>
-      </c>
-    </row>
-    <row r="551" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8640.63508333</v>
+      </c>
+    </row>
+    <row r="551" spans="1:4">
       <c r="A551" s="1" t="s">
         <v>5</v>
       </c>
@@ -8169,10 +8136,10 @@
         <v>46160</v>
       </c>
       <c r="D551" s="3">
-        <v>13126.793291669999</v>
-      </c>
-    </row>
-    <row r="552" spans="1:4" x14ac:dyDescent="0.25">
+        <v>13126.79329167</v>
+      </c>
+    </row>
+    <row r="552" spans="1:4">
       <c r="A552" s="1" t="s">
         <v>6</v>
       </c>
@@ -8186,7 +8153,7 @@
         <v>13722.37358333</v>
       </c>
     </row>
-    <row r="553" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:4">
       <c r="A553" s="1" t="s">
         <v>7</v>
       </c>
@@ -8200,7 +8167,7 @@
         <v>45250.373625</v>
       </c>
     </row>
-    <row r="554" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:4">
       <c r="A554" s="1" t="s">
         <v>4</v>
       </c>
@@ -8211,10 +8178,10 @@
         <v>46161</v>
       </c>
       <c r="D554" s="3">
-        <v>8670.2018750000007</v>
-      </c>
-    </row>
-    <row r="555" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8670.201875000001</v>
+      </c>
+    </row>
+    <row r="555" spans="1:4">
       <c r="A555" s="1" t="s">
         <v>5</v>
       </c>
@@ -8228,7 +8195,7 @@
         <v>13329.19266667</v>
       </c>
     </row>
-    <row r="556" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:4">
       <c r="A556" s="1" t="s">
         <v>6</v>
       </c>
@@ -8239,10 +8206,10 @@
         <v>46161</v>
       </c>
       <c r="D556" s="3">
-        <v>14038.144625000001</v>
-      </c>
-    </row>
-    <row r="557" spans="1:4" x14ac:dyDescent="0.25">
+        <v>14038.144625</v>
+      </c>
+    </row>
+    <row r="557" spans="1:4">
       <c r="A557" s="1" t="s">
         <v>7</v>
       </c>
@@ -8253,10 +8220,10 @@
         <v>46161</v>
       </c>
       <c r="D557" s="3">
-        <v>45623.808458330001</v>
-      </c>
-    </row>
-    <row r="558" spans="1:4" x14ac:dyDescent="0.25">
+        <v>45623.80845833</v>
+      </c>
+    </row>
+    <row r="558" spans="1:4">
       <c r="A558" s="1" t="s">
         <v>4</v>
       </c>
@@ -8267,10 +8234,10 @@
         <v>46162</v>
       </c>
       <c r="D558" s="3">
-        <v>8700.9040833300005</v>
-      </c>
-    </row>
-    <row r="559" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8700.904083330001</v>
+      </c>
+    </row>
+    <row r="559" spans="1:4">
       <c r="A559" s="1" t="s">
         <v>5</v>
       </c>
@@ -8284,7 +8251,7 @@
         <v>13466.02370833</v>
       </c>
     </row>
-    <row r="560" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:4">
       <c r="A560" s="1" t="s">
         <v>6</v>
       </c>
@@ -8298,7 +8265,7 @@
         <v>13742.01420833</v>
       </c>
     </row>
-    <row r="561" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:4">
       <c r="A561" s="1" t="s">
         <v>7</v>
       </c>
@@ -8312,7 +8279,7 @@
         <v>44537.25</v>
       </c>
     </row>
-    <row r="562" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:4">
       <c r="A562" s="1" t="s">
         <v>4</v>
       </c>
@@ -8323,10 +8290,10 @@
         <v>46163</v>
       </c>
       <c r="D562" s="3">
-        <v>8533.7514583299999</v>
-      </c>
-    </row>
-    <row r="563" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8533.75145833</v>
+      </c>
+    </row>
+    <row r="563" spans="1:4">
       <c r="A563" s="1" t="s">
         <v>5</v>
       </c>
@@ -8340,7 +8307,7 @@
         <v>13630.64579167</v>
       </c>
     </row>
-    <row r="564" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:4">
       <c r="A564" s="1" t="s">
         <v>6</v>
       </c>
@@ -8354,7 +8321,7 @@
         <v>13713.5975</v>
       </c>
     </row>
-    <row r="565" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:4">
       <c r="A565" s="1" t="s">
         <v>7</v>
       </c>
@@ -8365,10 +8332,10 @@
         <v>46163</v>
       </c>
       <c r="D565" s="3">
-        <v>43314.436666670001</v>
-      </c>
-    </row>
-    <row r="566" spans="1:4" x14ac:dyDescent="0.25">
+        <v>43314.43666667</v>
+      </c>
+    </row>
+    <row r="566" spans="1:4">
       <c r="A566" s="1" t="s">
         <v>4</v>
       </c>
@@ -8379,10 +8346,10 @@
         <v>46164</v>
       </c>
       <c r="D566" s="3">
-        <v>8427.5570416699993</v>
-      </c>
-    </row>
-    <row r="567" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8427.557041669999</v>
+      </c>
+    </row>
+    <row r="567" spans="1:4">
       <c r="A567" s="1" t="s">
         <v>5</v>
       </c>
@@ -8393,10 +8360,10 @@
         <v>46164</v>
       </c>
       <c r="D567" s="3">
-        <v>13573.841708329999</v>
-      </c>
-    </row>
-    <row r="568" spans="1:4" x14ac:dyDescent="0.25">
+        <v>13573.84170833</v>
+      </c>
+    </row>
+    <row r="568" spans="1:4">
       <c r="A568" s="1" t="s">
         <v>6</v>
       </c>
@@ -8410,7 +8377,7 @@
         <v>14456.00375</v>
       </c>
     </row>
-    <row r="569" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:4">
       <c r="A569" s="1" t="s">
         <v>7</v>
       </c>
@@ -8421,10 +8388,10 @@
         <v>46164</v>
       </c>
       <c r="D569" s="3">
-        <v>42793.234250000001</v>
-      </c>
-    </row>
-    <row r="570" spans="1:4" x14ac:dyDescent="0.25">
+        <v>42793.23425</v>
+      </c>
+    </row>
+    <row r="570" spans="1:4">
       <c r="A570" s="1" t="s">
         <v>4</v>
       </c>
@@ -8435,10 +8402,10 @@
         <v>46165</v>
       </c>
       <c r="D570" s="3">
-        <v>7926.3024583300003</v>
-      </c>
-    </row>
-    <row r="571" spans="1:4" x14ac:dyDescent="0.25">
+        <v>7926.30245833</v>
+      </c>
+    </row>
+    <row r="571" spans="1:4">
       <c r="A571" s="1" t="s">
         <v>5</v>
       </c>
@@ -8452,7 +8419,7 @@
         <v>12903.332875</v>
       </c>
     </row>
-    <row r="572" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:4">
       <c r="A572" s="1" t="s">
         <v>6</v>
       </c>
@@ -8466,7 +8433,7 @@
         <v>12305.151625</v>
       </c>
     </row>
-    <row r="573" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:4">
       <c r="A573" s="1" t="s">
         <v>7</v>
       </c>
@@ -8477,10 +8444,10 @@
         <v>46165</v>
       </c>
       <c r="D573" s="3">
-        <v>39742.391333330001</v>
-      </c>
-    </row>
-    <row r="574" spans="1:4" x14ac:dyDescent="0.25">
+        <v>39742.39133333</v>
+      </c>
+    </row>
+    <row r="574" spans="1:4">
       <c r="A574" s="1" t="s">
         <v>4</v>
       </c>
@@ -8491,10 +8458,10 @@
         <v>46166</v>
       </c>
       <c r="D574" s="3">
-        <v>7518.6561666699999</v>
-      </c>
-    </row>
-    <row r="575" spans="1:4" x14ac:dyDescent="0.25">
+        <v>7518.65616667</v>
+      </c>
+    </row>
+    <row r="575" spans="1:4">
       <c r="A575" s="1" t="s">
         <v>5</v>
       </c>
@@ -8508,7 +8475,7 @@
         <v>11858.69604167</v>
       </c>
     </row>
-    <row r="576" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:4">
       <c r="A576" s="1" t="s">
         <v>6</v>
       </c>
@@ -8519,10 +8486,10 @@
         <v>46166</v>
       </c>
       <c r="D576" s="3">
-        <v>10745.089833329999</v>
-      </c>
-    </row>
-    <row r="577" spans="1:4" x14ac:dyDescent="0.25">
+        <v>10745.08983333</v>
+      </c>
+    </row>
+    <row r="577" spans="1:4">
       <c r="A577" s="1" t="s">
         <v>7</v>
       </c>
@@ -8533,10 +8500,10 @@
         <v>46166</v>
       </c>
       <c r="D577" s="3">
-        <v>36171.107250000001</v>
-      </c>
-    </row>
-    <row r="578" spans="1:4" x14ac:dyDescent="0.25">
+        <v>36171.10725</v>
+      </c>
+    </row>
+    <row r="578" spans="1:4">
       <c r="A578" s="1" t="s">
         <v>4</v>
       </c>
@@ -8547,10 +8514,10 @@
         <v>46167</v>
       </c>
       <c r="D578" s="3">
-        <v>8005.3499583299999</v>
-      </c>
-    </row>
-    <row r="579" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8005.34995833</v>
+      </c>
+    </row>
+    <row r="579" spans="1:4">
       <c r="A579" s="1" t="s">
         <v>5</v>
       </c>
@@ -8564,7 +8531,7 @@
         <v>13242.32775</v>
       </c>
     </row>
-    <row r="580" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:4">
       <c r="A580" s="1" t="s">
         <v>6</v>
       </c>
@@ -8578,7 +8545,7 @@
         <v>13893.17179167</v>
       </c>
     </row>
-    <row r="581" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:4">
       <c r="A581" s="1" t="s">
         <v>7</v>
       </c>
@@ -8589,10 +8556,10 @@
         <v>46167</v>
       </c>
       <c r="D581" s="3">
-        <v>42091.838624999997</v>
-      </c>
-    </row>
-    <row r="582" spans="1:4" x14ac:dyDescent="0.25">
+        <v>42091.838625</v>
+      </c>
+    </row>
+    <row r="582" spans="1:4">
       <c r="A582" s="1" t="s">
         <v>4</v>
       </c>
@@ -8603,10 +8570,10 @@
         <v>46168</v>
       </c>
       <c r="D582" s="3">
-        <v>8145.9313333299997</v>
-      </c>
-    </row>
-    <row r="583" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8145.93133333</v>
+      </c>
+    </row>
+    <row r="583" spans="1:4">
       <c r="A583" s="1" t="s">
         <v>5</v>
       </c>
@@ -8620,7 +8587,7 @@
         <v>13415.95308333</v>
       </c>
     </row>
-    <row r="584" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:4">
       <c r="A584" s="1" t="s">
         <v>6</v>
       </c>
@@ -8634,7 +8601,7 @@
         <v>14171.45791667</v>
       </c>
     </row>
-    <row r="585" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:4">
       <c r="A585" s="1" t="s">
         <v>7</v>
       </c>
@@ -8645,10 +8612,10 @@
         <v>46168</v>
       </c>
       <c r="D585" s="3">
-        <v>43601.353541670003</v>
-      </c>
-    </row>
-    <row r="586" spans="1:4" x14ac:dyDescent="0.25">
+        <v>43601.35354167</v>
+      </c>
+    </row>
+    <row r="586" spans="1:4">
       <c r="A586" s="1" t="s">
         <v>4</v>
       </c>
@@ -8659,10 +8626,10 @@
         <v>46169</v>
       </c>
       <c r="D586" s="3">
-        <v>8280.6479166699992</v>
-      </c>
-    </row>
-    <row r="587" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8280.647916669999</v>
+      </c>
+    </row>
+    <row r="587" spans="1:4">
       <c r="A587" s="1" t="s">
         <v>5</v>
       </c>
@@ -8673,10 +8640,10 @@
         <v>46169</v>
       </c>
       <c r="D587" s="3">
-        <v>13626.706666669999</v>
-      </c>
-    </row>
-    <row r="588" spans="1:4" x14ac:dyDescent="0.25">
+        <v>13626.70666667</v>
+      </c>
+    </row>
+    <row r="588" spans="1:4">
       <c r="A588" s="1" t="s">
         <v>6</v>
       </c>
@@ -8690,7 +8657,7 @@
         <v>13255.13825</v>
       </c>
     </row>
-    <row r="589" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:4">
       <c r="A589" s="1" t="s">
         <v>7</v>
       </c>
@@ -8701,10 +8668,10 @@
         <v>46169</v>
       </c>
       <c r="D589" s="3">
-        <v>43960.538958329998</v>
-      </c>
-    </row>
-    <row r="590" spans="1:4" x14ac:dyDescent="0.25">
+        <v>43960.53895833</v>
+      </c>
+    </row>
+    <row r="590" spans="1:4">
       <c r="A590" s="1" t="s">
         <v>4</v>
       </c>
@@ -8715,10 +8682,10 @@
         <v>46170</v>
       </c>
       <c r="D590" s="3">
-        <v>8331.7510833300003</v>
-      </c>
-    </row>
-    <row r="591" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8331.75108333</v>
+      </c>
+    </row>
+    <row r="591" spans="1:4">
       <c r="A591" s="1" t="s">
         <v>5</v>
       </c>
@@ -8732,7 +8699,7 @@
         <v>13344.170375</v>
       </c>
     </row>
-    <row r="592" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:4">
       <c r="A592" s="1" t="s">
         <v>6</v>
       </c>
@@ -8746,7 +8713,7 @@
         <v>13371.86591667</v>
       </c>
     </row>
-    <row r="593" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:4">
       <c r="A593" s="1" t="s">
         <v>7</v>
       </c>
@@ -8757,10 +8724,10 @@
         <v>46170</v>
       </c>
       <c r="D593" s="3">
-        <v>42817.327499999999</v>
-      </c>
-    </row>
-    <row r="594" spans="1:4" x14ac:dyDescent="0.25">
+        <v>42817.3275</v>
+      </c>
+    </row>
+    <row r="594" spans="1:4">
       <c r="A594" s="1" t="s">
         <v>4</v>
       </c>
@@ -8771,10 +8738,10 @@
         <v>46171</v>
       </c>
       <c r="D594" s="3">
-        <v>8548.9400416699991</v>
-      </c>
-    </row>
-    <row r="595" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8548.940041669999</v>
+      </c>
+    </row>
+    <row r="595" spans="1:4">
       <c r="A595" s="1" t="s">
         <v>5</v>
       </c>
@@ -8785,10 +8752,10 @@
         <v>46171</v>
       </c>
       <c r="D595" s="3">
-        <v>13356.016166670001</v>
-      </c>
-    </row>
-    <row r="596" spans="1:4" x14ac:dyDescent="0.25">
+        <v>13356.01616667</v>
+      </c>
+    </row>
+    <row r="596" spans="1:4">
       <c r="A596" s="1" t="s">
         <v>6</v>
       </c>
@@ -8799,10 +8766,10 @@
         <v>46171</v>
       </c>
       <c r="D596" s="3">
-        <v>13604.567875000001</v>
-      </c>
-    </row>
-    <row r="597" spans="1:4" x14ac:dyDescent="0.25">
+        <v>13604.567875</v>
+      </c>
+    </row>
+    <row r="597" spans="1:4">
       <c r="A597" s="1" t="s">
         <v>7</v>
       </c>
@@ -8813,10 +8780,10 @@
         <v>46171</v>
       </c>
       <c r="D597" s="3">
-        <v>42532.498749999999</v>
-      </c>
-    </row>
-    <row r="598" spans="1:4" x14ac:dyDescent="0.25">
+        <v>42532.49875</v>
+      </c>
+    </row>
+    <row r="598" spans="1:4">
       <c r="A598" s="1" t="s">
         <v>4</v>
       </c>
@@ -8827,10 +8794,10 @@
         <v>46172</v>
       </c>
       <c r="D598" s="3">
-        <v>8343.7042916699993</v>
-      </c>
-    </row>
-    <row r="599" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8343.704291669999</v>
+      </c>
+    </row>
+    <row r="599" spans="1:4">
       <c r="A599" s="1" t="s">
         <v>5</v>
       </c>
@@ -8844,7 +8811,7 @@
         <v>13086.79920833</v>
       </c>
     </row>
-    <row r="600" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:4">
       <c r="A600" s="1" t="s">
         <v>6</v>
       </c>
@@ -8858,7 +8825,7 @@
         <v>11433.616125</v>
       </c>
     </row>
-    <row r="601" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:4">
       <c r="A601" s="1" t="s">
         <v>7</v>
       </c>
@@ -8869,10 +8836,10 @@
         <v>46172</v>
       </c>
       <c r="D601" s="3">
-        <v>39398.709291669998</v>
-      </c>
-    </row>
-    <row r="602" spans="1:4" x14ac:dyDescent="0.25">
+        <v>39398.70929167</v>
+      </c>
+    </row>
+    <row r="602" spans="1:4">
       <c r="A602" s="1" t="s">
         <v>4</v>
       </c>
@@ -8883,10 +8850,10 @@
         <v>46173</v>
       </c>
       <c r="D602" s="3">
-        <v>7841.5592500000002</v>
-      </c>
-    </row>
-    <row r="603" spans="1:4" x14ac:dyDescent="0.25">
+        <v>7841.55925</v>
+      </c>
+    </row>
+    <row r="603" spans="1:4">
       <c r="A603" s="1" t="s">
         <v>5</v>
       </c>
@@ -8900,7 +8867,7 @@
         <v>11816.12216667</v>
       </c>
     </row>
-    <row r="604" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:4">
       <c r="A604" s="1" t="s">
         <v>6</v>
       </c>
@@ -8911,10 +8878,10 @@
         <v>46173</v>
       </c>
       <c r="D604" s="3">
-        <v>9991.3053333299995</v>
-      </c>
-    </row>
-    <row r="605" spans="1:4" x14ac:dyDescent="0.25">
+        <v>9991.305333329999</v>
+      </c>
+    </row>
+    <row r="605" spans="1:4">
       <c r="A605" s="1" t="s">
         <v>7</v>
       </c>
@@ -8925,10 +8892,10 @@
         <v>46173</v>
       </c>
       <c r="D605" s="3">
-        <v>35604.140333329997</v>
-      </c>
-    </row>
-    <row r="606" spans="1:4" x14ac:dyDescent="0.25">
+        <v>35604.14033333</v>
+      </c>
+    </row>
+    <row r="606" spans="1:4">
       <c r="A606" s="1" t="s">
         <v>4</v>
       </c>
@@ -8939,10 +8906,10 @@
         <v>46174</v>
       </c>
       <c r="D606" s="3">
-        <v>8217.8950000000004</v>
-      </c>
-    </row>
-    <row r="607" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8217.895</v>
+      </c>
+    </row>
+    <row r="607" spans="1:4">
       <c r="A607" s="1" t="s">
         <v>5</v>
       </c>
@@ -8953,10 +8920,10 @@
         <v>46174</v>
       </c>
       <c r="D607" s="3">
-        <v>13220.581541670001</v>
-      </c>
-    </row>
-    <row r="608" spans="1:4" x14ac:dyDescent="0.25">
+        <v>13220.58154167</v>
+      </c>
+    </row>
+    <row r="608" spans="1:4">
       <c r="A608" s="1" t="s">
         <v>6</v>
       </c>
@@ -8967,10 +8934,10 @@
         <v>46174</v>
       </c>
       <c r="D608" s="3">
-        <v>13016.418166670001</v>
-      </c>
-    </row>
-    <row r="609" spans="1:4" x14ac:dyDescent="0.25">
+        <v>13016.41816667</v>
+      </c>
+    </row>
+    <row r="609" spans="1:4">
       <c r="A609" s="1" t="s">
         <v>7</v>
       </c>
@@ -8984,7 +8951,7 @@
         <v>40839.57191667</v>
       </c>
     </row>
-    <row r="610" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:4">
       <c r="A610" s="1" t="s">
         <v>4</v>
       </c>
@@ -8995,10 +8962,10 @@
         <v>46175</v>
       </c>
       <c r="D610" s="3">
-        <v>7759.6327083300002</v>
-      </c>
-    </row>
-    <row r="611" spans="1:4" x14ac:dyDescent="0.25">
+        <v>7759.63270833</v>
+      </c>
+    </row>
+    <row r="611" spans="1:4">
       <c r="A611" s="1" t="s">
         <v>5</v>
       </c>
@@ -9009,10 +8976,10 @@
         <v>46175</v>
       </c>
       <c r="D611" s="3">
-        <v>13539.47204167</v>
-      </c>
-    </row>
-    <row r="612" spans="1:4" x14ac:dyDescent="0.25">
+        <v>13539.28283333</v>
+      </c>
+    </row>
+    <row r="612" spans="1:4">
       <c r="A612" s="1" t="s">
         <v>6</v>
       </c>
@@ -9026,7 +8993,7 @@
         <v>13520.975</v>
       </c>
     </row>
-    <row r="613" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:4">
       <c r="A613" s="1" t="s">
         <v>7</v>
       </c>
@@ -9037,10 +9004,10 @@
         <v>46175</v>
       </c>
       <c r="D613" s="3">
-        <v>41164.650791669999</v>
-      </c>
-    </row>
-    <row r="614" spans="1:4" x14ac:dyDescent="0.25">
+        <v>41164.65079167</v>
+      </c>
+    </row>
+    <row r="614" spans="1:4">
       <c r="A614" s="1" t="s">
         <v>4</v>
       </c>
@@ -9051,10 +9018,10 @@
         <v>46176</v>
       </c>
       <c r="D614" s="3">
-        <v>8063.9354583300001</v>
-      </c>
-    </row>
-    <row r="615" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8063.93545833</v>
+      </c>
+    </row>
+    <row r="615" spans="1:4">
       <c r="A615" s="1" t="s">
         <v>5</v>
       </c>
@@ -9065,10 +9032,10 @@
         <v>46176</v>
       </c>
       <c r="D615" s="3">
-        <v>13689.659750000001</v>
-      </c>
-    </row>
-    <row r="616" spans="1:4" x14ac:dyDescent="0.25">
+        <v>13689.47433333</v>
+      </c>
+    </row>
+    <row r="616" spans="1:4">
       <c r="A616" s="1" t="s">
         <v>6</v>
       </c>
@@ -9082,7 +9049,7 @@
         <v>13425.90620833</v>
       </c>
     </row>
-    <row r="617" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:4">
       <c r="A617" s="1" t="s">
         <v>7</v>
       </c>
@@ -9093,10 +9060,10 @@
         <v>46176</v>
       </c>
       <c r="D617" s="3">
-        <v>41144.020499999999</v>
-      </c>
-    </row>
-    <row r="618" spans="1:4" x14ac:dyDescent="0.25">
+        <v>41144.0205</v>
+      </c>
+    </row>
+    <row r="618" spans="1:4">
       <c r="A618" s="1" t="s">
         <v>4</v>
       </c>
@@ -9107,10 +9074,10 @@
         <v>46177</v>
       </c>
       <c r="D618" s="3">
-        <v>7924.8829166699998</v>
-      </c>
-    </row>
-    <row r="619" spans="1:4" x14ac:dyDescent="0.25">
+        <v>7924.88291667</v>
+      </c>
+    </row>
+    <row r="619" spans="1:4">
       <c r="A619" s="1" t="s">
         <v>5</v>
       </c>
@@ -9121,10 +9088,10 @@
         <v>46177</v>
       </c>
       <c r="D619" s="3">
-        <v>12863.44441667</v>
-      </c>
-    </row>
-    <row r="620" spans="1:4" x14ac:dyDescent="0.25">
+        <v>12863.29954167</v>
+      </c>
+    </row>
+    <row r="620" spans="1:4">
       <c r="A620" s="1" t="s">
         <v>6</v>
       </c>
@@ -9135,10 +9102,10 @@
         <v>46177</v>
       </c>
       <c r="D620" s="3">
-        <v>12295.203958329999</v>
-      </c>
-    </row>
-    <row r="621" spans="1:4" x14ac:dyDescent="0.25">
+        <v>12295.20395833</v>
+      </c>
+    </row>
+    <row r="621" spans="1:4">
       <c r="A621" s="1" t="s">
         <v>7</v>
       </c>
@@ -9149,10 +9116,10 @@
         <v>46177</v>
       </c>
       <c r="D621" s="3">
-        <v>38230.37079167</v>
-      </c>
-    </row>
-    <row r="622" spans="1:4" x14ac:dyDescent="0.25">
+        <v>38230.37075</v>
+      </c>
+    </row>
+    <row r="622" spans="1:4">
       <c r="A622" s="1" t="s">
         <v>4</v>
       </c>
@@ -9163,10 +9130,10 @@
         <v>46178</v>
       </c>
       <c r="D622" s="3">
-        <v>8476.7687916699997</v>
-      </c>
-    </row>
-    <row r="623" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8476.76879167</v>
+      </c>
+    </row>
+    <row r="623" spans="1:4">
       <c r="A623" s="1" t="s">
         <v>5</v>
       </c>
@@ -9177,10 +9144,10 @@
         <v>46178</v>
       </c>
       <c r="D623" s="3">
-        <v>12941.46541667</v>
-      </c>
-    </row>
-    <row r="624" spans="1:4" x14ac:dyDescent="0.25">
+        <v>12941.32675</v>
+      </c>
+    </row>
+    <row r="624" spans="1:4">
       <c r="A624" s="1" t="s">
         <v>6</v>
       </c>
@@ -9194,7 +9161,7 @@
         <v>12694.803375</v>
       </c>
     </row>
-    <row r="625" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:4">
       <c r="A625" s="1" t="s">
         <v>7</v>
       </c>
@@ -9205,10 +9172,10 @@
         <v>46178</v>
       </c>
       <c r="D625" s="3">
-        <v>38778.864083330001</v>
-      </c>
-    </row>
-    <row r="626" spans="1:4" x14ac:dyDescent="0.25">
+        <v>38778.77395833</v>
+      </c>
+    </row>
+    <row r="626" spans="1:4">
       <c r="A626" s="1" t="s">
         <v>4</v>
       </c>
@@ -9219,10 +9186,10 @@
         <v>46179</v>
       </c>
       <c r="D626" s="3">
-        <v>7767.6690833299999</v>
-      </c>
-    </row>
-    <row r="627" spans="1:4" x14ac:dyDescent="0.25">
+        <v>7767.66908333</v>
+      </c>
+    </row>
+    <row r="627" spans="1:4">
       <c r="A627" s="1" t="s">
         <v>5</v>
       </c>
@@ -9233,10 +9200,10 @@
         <v>46179</v>
       </c>
       <c r="D627" s="3">
-        <v>12271.314666669999</v>
-      </c>
-    </row>
-    <row r="628" spans="1:4" x14ac:dyDescent="0.25">
+        <v>12271.152125</v>
+      </c>
+    </row>
+    <row r="628" spans="1:4">
       <c r="A628" s="1" t="s">
         <v>6</v>
       </c>
@@ -9250,7 +9217,7 @@
         <v>11315.6975</v>
       </c>
     </row>
-    <row r="629" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:4">
       <c r="A629" s="1" t="s">
         <v>7</v>
       </c>
@@ -9261,10 +9228,10 @@
         <v>46179</v>
       </c>
       <c r="D629" s="3">
-        <v>36276.983458330003</v>
-      </c>
-    </row>
-    <row r="630" spans="1:4" x14ac:dyDescent="0.25">
+        <v>36276.92770833</v>
+      </c>
+    </row>
+    <row r="630" spans="1:4">
       <c r="A630" s="1" t="s">
         <v>4</v>
       </c>
@@ -9275,10 +9242,10 @@
         <v>46180</v>
       </c>
       <c r="D630" s="3">
-        <v>7921.3678749999999</v>
-      </c>
-    </row>
-    <row r="631" spans="1:4" x14ac:dyDescent="0.25">
+        <v>7921.367875</v>
+      </c>
+    </row>
+    <row r="631" spans="1:4">
       <c r="A631" s="1" t="s">
         <v>5</v>
       </c>
@@ -9289,10 +9256,10 @@
         <v>46180</v>
       </c>
       <c r="D631" s="3">
-        <v>11363.388499999999</v>
-      </c>
-    </row>
-    <row r="632" spans="1:4" x14ac:dyDescent="0.25">
+        <v>11363.21370833</v>
+      </c>
+    </row>
+    <row r="632" spans="1:4">
       <c r="A632" s="1" t="s">
         <v>6</v>
       </c>
@@ -9303,10 +9270,10 @@
         <v>46180</v>
       </c>
       <c r="D632" s="3">
-        <v>10592.695458329999</v>
-      </c>
-    </row>
-    <row r="633" spans="1:4" x14ac:dyDescent="0.25">
+        <v>10592.69545833</v>
+      </c>
+    </row>
+    <row r="633" spans="1:4">
       <c r="A633" s="1" t="s">
         <v>7</v>
       </c>
@@ -9317,10 +9284,10 @@
         <v>46180</v>
       </c>
       <c r="D633" s="3">
-        <v>33860.595791669999</v>
-      </c>
-    </row>
-    <row r="634" spans="1:4" x14ac:dyDescent="0.25">
+        <v>33860.52316667</v>
+      </c>
+    </row>
+    <row r="634" spans="1:4">
       <c r="A634" s="1" t="s">
         <v>4</v>
       </c>
@@ -9331,10 +9298,10 @@
         <v>46181</v>
       </c>
       <c r="D634" s="3">
-        <v>8399.3372916699991</v>
-      </c>
-    </row>
-    <row r="635" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8399.337291669999</v>
+      </c>
+    </row>
+    <row r="635" spans="1:4">
       <c r="A635" s="1" t="s">
         <v>5</v>
       </c>
@@ -9345,10 +9312,10 @@
         <v>46181</v>
       </c>
       <c r="D635" s="3">
-        <v>12804.44183333</v>
-      </c>
-    </row>
-    <row r="636" spans="1:4" x14ac:dyDescent="0.25">
+        <v>12804.356125</v>
+      </c>
+    </row>
+    <row r="636" spans="1:4">
       <c r="A636" s="1" t="s">
         <v>6</v>
       </c>
@@ -9359,10 +9326,10 @@
         <v>46181</v>
       </c>
       <c r="D636" s="3">
-        <v>13880.486208329999</v>
-      </c>
-    </row>
-    <row r="637" spans="1:4" x14ac:dyDescent="0.25">
+        <v>13880.48620833</v>
+      </c>
+    </row>
+    <row r="637" spans="1:4">
       <c r="A637" s="1" t="s">
         <v>7</v>
       </c>
@@ -9373,10 +9340,10 @@
         <v>46181</v>
       </c>
       <c r="D637" s="3">
-        <v>39493.378708329998</v>
-      </c>
-    </row>
-    <row r="638" spans="1:4" x14ac:dyDescent="0.25">
+        <v>39493.24379167</v>
+      </c>
+    </row>
+    <row r="638" spans="1:4">
       <c r="A638" s="1" t="s">
         <v>4</v>
       </c>
@@ -9387,10 +9354,10 @@
         <v>46182</v>
       </c>
       <c r="D638" s="3">
-        <v>8266.5918750000001</v>
-      </c>
-    </row>
-    <row r="639" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8266.591875</v>
+      </c>
+    </row>
+    <row r="639" spans="1:4">
       <c r="A639" s="1" t="s">
         <v>5</v>
       </c>
@@ -9401,10 +9368,10 @@
         <v>46182</v>
       </c>
       <c r="D639" s="3">
-        <v>13117.771083330001</v>
-      </c>
-    </row>
-    <row r="640" spans="1:4" x14ac:dyDescent="0.25">
+        <v>13117.74070833</v>
+      </c>
+    </row>
+    <row r="640" spans="1:4">
       <c r="A640" s="1" t="s">
         <v>6</v>
       </c>
@@ -9418,7 +9385,7 @@
         <v>14353.82333333</v>
       </c>
     </row>
-    <row r="641" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:4">
       <c r="A641" s="1" t="s">
         <v>7</v>
       </c>
@@ -9429,10 +9396,10 @@
         <v>46182</v>
       </c>
       <c r="D641" s="3">
-        <v>41323.16108333</v>
-      </c>
-    </row>
-    <row r="642" spans="1:4" x14ac:dyDescent="0.25">
+        <v>41322.966625</v>
+      </c>
+    </row>
+    <row r="642" spans="1:4">
       <c r="A642" s="1" t="s">
         <v>4</v>
       </c>
@@ -9443,10 +9410,10 @@
         <v>46183</v>
       </c>
       <c r="D642" s="3">
-        <v>8688.4266250000001</v>
-      </c>
-    </row>
-    <row r="643" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8688.426625</v>
+      </c>
+    </row>
+    <row r="643" spans="1:4">
       <c r="A643" s="1" t="s">
         <v>5</v>
       </c>
@@ -9457,10 +9424,10 @@
         <v>46183</v>
       </c>
       <c r="D643" s="3">
-        <v>13044.752</v>
-      </c>
-    </row>
-    <row r="644" spans="1:4" x14ac:dyDescent="0.25">
+        <v>13044.674</v>
+      </c>
+    </row>
+    <row r="644" spans="1:4">
       <c r="A644" s="1" t="s">
         <v>6</v>
       </c>
@@ -9474,7 +9441,7 @@
         <v>15051.935125</v>
       </c>
     </row>
-    <row r="645" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:4">
       <c r="A645" s="1" t="s">
         <v>7</v>
       </c>
@@ -9485,10 +9452,10 @@
         <v>46183</v>
       </c>
       <c r="D645" s="3">
-        <v>42040.66704167</v>
-      </c>
-    </row>
-    <row r="646" spans="1:4" x14ac:dyDescent="0.25">
+        <v>42040.49404167</v>
+      </c>
+    </row>
+    <row r="646" spans="1:4">
       <c r="A646" s="1" t="s">
         <v>4</v>
       </c>
@@ -9499,10 +9466,10 @@
         <v>46184</v>
       </c>
       <c r="D646" s="3">
-        <v>8769.2296666700004</v>
-      </c>
-    </row>
-    <row r="647" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8769.22966667</v>
+      </c>
+    </row>
+    <row r="647" spans="1:4">
       <c r="A647" s="1" t="s">
         <v>5</v>
       </c>
@@ -9513,10 +9480,10 @@
         <v>46184</v>
       </c>
       <c r="D647" s="3">
-        <v>13081.633250000001</v>
-      </c>
-    </row>
-    <row r="648" spans="1:4" x14ac:dyDescent="0.25">
+        <v>13081.58291667</v>
+      </c>
+    </row>
+    <row r="648" spans="1:4">
       <c r="A648" s="1" t="s">
         <v>6</v>
       </c>
@@ -9530,7 +9497,7 @@
         <v>14705.218625</v>
       </c>
     </row>
-    <row r="649" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:4">
       <c r="A649" s="1" t="s">
         <v>7</v>
       </c>
@@ -9541,10 +9508,10 @@
         <v>46184</v>
       </c>
       <c r="D649" s="3">
-        <v>43146.462791669997</v>
-      </c>
-    </row>
-    <row r="650" spans="1:4" x14ac:dyDescent="0.25">
+        <v>43146.34008333</v>
+      </c>
+    </row>
+    <row r="650" spans="1:4">
       <c r="A650" s="1" t="s">
         <v>4</v>
       </c>
@@ -9555,10 +9522,10 @@
         <v>46185</v>
       </c>
       <c r="D650" s="3">
-        <v>8957.1641666699998</v>
-      </c>
-    </row>
-    <row r="651" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8957.16416667</v>
+      </c>
+    </row>
+    <row r="651" spans="1:4">
       <c r="A651" s="1" t="s">
         <v>5</v>
       </c>
@@ -9569,10 +9536,10 @@
         <v>46185</v>
       </c>
       <c r="D651" s="3">
-        <v>13240.81925</v>
-      </c>
-    </row>
-    <row r="652" spans="1:4" x14ac:dyDescent="0.25">
+        <v>13240.66754167</v>
+      </c>
+    </row>
+    <row r="652" spans="1:4">
       <c r="A652" s="1" t="s">
         <v>6</v>
       </c>
@@ -9586,7 +9553,7 @@
         <v>14337.76525</v>
       </c>
     </row>
-    <row r="653" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:4">
       <c r="A653" s="1" t="s">
         <v>7</v>
       </c>
@@ -9597,10 +9564,10 @@
         <v>46185</v>
       </c>
       <c r="D653" s="3">
-        <v>43811.22</v>
-      </c>
-    </row>
-    <row r="654" spans="1:4" x14ac:dyDescent="0.25">
+        <v>43811.11070833</v>
+      </c>
+    </row>
+    <row r="654" spans="1:4">
       <c r="A654" s="1" t="s">
         <v>4</v>
       </c>
@@ -9611,10 +9578,10 @@
         <v>46186</v>
       </c>
       <c r="D654" s="3">
-        <v>8538.7175416699993</v>
-      </c>
-    </row>
-    <row r="655" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8538.717541669999</v>
+      </c>
+    </row>
+    <row r="655" spans="1:4">
       <c r="A655" s="1" t="s">
         <v>5</v>
       </c>
@@ -9625,10 +9592,10 @@
         <v>46186</v>
       </c>
       <c r="D655" s="3">
-        <v>12635.41616667</v>
-      </c>
-    </row>
-    <row r="656" spans="1:4" x14ac:dyDescent="0.25">
+        <v>12635.206125</v>
+      </c>
+    </row>
+    <row r="656" spans="1:4">
       <c r="A656" s="1" t="s">
         <v>6</v>
       </c>
@@ -9639,10 +9606,10 @@
         <v>46186</v>
       </c>
       <c r="D656" s="3">
-        <v>11827.635333329999</v>
-      </c>
-    </row>
-    <row r="657" spans="1:4" x14ac:dyDescent="0.25">
+        <v>11827.63533333</v>
+      </c>
+    </row>
+    <row r="657" spans="1:4">
       <c r="A657" s="1" t="s">
         <v>7</v>
       </c>
@@ -9653,10 +9620,10 @@
         <v>46186</v>
       </c>
       <c r="D657" s="3">
-        <v>41327.383875</v>
-      </c>
-    </row>
-    <row r="658" spans="1:4" x14ac:dyDescent="0.25">
+        <v>41327.22725</v>
+      </c>
+    </row>
+    <row r="658" spans="1:4">
       <c r="A658" s="1" t="s">
         <v>4</v>
       </c>
@@ -9667,10 +9634,10 @@
         <v>46187</v>
       </c>
       <c r="D658" s="3">
-        <v>8322.0361250000005</v>
-      </c>
-    </row>
-    <row r="659" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8322.036125000001</v>
+      </c>
+    </row>
+    <row r="659" spans="1:4">
       <c r="A659" s="1" t="s">
         <v>5</v>
       </c>
@@ -9681,10 +9648,10 @@
         <v>46187</v>
       </c>
       <c r="D659" s="3">
-        <v>12035.67554167</v>
-      </c>
-    </row>
-    <row r="660" spans="1:4" x14ac:dyDescent="0.25">
+        <v>12035.494</v>
+      </c>
+    </row>
+    <row r="660" spans="1:4">
       <c r="A660" s="1" t="s">
         <v>6</v>
       </c>
@@ -9695,10 +9662,10 @@
         <v>46187</v>
       </c>
       <c r="D660" s="3">
-        <v>10805.570791669999</v>
-      </c>
-    </row>
-    <row r="661" spans="1:4" x14ac:dyDescent="0.25">
+        <v>10805.57079167</v>
+      </c>
+    </row>
+    <row r="661" spans="1:4">
       <c r="A661" s="1" t="s">
         <v>7</v>
       </c>
@@ -9709,10 +9676,10 @@
         <v>46187</v>
       </c>
       <c r="D661" s="3">
-        <v>38387.525874999999</v>
-      </c>
-    </row>
-    <row r="662" spans="1:4" x14ac:dyDescent="0.25">
+        <v>38387.404625</v>
+      </c>
+    </row>
+    <row r="662" spans="1:4">
       <c r="A662" s="1" t="s">
         <v>4</v>
       </c>
@@ -9723,10 +9690,10 @@
         <v>46188</v>
       </c>
       <c r="D662" s="3">
-        <v>8771.2761666700007</v>
-      </c>
-    </row>
-    <row r="663" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8771.276166670001</v>
+      </c>
+    </row>
+    <row r="663" spans="1:4">
       <c r="A663" s="1" t="s">
         <v>5</v>
       </c>
@@ -9737,10 +9704,10 @@
         <v>46188</v>
       </c>
       <c r="D663" s="3">
-        <v>13387.41179167</v>
-      </c>
-    </row>
-    <row r="664" spans="1:4" x14ac:dyDescent="0.25">
+        <v>13387.24845833</v>
+      </c>
+    </row>
+    <row r="664" spans="1:4">
       <c r="A664" s="1" t="s">
         <v>6</v>
       </c>
@@ -9754,7 +9721,7 @@
         <v>14305.4195</v>
       </c>
     </row>
-    <row r="665" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:4">
       <c r="A665" s="1" t="s">
         <v>7</v>
       </c>
@@ -9765,10 +9732,10 @@
         <v>46188</v>
       </c>
       <c r="D665" s="3">
-        <v>43741.538124999999</v>
-      </c>
-    </row>
-    <row r="666" spans="1:4" x14ac:dyDescent="0.25">
+        <v>43737.34183333</v>
+      </c>
+    </row>
+    <row r="666" spans="1:4">
       <c r="A666" s="1" t="s">
         <v>4</v>
       </c>
@@ -9779,10 +9746,10 @@
         <v>46189</v>
       </c>
       <c r="D666" s="3">
-        <v>8127.4784583299997</v>
-      </c>
-    </row>
-    <row r="667" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8127.47845833</v>
+      </c>
+    </row>
+    <row r="667" spans="1:4">
       <c r="A667" s="1" t="s">
         <v>5</v>
       </c>
@@ -9793,10 +9760,10 @@
         <v>46189</v>
       </c>
       <c r="D667" s="3">
-        <v>13661.746958330001</v>
-      </c>
-    </row>
-    <row r="668" spans="1:4" x14ac:dyDescent="0.25">
+        <v>13661.61591667</v>
+      </c>
+    </row>
+    <row r="668" spans="1:4">
       <c r="A668" s="1" t="s">
         <v>6</v>
       </c>
@@ -9810,7 +9777,7 @@
         <v>14137.63795833</v>
       </c>
     </row>
-    <row r="669" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:4">
       <c r="A669" s="1" t="s">
         <v>7</v>
       </c>
@@ -9821,10 +9788,10 @@
         <v>46189</v>
       </c>
       <c r="D669" s="3">
-        <v>43833.277750000001</v>
-      </c>
-    </row>
-    <row r="670" spans="1:4" x14ac:dyDescent="0.25">
+        <v>43833.49245833</v>
+      </c>
+    </row>
+    <row r="670" spans="1:4">
       <c r="A670" s="1" t="s">
         <v>4</v>
       </c>
@@ -9835,10 +9802,10 @@
         <v>46190</v>
       </c>
       <c r="D670" s="3">
-        <v>8663.5353333300009</v>
-      </c>
-    </row>
-    <row r="671" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8663.535333330001</v>
+      </c>
+    </row>
+    <row r="671" spans="1:4">
       <c r="A671" s="1" t="s">
         <v>5</v>
       </c>
@@ -9852,7 +9819,7 @@
         <v>13771.50454167</v>
       </c>
     </row>
-    <row r="672" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:4">
       <c r="A672" s="1" t="s">
         <v>6</v>
       </c>
@@ -9866,7 +9833,7 @@
         <v>14091.91416667</v>
       </c>
     </row>
-    <row r="673" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:4">
       <c r="A673" s="1" t="s">
         <v>7</v>
       </c>
@@ -9877,10 +9844,10 @@
         <v>46190</v>
       </c>
       <c r="D673" s="3">
-        <v>42435.73091667</v>
-      </c>
-    </row>
-    <row r="674" spans="1:5" x14ac:dyDescent="0.25">
+        <v>42435.68195833</v>
+      </c>
+    </row>
+    <row r="674" spans="1:4">
       <c r="A674" s="1" t="s">
         <v>4</v>
       </c>
@@ -9891,10 +9858,10 @@
         <v>46191</v>
       </c>
       <c r="D674" s="3">
-        <v>8633.4685416699995</v>
-      </c>
-    </row>
-    <row r="675" spans="1:5" x14ac:dyDescent="0.25">
+        <v>8633.468541669999</v>
+      </c>
+    </row>
+    <row r="675" spans="1:4">
       <c r="A675" s="1" t="s">
         <v>5</v>
       </c>
@@ -9905,10 +9872,10 @@
         <v>46191</v>
       </c>
       <c r="D675" s="3">
-        <v>13730.852916669999</v>
-      </c>
-    </row>
-    <row r="676" spans="1:5" x14ac:dyDescent="0.25">
+        <v>13730.85291667</v>
+      </c>
+    </row>
+    <row r="676" spans="1:4">
       <c r="A676" s="1" t="s">
         <v>6</v>
       </c>
@@ -9919,10 +9886,10 @@
         <v>46191</v>
       </c>
       <c r="D676" s="3">
-        <v>14220.098749999999</v>
-      </c>
-    </row>
-    <row r="677" spans="1:5" x14ac:dyDescent="0.25">
+        <v>14220.09875</v>
+      </c>
+    </row>
+    <row r="677" spans="1:4">
       <c r="A677" s="1" t="s">
         <v>7</v>
       </c>
@@ -9933,10 +9900,10 @@
         <v>46191</v>
       </c>
       <c r="D677" s="3">
-        <v>40922.062041669997</v>
-      </c>
-    </row>
-    <row r="678" spans="1:5" x14ac:dyDescent="0.25">
+        <v>40923.45033333</v>
+      </c>
+    </row>
+    <row r="678" spans="1:4">
       <c r="A678" s="1" t="s">
         <v>4</v>
       </c>
@@ -9947,10 +9914,10 @@
         <v>46192</v>
       </c>
       <c r="D678" s="3">
-        <v>8670.2950833300001</v>
-      </c>
-    </row>
-    <row r="679" spans="1:5" x14ac:dyDescent="0.25">
+        <v>8670.29508333</v>
+      </c>
+    </row>
+    <row r="679" spans="1:4">
       <c r="A679" s="1" t="s">
         <v>5</v>
       </c>
@@ -9961,10 +9928,10 @@
         <v>46192</v>
       </c>
       <c r="D679" s="3">
-        <v>13382.899833330001</v>
-      </c>
-    </row>
-    <row r="680" spans="1:5" x14ac:dyDescent="0.25">
+        <v>13382.89983333</v>
+      </c>
+    </row>
+    <row r="680" spans="1:4">
       <c r="A680" s="1" t="s">
         <v>6</v>
       </c>
@@ -9975,10 +9942,10 @@
         <v>46192</v>
       </c>
       <c r="D680" s="3">
-        <v>14543.481750000001</v>
-      </c>
-    </row>
-    <row r="681" spans="1:5" x14ac:dyDescent="0.25">
+        <v>14543.48175</v>
+      </c>
+    </row>
+    <row r="681" spans="1:4">
       <c r="A681" s="1" t="s">
         <v>7</v>
       </c>
@@ -9989,10 +9956,10 @@
         <v>46192</v>
       </c>
       <c r="D681" s="3">
-        <v>40768.233749999999</v>
-      </c>
-    </row>
-    <row r="682" spans="1:5" x14ac:dyDescent="0.25">
+        <v>40768.69225</v>
+      </c>
+    </row>
+    <row r="682" spans="1:4">
       <c r="A682" s="1" t="s">
         <v>4</v>
       </c>
@@ -10003,11 +9970,10 @@
         <v>46193</v>
       </c>
       <c r="D682" s="3">
-        <v>8524.3106666700005</v>
-      </c>
-      <c r="E682" s="3"/>
-    </row>
-    <row r="683" spans="1:5" x14ac:dyDescent="0.25">
+        <v>8524.310666670001</v>
+      </c>
+    </row>
+    <row r="683" spans="1:4">
       <c r="A683" s="1" t="s">
         <v>5</v>
       </c>
@@ -10018,10 +9984,10 @@
         <v>46193</v>
       </c>
       <c r="D683" s="3">
-        <v>12770.021708329999</v>
-      </c>
-    </row>
-    <row r="684" spans="1:5" x14ac:dyDescent="0.25">
+        <v>12771.592875</v>
+      </c>
+    </row>
+    <row r="684" spans="1:4">
       <c r="A684" s="1" t="s">
         <v>6</v>
       </c>
@@ -10032,10 +9998,10 @@
         <v>46193</v>
       </c>
       <c r="D684" s="3">
-        <v>12603.126833329999</v>
-      </c>
-    </row>
-    <row r="685" spans="1:5" x14ac:dyDescent="0.25">
+        <v>12603.12683333</v>
+      </c>
+    </row>
+    <row r="685" spans="1:4">
       <c r="A685" s="1" t="s">
         <v>7</v>
       </c>
@@ -10046,11 +10012,10 @@
         <v>46193</v>
       </c>
       <c r="D685" s="3">
-        <v>39099.582999999999</v>
-      </c>
-      <c r="E685" s="3"/>
-    </row>
-    <row r="686" spans="1:5" x14ac:dyDescent="0.25">
+        <v>39099.583</v>
+      </c>
+    </row>
+    <row r="686" spans="1:4">
       <c r="A686" s="1" t="s">
         <v>4</v>
       </c>
@@ -10061,11 +10026,10 @@
         <v>46194</v>
       </c>
       <c r="D686" s="3">
-        <v>8155.4070833300002</v>
-      </c>
-      <c r="E686" s="3"/>
-    </row>
-    <row r="687" spans="1:5" x14ac:dyDescent="0.25">
+        <v>8155.40708333</v>
+      </c>
+    </row>
+    <row r="687" spans="1:4">
       <c r="A687" s="1" t="s">
         <v>5</v>
       </c>
@@ -10076,10 +10040,10 @@
         <v>46194</v>
       </c>
       <c r="D687" s="3">
-        <v>11805.747291670001</v>
-      </c>
-    </row>
-    <row r="688" spans="1:5" x14ac:dyDescent="0.25">
+        <v>11807.01370833</v>
+      </c>
+    </row>
+    <row r="688" spans="1:4">
       <c r="A688" s="1" t="s">
         <v>6</v>
       </c>
@@ -10093,7 +10057,7 @@
         <v>10650.739</v>
       </c>
     </row>
-    <row r="689" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:4">
       <c r="A689" s="1" t="s">
         <v>7</v>
       </c>
@@ -10104,10 +10068,10 @@
         <v>46194</v>
       </c>
       <c r="D689" s="3">
-        <v>35119.250375000003</v>
-      </c>
-    </row>
-    <row r="690" spans="1:5" x14ac:dyDescent="0.25">
+        <v>35117.57183333</v>
+      </c>
+    </row>
+    <row r="690" spans="1:4">
       <c r="A690" s="1" t="s">
         <v>4</v>
       </c>
@@ -10118,11 +10082,10 @@
         <v>46195</v>
       </c>
       <c r="D690" s="3">
-        <v>8599.8912916699992</v>
-      </c>
-      <c r="E690" s="3"/>
-    </row>
-    <row r="691" spans="1:5" x14ac:dyDescent="0.25">
+        <v>8599.891291669999</v>
+      </c>
+    </row>
+    <row r="691" spans="1:4">
       <c r="A691" s="1" t="s">
         <v>5</v>
       </c>
@@ -10133,10 +10096,10 @@
         <v>46195</v>
       </c>
       <c r="D691" s="3">
-        <v>13191.06816667</v>
-      </c>
-    </row>
-    <row r="692" spans="1:5" x14ac:dyDescent="0.25">
+        <v>13193.242625</v>
+      </c>
+    </row>
+    <row r="692" spans="1:4">
       <c r="A692" s="1" t="s">
         <v>6</v>
       </c>
@@ -10147,10 +10110,10 @@
         <v>46195</v>
       </c>
       <c r="D692" s="3">
-        <v>14363.544666670001</v>
-      </c>
-    </row>
-    <row r="693" spans="1:5" x14ac:dyDescent="0.25">
+        <v>14365.29995833</v>
+      </c>
+    </row>
+    <row r="693" spans="1:4">
       <c r="A693" s="1" t="s">
         <v>7</v>
       </c>
@@ -10161,10 +10124,10 @@
         <v>46195</v>
       </c>
       <c r="D693" s="3">
-        <v>41037.944000000003</v>
-      </c>
-    </row>
-    <row r="694" spans="1:5" x14ac:dyDescent="0.25">
+        <v>41040.07420833</v>
+      </c>
+    </row>
+    <row r="694" spans="1:4">
       <c r="A694" s="1" t="s">
         <v>4</v>
       </c>
@@ -10175,11 +10138,10 @@
         <v>46196</v>
       </c>
       <c r="D694" s="3">
-        <v>8756.4405000000006</v>
-      </c>
-      <c r="E694" s="3"/>
-    </row>
-    <row r="695" spans="1:5" x14ac:dyDescent="0.25">
+        <v>8756.440500000001</v>
+      </c>
+    </row>
+    <row r="695" spans="1:4">
       <c r="A695" s="1" t="s">
         <v>5</v>
       </c>
@@ -10190,10 +10152,10 @@
         <v>46196</v>
       </c>
       <c r="D695" s="3">
-        <v>13033.46120833</v>
-      </c>
-    </row>
-    <row r="696" spans="1:5" x14ac:dyDescent="0.25">
+        <v>13039.11270833</v>
+      </c>
+    </row>
+    <row r="696" spans="1:4">
       <c r="A696" s="1" t="s">
         <v>6</v>
       </c>
@@ -10204,10 +10166,10 @@
         <v>46196</v>
       </c>
       <c r="D696" s="3">
-        <v>14452.345458330001</v>
-      </c>
-    </row>
-    <row r="697" spans="1:5" x14ac:dyDescent="0.25">
+        <v>14456.84383333</v>
+      </c>
+    </row>
+    <row r="697" spans="1:4">
       <c r="A697" s="1" t="s">
         <v>7</v>
       </c>
@@ -10218,10 +10180,10 @@
         <v>46196</v>
       </c>
       <c r="D697" s="3">
-        <v>43724.1175</v>
-      </c>
-    </row>
-    <row r="698" spans="1:5" x14ac:dyDescent="0.25">
+        <v>43726.48745833</v>
+      </c>
+    </row>
+    <row r="698" spans="1:4">
       <c r="A698" s="1" t="s">
         <v>4</v>
       </c>
@@ -10232,11 +10194,10 @@
         <v>46197</v>
       </c>
       <c r="D698" s="3">
-        <v>8627.890625</v>
-      </c>
-      <c r="E698" s="3"/>
-    </row>
-    <row r="699" spans="1:5" x14ac:dyDescent="0.25">
+        <v>8627.983875</v>
+      </c>
+    </row>
+    <row r="699" spans="1:4">
       <c r="A699" s="1" t="s">
         <v>5</v>
       </c>
@@ -10247,10 +10208,10 @@
         <v>46197</v>
       </c>
       <c r="D699" s="3">
-        <v>12293.92425</v>
-      </c>
-    </row>
-    <row r="700" spans="1:5" x14ac:dyDescent="0.25">
+        <v>12364.718625</v>
+      </c>
+    </row>
+    <row r="700" spans="1:4">
       <c r="A700" s="1" t="s">
         <v>6</v>
       </c>
@@ -10261,10 +10222,10 @@
         <v>46197</v>
       </c>
       <c r="D700" s="3">
-        <v>14394.45629167</v>
-      </c>
-    </row>
-    <row r="701" spans="1:5" x14ac:dyDescent="0.25">
+        <v>14395.32304167</v>
+      </c>
+    </row>
+    <row r="701" spans="1:4">
       <c r="A701" s="1" t="s">
         <v>7</v>
       </c>
@@ -10275,10 +10236,10 @@
         <v>46197</v>
       </c>
       <c r="D701" s="3">
-        <v>43937.149416669999</v>
-      </c>
-    </row>
-    <row r="702" spans="1:5" x14ac:dyDescent="0.25">
+        <v>43929.97870833</v>
+      </c>
+    </row>
+    <row r="702" spans="1:4">
       <c r="A702" s="1" t="s">
         <v>4</v>
       </c>
@@ -10288,9 +10249,11 @@
       <c r="C702" s="5">
         <v>46198</v>
       </c>
-      <c r="E702" s="3"/>
-    </row>
-    <row r="703" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D702" s="3">
+        <v>8403.49020833</v>
+      </c>
+    </row>
+    <row r="703" spans="1:4">
       <c r="A703" s="1" t="s">
         <v>5</v>
       </c>
@@ -10300,8 +10263,11 @@
       <c r="C703" s="5">
         <v>46198</v>
       </c>
-    </row>
-    <row r="704" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D703" s="3">
+        <v>13418.92891667</v>
+      </c>
+    </row>
+    <row r="704" spans="1:4">
       <c r="A704" s="1" t="s">
         <v>6</v>
       </c>
@@ -10311,9 +10277,11 @@
       <c r="C704" s="5">
         <v>46198</v>
       </c>
-      <c r="E704" s="3"/>
-    </row>
-    <row r="705" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D704" s="3">
+        <v>14518.63641667</v>
+      </c>
+    </row>
+    <row r="705" spans="1:4">
       <c r="A705" s="1" t="s">
         <v>7</v>
       </c>
@@ -10323,9 +10291,179 @@
       <c r="C705" s="5">
         <v>46198</v>
       </c>
+      <c r="D705" s="3">
+        <v>43879.88066667</v>
+      </c>
+    </row>
+    <row r="706" spans="1:4">
+      <c r="A706" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B706" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C706" s="5">
+        <v>46199</v>
+      </c>
+      <c r="D706" s="3">
+        <v>8714.140458329999</v>
+      </c>
+    </row>
+    <row r="707" spans="1:4">
+      <c r="A707" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B707" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C707" s="5">
+        <v>46199</v>
+      </c>
+      <c r="D707" s="3">
+        <v>13536.81266667</v>
+      </c>
+    </row>
+    <row r="708" spans="1:4">
+      <c r="A708" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B708" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C708" s="5">
+        <v>46199</v>
+      </c>
+      <c r="D708" s="3">
+        <v>14330.92854167</v>
+      </c>
+    </row>
+    <row r="709" spans="1:4">
+      <c r="A709" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B709" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C709" s="5">
+        <v>46199</v>
+      </c>
+      <c r="D709" s="3">
+        <v>43765.89470833</v>
+      </c>
+    </row>
+    <row r="710" spans="1:4">
+      <c r="A710" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B710" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C710" s="5">
+        <v>46200</v>
+      </c>
+      <c r="D710" s="3">
+        <v>8412.966125000001</v>
+      </c>
+    </row>
+    <row r="711" spans="1:4">
+      <c r="A711" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B711" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C711" s="5">
+        <v>46200</v>
+      </c>
+      <c r="D711" s="3">
+        <v>13116.737375</v>
+      </c>
+    </row>
+    <row r="712" spans="1:4">
+      <c r="A712" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B712" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C712" s="5">
+        <v>46200</v>
+      </c>
+      <c r="D712" s="3">
+        <v>12699.45120833</v>
+      </c>
+    </row>
+    <row r="713" spans="1:4">
+      <c r="A713" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B713" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C713" s="5">
+        <v>46200</v>
+      </c>
+      <c r="D713" s="3">
+        <v>40006.476125</v>
+      </c>
+    </row>
+    <row r="714" spans="1:4">
+      <c r="A714" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B714" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C714" s="5">
+        <v>46201</v>
+      </c>
+      <c r="D714" s="3">
+        <v>8097.54870833</v>
+      </c>
+    </row>
+    <row r="715" spans="1:4">
+      <c r="A715" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B715" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C715" s="5">
+        <v>46201</v>
+      </c>
+      <c r="D715" s="3">
+        <v>11612.132625</v>
+      </c>
+    </row>
+    <row r="716" spans="1:4">
+      <c r="A716" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B716" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C716" s="5">
+        <v>46201</v>
+      </c>
+      <c r="D716" s="3">
+        <v>10710.624125</v>
+      </c>
+    </row>
+    <row r="717" spans="1:4">
+      <c r="A717" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B717" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C717" s="5">
+        <v>46201</v>
+      </c>
+      <c r="D717" s="3">
+        <v>35867.83295833</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>